--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -72,6 +72,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1_분산_EXAONE" sheetId="63" state="visible" r:id="rId63"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_ablation" sheetId="64" state="visible" r:id="rId64"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_문항부트스트랩" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_프레이밍검정" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_문항보조통계" sheetId="67" state="visible" r:id="rId67"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1803,7 +1805,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DPD_최대격차%p</t>
+          <t>Re_최대격차%p</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2057,7 +2059,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DPD_최대격차%p</t>
+          <t>Re_최대격차%p</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2570,7 +2572,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2592,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2632,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2652,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2672,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2692,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2712,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>본문 Table 2(지역축은 rq2_region.py의 RQ2_지역축)</t>
+          <t>Table 5 (region axis: RQ2_지역축 from rq2_region.py)</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2800,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>본문 Table 3 하단+캡션(시점 홀드아웃, out-of-time 베이스라인 대비)</t>
+          <t>Table 7 bottom and caption(시점 홀드아웃, out-of-time 베이스라인 대비)</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2832,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>본문 Table 3 하단+캡션(시점 홀드아웃, out-of-time 베이스라인 대비)</t>
+          <t>Table 7 bottom and caption(시점 홀드아웃, out-of-time 베이스라인 대비)</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2928,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>본문 Table 3 상단(채택 추정치)</t>
+          <t>Table 7 top(채택 추정치)</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2963,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>본문 Table 3 상단(채택 추정치)</t>
+          <t>Table 7 top(채택 추정치)</t>
         </is>
       </c>
     </row>
@@ -9059,10 +9061,6 @@
       <c r="C6" t="n">
         <v>8168</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -9087,10 +9085,6 @@
       <c r="C7" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>144</v>
       </c>
@@ -9192,8 +9186,6 @@
       <c r="G2" t="n">
         <v>0.26</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9223,8 +9215,6 @@
       <c r="G3" t="n">
         <v>0.17</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9254,8 +9244,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9285,8 +9273,6 @@
       <c r="G5" t="n">
         <v>0.17</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9316,8 +9302,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9347,8 +9331,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9378,8 +9360,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9409,8 +9389,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9440,8 +9418,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9471,8 +9447,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9502,8 +9476,6 @@
       <c r="G12" t="n">
         <v>0.33</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9533,8 +9505,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9564,8 +9534,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9595,8 +9563,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9626,8 +9592,6 @@
       <c r="G16" t="n">
         <v>5.86</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9657,8 +9621,6 @@
       <c r="G17" t="n">
         <v>0.5</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9688,8 +9650,6 @@
       <c r="G18" t="n">
         <v>0.17</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9719,8 +9679,6 @@
       <c r="G19" t="n">
         <v>0.33</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9750,8 +9708,6 @@
       <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9781,8 +9737,6 @@
       <c r="G21" t="n">
         <v>0.17</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9812,8 +9766,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9843,8 +9795,6 @@
       <c r="G23" t="n">
         <v>3.47</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9874,8 +9824,6 @@
       <c r="G24" t="n">
         <v>3.67</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9905,8 +9853,6 @@
       <c r="G25" t="n">
         <v>0.17</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9936,8 +9882,6 @@
       <c r="G26" t="n">
         <v>0.67</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9967,8 +9911,6 @@
       <c r="G27" t="n">
         <v>2.33</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9998,8 +9940,6 @@
       <c r="G28" t="n">
         <v>0.17</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10029,8 +9969,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10051,11 +9989,15 @@
           <t>10대</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>478</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10076,11 +10018,15 @@
           <t>20대</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>600</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10101,11 +10047,15 @@
           <t>30대</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>600</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10126,11 +10076,15 @@
           <t>40대</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>600</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10151,11 +10105,15 @@
           <t>50대</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>600</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10176,11 +10134,15 @@
           <t>60대</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>600</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10201,11 +10163,15 @@
           <t>70대이상</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>600</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10226,11 +10192,15 @@
           <t>10대</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>490</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10251,11 +10221,15 @@
           <t>20대</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>600</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10276,11 +10250,15 @@
           <t>30대</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>600</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10301,11 +10279,15 @@
           <t>40대</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>600</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10326,11 +10308,15 @@
           <t>50대</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>600</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10351,11 +10337,15 @@
           <t>60대</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>600</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10376,11 +10366,15 @@
           <t>70대이상</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>600</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10401,11 +10395,15 @@
           <t>10대</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>382</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10426,11 +10424,15 @@
           <t>20대</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>600</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10451,11 +10453,15 @@
           <t>30대</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>600</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10476,11 +10482,15 @@
           <t>40대</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>600</v>
+      </c>
+      <c r="H47" t="n">
+        <v>45</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10501,11 +10511,15 @@
           <t>50대</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>600</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10526,11 +10540,15 @@
           <t>60대</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>600</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.33</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10551,11 +10569,15 @@
           <t>70대이상</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>600</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10576,11 +10598,15 @@
           <t>10대</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>356</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10601,11 +10627,15 @@
           <t>20대</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>600</v>
+      </c>
+      <c r="H52" t="n">
+        <v>28</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.67</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10626,11 +10656,15 @@
           <t>30대</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>600</v>
+      </c>
+      <c r="H53" t="n">
+        <v>21</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10651,11 +10685,15 @@
           <t>40대</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>600</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.67</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10676,11 +10714,15 @@
           <t>50대</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>600</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10701,11 +10743,15 @@
           <t>60대</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>600</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10726,11 +10772,15 @@
           <t>70대이상</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>600</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11133,8 +11183,6 @@
       <c r="B4" t="n">
         <v>8234</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24942,6 +24990,341 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_통제</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_처치</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>숏폼_통제%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>숏폼_처치%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>변화%p</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>변화_CI_하한</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변화_CI_상한</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>P(숏폼|유튜브)_통제%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>P(숏폼|유튜브)_처치%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Holm_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>exaone</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>969</v>
+      </c>
+      <c r="C3" t="n">
+        <v>998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>차수</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MAE%p</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>중앙절대오차%p</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LOIO_최소</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LOIO_최대</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>숏폼제외_MAE%p</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>숏폼제외_중앙값%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -24996,7 +24996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25060,11 +25060,6 @@
           <t>P(숏폼|유튜브)_처치%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Holm_p</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25097,7 +25092,7 @@
         <v>21.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.454244210227522e-101</v>
       </c>
       <c r="K2" t="n">
         <v>32.7</v>
@@ -25105,9 +25100,6 @@
       <c r="L2" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25140,16 +25132,13 @@
         <v>13.4</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4.352803174439392e-41</v>
       </c>
       <c r="K3" t="n">
         <v>59.9</v>
       </c>
       <c r="L3" t="n">
         <v>92.59999999999999</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -24996,7 +24996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25060,6 +25060,11 @@
           <t>P(숏폼|유튜브)_처치%</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Holm_p</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25100,6 +25105,9 @@
       <c r="L2" t="n">
         <v>79.59999999999999</v>
       </c>
+      <c r="M2" t="n">
+        <v>2.908488420455043e-101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25139,6 +25147,9 @@
       </c>
       <c r="L3" t="n">
         <v>92.59999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.352803174439392e-41</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -23579,7 +23579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23615,28 +23615,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>문항평균상관r</t>
+          <t>r_이진8</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>상관_문항수</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>r_이진8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>r_구성8</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2024</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -23656,21 +23648,17 @@
         <v>0.029</v>
       </c>
       <c r="G2" t="n">
-        <v>0.957</v>
+        <v>0.795</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="J2" t="n">
         <v>0.788</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2024</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -23690,21 +23678,17 @@
         <v>0.0193</v>
       </c>
       <c r="G3" t="n">
-        <v>0.974</v>
+        <v>0.903</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2025</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -23726,16 +23710,12 @@
       <c r="G4" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="H4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.6889999999999999</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2025</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -23755,12 +23735,6 @@
         <v>0.0349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.765</v>
       </c>
     </row>
@@ -24192,7 +24166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24245,10 +24219,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="5">
@@ -24258,33 +24232,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>보정 합성 Gemini(연령회귀)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>보정 합성 EXAONE(연령회귀)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6.7</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -74,6 +74,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_문항부트스트랩" sheetId="65" state="visible" r:id="rId65"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_프레이밍검정" sheetId="66" state="visible" r:id="rId66"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_문항보조통계" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베이스라인_공통6_보정" sheetId="68" state="visible" r:id="rId68"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2788,7 +2789,7 @@
         <v>14.5</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>6.7</v>
@@ -2820,7 +2821,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>6.7</v>
@@ -25273,6 +25274,89 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>공통6_보정선형_셀MAE%p</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>전체8_보정선형_셀MAE%p</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>분할</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>층화 30/70 × 200회</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>층화 30/70 × 200회</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -75,6 +75,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_프레이밍검정" sheetId="66" state="visible" r:id="rId66"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_문항보조통계" sheetId="67" state="visible" r:id="rId67"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베이스라인_공통6_보정" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_보조수치" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_연령대별_부호오차" sheetId="70" state="visible" r:id="rId70"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1667,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1718,11 @@
           <t>상위4·5%</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1724,7 +1731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.549</v>
+        <v>0.533</v>
       </c>
       <c r="C2" t="n">
         <v>2.45</v>
@@ -1747,6 +1754,11 @@
       <c r="I2" t="n">
         <v>15</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>이진_예선택률 = 8개 이진 지표 원문항 응답 합산 '예' 비율(비가중; code/rr_misc_numbers.py, 시트 심사_보조수치와 동일 산식). v1.10 이전에 옮겨 적힌 0.549/0.602는 산식이 기록되지 않아 재현되지 않았으며 v1.11에서 정정함.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1755,7 +1767,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.602</v>
+        <v>0.582</v>
       </c>
       <c r="C3" t="n">
         <v>3.05</v>
@@ -25357,6 +25369,622 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>논문값</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>산식/출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gemini 2024 유튜브 이용률(유효 페르소나 비가중)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_gemini.csv, 유튜브_이용 단순평균 n=8168</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gemini 2024 유튜브 이용률(사후층화)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_gemini.csv, 실측 2024 셀 점유율 사후층화</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gemini 2025 유튜브 이용률(유효 페르소나 비가중)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>93.9 (IV-D, 2025 문항셋)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_2025_gemini.csv, 유튜브_이용 단순평균 n=7938</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gemini 2025 유튜브 이용률(사후층화)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_2025_gemini.csv, 실측 2025 셀 점유율 사후층화</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>실측 2025 유튜브 이용률(가중, 전체 표본)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>95.5 (IV-D)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>analysis_ready.csv 2025 전체(n=8,411), WT 가중; 만 10세 이상 표본에서는 95.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gemini 온도 1.0 대 0.7 사후층화 비율 평균절대차(이진 8지표)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>%p</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.5 (Gemini), 4.0 (EXAONE) (IV-F)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_gemini.csv vs outputs/synthetic_recoded_gemini_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=0.6, OTT_이용=1.4, 유튜브_이용=0.1, 숏폼_이용=0.4, SNS_이용=0.6, 메신저_이용=0.2, 메타버스_이용=0.5, 콘텐츠구독_이용=0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EXAONE 온도 1.0 대 0.7 사후층화 비율 평균절대차(이진 8지표)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>%p</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.5 (Gemini), 4.0 (EXAONE) (IV-F)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>outputs/synthetic_recoded_exaone.csv vs outputs/synthetic_recoded_exaone_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=1.8, OTT_이용=6.1, 유튜브_이용=4.4, 숏폼_이용=2.7, SNS_이용=3.6, 메신저_이용=5.2, 메타버스_이용=6.8, 콘텐츠구독_이용=1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>순서 실험 F1 1차 페이로드(2024 문항셋) 요청당 평균 입력 문자</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>약 4,400 (III-D, 2024 요청 추정치)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>logs/order_F1_r0c*.jsonl: 요청 1,144건, 총 5.03M 문자</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025 배치 1차 페이로드 요청당 평균 입력 문자</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1775</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>약 1,800 (III-D)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>logs/batch_w2025_r0c*.jsonl: 요청 7,938건, 총 14.09M 문자</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025 배치 전체 라운드 페이로드 요청당 평균 입력 문자</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1775</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>약 1,800 (III-D)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>logs/batch_w2025_r*c*.jsonl: 요청 7,943건, 총 14.10M 문자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025 배치 전체 라운드 페이로드 총 입력 문자</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M 문자</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14.1M (III-D)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>logs/batch_w2025_r*c*.jsonl: 요청 7,943건</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gemini 5점 문항 최상점(5) 선택 비율</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>almost never (IV-C, Gemini)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>원문항 24개 응답 196,032건; 분포 1~5 = 19.0 / 33.0 / 32.7 / 14.9 / 0.4; 상위 4-5 = 15.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gemini 5점 문항 응답 평균(원문항 24개, 비가중)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>점</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.45 (Gemini), 3.05 (EXAONE) (IV-C)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>진단_응답스타일 의 5점_평균과 동일 산식</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EXAONE 5점 문항 최상점(5) 선택 비율</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>원문항 24개 응답 195,960건; 분포 1~5 = 5.3 / 26.7 / 29.7 / 33.7 / 4.5; 상위 4-5 = 38.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EXAONE 5점 문항 응답 평균(원문항 24개, 비가중)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>점</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.45 (Gemini), 3.05 (EXAONE) (IV-C)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>진단_응답스타일 의 5점_평균과 동일 산식</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 만 10세 이상)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>점</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>analysis_ready.csv 2024 만 10세 이상, 구성개념별 WT 가중평균의 단순평균</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 전체 표본)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>점</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.83 (IV-C)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>analysis_ready.csv 2024 전체(n=8,693), 구성개념 시트의 실측_가중 8개 값의 평균</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gemini 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.533 (Gemini), 0.582 (EXAONE) (IV-C; 진단_응답스타일 의 이진_예선택률과 동일 산식; v1.10 이전의 0.549/0.602는 산식 미기록으로 재현되지 않아 v1.11에서 정정)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>응답 65,344건</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gemini 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>응답 68,824건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gemini 이진 '예' 선택률(2택 문항 9개, 문항별 비율의 평균)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>p__d31002=0.426; p__d31007=0.042; p__d26001=0.660; p__d26075=0.967; p__d26092=0.285; p__d11001=0.512; p__d22001=0.974; p__d28001=0.023; p__d29001=0.416</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EXAONE 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.533 (Gemini), 0.582 (EXAONE) (IV-C; 진단_응답스타일 의 이진_예선택률과 동일 산식; v1.10 이전의 0.549/0.602는 산식 미기록으로 재현되지 않아 v1.11에서 정정)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>응답 65,320건</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EXAONE 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>응답 68,478건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EXAONE 이진 '예' 선택률(2택 문항 9개, 문항별 비율의 평균)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>p__d31002=0.387; p__d31007=0.253; p__d26001=0.840; p__d26075=0.869; p__d26092=0.522; p__d11001=0.753; p__d22001=0.703; p__d28001=0.139; p__d29001=0.443</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -25572,6 +26200,3112 @@
       </c>
       <c r="F9" t="n">
         <v>21.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>값종류</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>10대</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>20대</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>30대</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>40대</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>50대</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>60대</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>70대이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="E3" t="n">
+        <v>83.17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="E5" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-39.94</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-63.99</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-40.03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="H10" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-10.73</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-39.94</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-64.01000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-40.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="G12" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>93.73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="J12" t="n">
+        <v>97.40000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="I13" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>78.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-18.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="I15" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>78.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-18.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="G17" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-15.63</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-51.84</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.62</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-61.93</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-50.23</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-28.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-15.76</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-51.82</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-62.67</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-61.93</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-50.21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-28.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="I22" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E23" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-30.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-35.44</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-26.19</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E25" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-31.34</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-35.44</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="F27" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="G27" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="I27" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="J27" t="n">
+        <v>60.48</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="I28" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="J28" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22.52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="I30" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="J30" t="n">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="J31" t="n">
+        <v>21.92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="H37" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="E38" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="F38" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="G38" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="E39" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="F39" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="E40" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>73.14</v>
+      </c>
+      <c r="G40" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="H40" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="E41" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="F41" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="F42" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="G42" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="F43" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="G43" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="H43" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="J43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="F44" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="G44" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="F45" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="G45" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="H45" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="I45" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AI_이용여부</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="G46" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="E47" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="G47" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="J47" t="n">
+        <v>45.87</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="E48" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="F48" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="G48" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="I48" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="J48" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-10.71</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-14.57</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21.13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="E50" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="G50" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="H50" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="I50" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="J50" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OTT_이용</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-14.63</v>
+      </c>
+      <c r="J51" t="n">
+        <v>21.13</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="E52" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="F52" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="G52" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>93.73</v>
+      </c>
+      <c r="I52" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="J52" t="n">
+        <v>97.40000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="E53" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="F53" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="I53" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="J53" t="n">
+        <v>68.58</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-28.82</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="E55" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="F55" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="H55" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="J55" t="n">
+        <v>68.59</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>유튜브_이용</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-17.68</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-28.81</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="E57" t="n">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="G57" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="J57" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="F58" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="G58" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="H58" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="J58" t="n">
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-11.37</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-24.82</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-22.41</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="E60" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="F60" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="G60" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="H60" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="I60" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="J60" t="n">
+        <v>33.09</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>숏폼_이용</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-24.82</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-17.77</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-13.03</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="F62" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G62" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="I62" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="E63" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="F63" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="G63" t="n">
+        <v>79.98</v>
+      </c>
+      <c r="H63" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I63" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="J63" t="n">
+        <v>48.08</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I64" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="J64" t="n">
+        <v>41.64</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="E65" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="F65" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="G65" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="H65" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I65" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="J65" t="n">
+        <v>48.04</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SNS_이용</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="H66" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I66" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="J66" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E67" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="F67" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="G67" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="H67" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="I67" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="J67" t="n">
+        <v>60.48</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="E68" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="F68" t="n">
+        <v>81.47</v>
+      </c>
+      <c r="G68" t="n">
+        <v>75.06</v>
+      </c>
+      <c r="H68" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="J68" t="n">
+        <v>44.17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-17.17</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-24.06</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-32.92</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-41</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-16.31</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="E70" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="G70" t="n">
+        <v>75.03</v>
+      </c>
+      <c r="H70" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="J70" t="n">
+        <v>44.11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>메신저_이용</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-10.01</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-17.18</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-24.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-32.92</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-40.98</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-16.36</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="E73" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F73" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G73" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="I73" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="J73" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="E74" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="F74" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="H74" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="I74" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="J74" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="E75" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="I75" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>메타버스_이용</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="E76" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="F76" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G76" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="H76" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="I76" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>실측_가중률%</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="E77" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="G77" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="H77" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>합성_비가중률%</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="E78" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="F78" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="G78" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="H78" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="J78" t="n">
+        <v>28.42</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>부호오차%p</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F79" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G79" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="H79" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>합성_사후층화율%</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="E80" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="F80" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="G80" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="H80" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I80" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="J80" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>콘텐츠구독_이용</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>부호오차_사후층화%p</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F81" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="G81" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="H81" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="J81" t="n">
+        <v>26.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>이진_예선택률</t>
+          <t>이진_예선택률_사후층화</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1715,12 +1715,22 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>상위4·5%</t>
+          <t>상위4-5%</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>이진_예선택률_비가중</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>실측_이진_예선택률_사후층화</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1741,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.533</v>
+        <v>0.516</v>
       </c>
       <c r="C2" t="n">
         <v>2.45</v>
@@ -1756,8 +1766,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>이진_예선택률 = 8개 이진 지표 원문항 응답 합산 '예' 비율(비가중; code/rr_misc_numbers.py, 시트 심사_보조수치와 동일 산식). v1.10 이전에 옮겨 적힌 0.549/0.602는 산식이 기록되지 않아 재현되지 않았으며 v1.11에서 정정함.</t>
-        </is>
+          <t>이진_예선택률_사후층화 = 8개 이진 지표의 사후층화 이용률 평균(RQ1_전체일치도 와 동일 산식). 실측 비교값 0.559 와 같은 기준이다. 비가중 열은 원문항 응답 합산 비율. v1.10 이전에 옮겨 적힌 0.549/0.602 는 산식이 기록되지 않아 재현되지 않았으며 v1.12에서 정정함. 5점_평균 2.45/3.05 는 원문항 24개 비가중 평균이고, 논문 IV-C 가 인용하는 값은 구성개념 8개 사후층화 평균 2.54/3.03(구성개념 시트)이다.</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1767,7 +1783,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.582</v>
+        <v>0.575</v>
       </c>
       <c r="C3" t="n">
         <v>3.05</v>
@@ -1789,6 +1805,12 @@
       </c>
       <c r="I3" t="n">
         <v>38</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5590000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11208,7 +11230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11224,40 +11246,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>짝 페르소나 n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>지표</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A_MAE%p</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>B_MAE%p</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>차이(A-B)%p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CI_하한</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CI_상한</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>부트스트랩p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Holm_p</t>
         </is>
@@ -11274,28 +11301,31 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>MAE 전체</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>17.11</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>14.92</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2.2</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.96</v>
+        <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0017</v>
+        <v>2.93</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0033</v>
       </c>
     </row>
     <row r="3">
@@ -11309,31 +11339,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>AI_이용여부</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>26.07</v>
-      </c>
       <c r="E3" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="F3" t="n">
         <v>23.28</v>
       </c>
-      <c r="F3" t="n">
-        <v>2.79</v>
-      </c>
       <c r="G3" t="n">
-        <v>1.37</v>
+        <v>2.81</v>
       </c>
       <c r="H3" t="n">
-        <v>4.12</v>
+        <v>1.66</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0017</v>
+        <v>3.97</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="4">
@@ -11347,31 +11380,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>OTT_이용</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>24.74</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5.56</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>19.18</v>
       </c>
-      <c r="G4" t="n">
-        <v>17.77</v>
-      </c>
       <c r="H4" t="n">
-        <v>20.84</v>
+        <v>17.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0017</v>
+        <v>20.77</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="5">
@@ -11385,32 +11421,35 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>유튜브_이용</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>3.73</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6.65</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-2.92</v>
       </c>
-      <c r="G5" t="n">
-        <v>-5.3</v>
-      </c>
       <c r="H5" t="n">
-        <v>-0.51</v>
+        <v>-5.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0167</v>
+        <v>-0.44</v>
       </c>
       <c r="J5" t="n">
         <v>0.0333</v>
       </c>
+      <c r="K5" t="n">
+        <v>0.06660000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11423,31 +11462,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>숏폼_이용</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>44.57</v>
-      </c>
       <c r="E6" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="F6" t="n">
         <v>18.38</v>
       </c>
-      <c r="F6" t="n">
-        <v>26.19</v>
-      </c>
       <c r="G6" t="n">
-        <v>24.56</v>
+        <v>26.18</v>
       </c>
       <c r="H6" t="n">
-        <v>27.65</v>
+        <v>24.65</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0017</v>
+        <v>27.56</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="7">
@@ -11461,31 +11503,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>SNS_이용</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>13.35</v>
-      </c>
       <c r="E7" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="F7" t="n">
         <v>13.04</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.31</v>
-      </c>
       <c r="G7" t="n">
-        <v>-3.59</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.27</v>
+        <v>-3.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.89</v>
+        <v>4.15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.89</v>
+        <v>0.8752</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8752</v>
       </c>
     </row>
     <row r="8">
@@ -11499,31 +11544,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>메신저_이용</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>5.07</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>23.11</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-18.05</v>
       </c>
-      <c r="G8" t="n">
-        <v>-20.02</v>
-      </c>
       <c r="H8" t="n">
-        <v>-15.91</v>
+        <v>-19.93</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0017</v>
+        <v>-15.89</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="9">
@@ -11537,31 +11585,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>메타버스_이용</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>3.51</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>8.09</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-4.58</v>
       </c>
-      <c r="G9" t="n">
-        <v>-6.54</v>
-      </c>
       <c r="H9" t="n">
-        <v>-2.23</v>
+        <v>-6.63</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0017</v>
+        <v>-2.47</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="10">
@@ -11575,31 +11626,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>콘텐츠구독_이용</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>15.88</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>21.21</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-5.33</v>
       </c>
-      <c r="G10" t="n">
-        <v>-7.03</v>
-      </c>
       <c r="H10" t="n">
-        <v>-3.73</v>
+        <v>-6.83</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0017</v>
+        <v>-3.64</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="11">
@@ -11613,28 +11667,31 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>MAE 전체</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>17.11</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>17.01</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.1</v>
       </c>
-      <c r="G11" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.45</v>
+        <v>0.28</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2496</v>
       </c>
     </row>
     <row r="12">
@@ -11648,31 +11705,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>AI_이용여부</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>26.07</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>26.66</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-0.59</v>
       </c>
-      <c r="G12" t="n">
-        <v>-1.67</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3033</v>
+        <v>-0.24</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="13">
@@ -11686,31 +11746,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>OTT_이용</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>24.74</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>23.37</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1.37</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.24</v>
-      </c>
       <c r="H13" t="n">
-        <v>2.47</v>
+        <v>0.76</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0167</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1167</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="14">
@@ -11724,31 +11787,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>유튜브_이용</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>3.73</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>3.61</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.12</v>
       </c>
-      <c r="G14" t="n">
-        <v>-0.31</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.58</v>
+        <v>-0.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.3195</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4592</v>
       </c>
     </row>
     <row r="15">
@@ -11762,31 +11828,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>숏폼_이용</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>44.57</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>44.12</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.45</v>
       </c>
-      <c r="G15" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="H15" t="n">
-        <v>1.41</v>
+        <v>-0.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.36</v>
+        <v>0.97</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.1198</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3594</v>
       </c>
     </row>
     <row r="16">
@@ -11800,31 +11869,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>SNS_이용</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>13.35</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>12.73</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.62</v>
       </c>
-      <c r="G16" t="n">
-        <v>-0.51</v>
-      </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>0.03</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2467</v>
+        <v>1.23</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.0499</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2163</v>
       </c>
     </row>
     <row r="17">
@@ -11838,31 +11910,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>메신저_이용</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>5.07</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>5.29</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-0.23</v>
       </c>
-      <c r="G17" t="n">
-        <v>-0.66</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.18</v>
+        <v>-0.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2567</v>
+        <v>-0.01</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.0433</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2163</v>
       </c>
     </row>
     <row r="18">
@@ -11876,31 +11951,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>메타버스_이용</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>3.51</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>4.05</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-0.54</v>
       </c>
-      <c r="G18" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="H18" t="n">
-        <v>-0.17</v>
+        <v>-0.76</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01</v>
+        <v>-0.31</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="19">
@@ -11914,31 +11992,34 @@
           <t>Gemini t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>콘텐츠구독_이용</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>15.88</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>16.26</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G19" t="n">
-        <v>-1.49</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.73</v>
+        <v>-0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5033</v>
+        <v>0.26</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.2296</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4592</v>
       </c>
     </row>
     <row r="20">
@@ -11952,28 +12033,31 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>MAE 전체</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>14.92</v>
-      </c>
       <c r="E20" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="F20" t="n">
         <v>11.99</v>
       </c>
-      <c r="F20" t="n">
-        <v>2.92</v>
-      </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="H20" t="n">
-        <v>3.41</v>
+        <v>2.51</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0017</v>
+        <v>3.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0033</v>
       </c>
     </row>
     <row r="21">
@@ -11987,31 +12071,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>AI_이용여부</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>23.28</v>
       </c>
-      <c r="E21" t="n">
-        <v>21.53</v>
-      </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>21.52</v>
       </c>
       <c r="G21" t="n">
-        <v>0.47</v>
+        <v>1.76</v>
       </c>
       <c r="H21" t="n">
-        <v>3.08</v>
+        <v>0.61</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0033</v>
+        <v>2.96</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0133</v>
+        <v>0.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="22">
@@ -12025,31 +12112,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>OTT_이용</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>5.56</v>
-      </c>
       <c r="E22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.53</v>
       </c>
-      <c r="F22" t="n">
-        <v>5.03</v>
-      </c>
       <c r="G22" t="n">
-        <v>3.07</v>
+        <v>4.97</v>
       </c>
       <c r="H22" t="n">
-        <v>6.45</v>
+        <v>3.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0017</v>
+        <v>6.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="23">
@@ -12063,31 +12153,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>유튜브_이용</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>6.65</v>
-      </c>
       <c r="E23" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="F23" t="n">
         <v>2.27</v>
       </c>
-      <c r="F23" t="n">
-        <v>4.38</v>
-      </c>
       <c r="G23" t="n">
-        <v>3.47</v>
+        <v>4.31</v>
       </c>
       <c r="H23" t="n">
-        <v>5.32</v>
+        <v>3.41</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0017</v>
+        <v>5.19</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="24">
@@ -12101,31 +12194,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>숏폼_이용</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>18.38</v>
-      </c>
       <c r="E24" t="n">
-        <v>15.67</v>
+        <v>18.36</v>
       </c>
       <c r="F24" t="n">
-        <v>2.72</v>
+        <v>15.65</v>
       </c>
       <c r="G24" t="n">
-        <v>1.28</v>
+        <v>2.71</v>
       </c>
       <c r="H24" t="n">
-        <v>4.22</v>
+        <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0017</v>
+        <v>4.06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="25">
@@ -12139,31 +12235,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>SNS_이용</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>13.04</v>
-      </c>
       <c r="E25" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="F25" t="n">
         <v>16.62</v>
       </c>
-      <c r="F25" t="n">
-        <v>-3.58</v>
-      </c>
       <c r="G25" t="n">
-        <v>-4.75</v>
+        <v>-3.53</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.27</v>
+        <v>-4.86</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0017</v>
+        <v>-2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="26">
@@ -12177,31 +12276,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>메신저_이용</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>23.11</v>
-      </c>
       <c r="E26" t="n">
-        <v>17.92</v>
+        <v>23.15</v>
       </c>
       <c r="F26" t="n">
-        <v>5.19</v>
+        <v>17.93</v>
       </c>
       <c r="G26" t="n">
-        <v>3.83</v>
+        <v>5.22</v>
       </c>
       <c r="H26" t="n">
-        <v>6.46</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0017</v>
+        <v>6.42</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="27">
@@ -12215,31 +12317,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>메타버스_이용</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>8.09</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>1.27</v>
       </c>
-      <c r="F27" t="n">
-        <v>6.82</v>
-      </c>
       <c r="G27" t="n">
-        <v>5.93</v>
+        <v>6.81</v>
       </c>
       <c r="H27" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0017</v>
+        <v>7.72</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="28">
@@ -12253,31 +12358,34 @@
           <t>EXAONE t1.0 − t0.7</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>콘텐츠구독_이용</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>21.21</v>
-      </c>
       <c r="E28" t="n">
-        <v>20.12</v>
+        <v>21.25</v>
       </c>
       <c r="F28" t="n">
-        <v>1.09</v>
+        <v>20.1</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.23</v>
+        <v>1.15</v>
       </c>
       <c r="H28" t="n">
-        <v>2.62</v>
+        <v>-0.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1333</v>
+        <v>2.65</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1333</v>
+        <v>0.1331</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1331</v>
       </c>
     </row>
     <row r="29">
@@ -12291,28 +12399,31 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>MAE 전체</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>19.35</v>
-      </c>
       <c r="E29" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="F29" t="n">
         <v>16.66</v>
       </c>
-      <c r="F29" t="n">
-        <v>2.69</v>
-      </c>
       <c r="G29" t="n">
-        <v>2.06</v>
+        <v>2.68</v>
       </c>
       <c r="H29" t="n">
-        <v>3.27</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0017</v>
+        <v>3.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0033</v>
       </c>
     </row>
     <row r="30">
@@ -12326,31 +12437,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>AI_이용여부</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>5.18</v>
-      </c>
       <c r="E30" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="F30" t="n">
         <v>11.59</v>
       </c>
-      <c r="F30" t="n">
-        <v>-6.41</v>
-      </c>
       <c r="G30" t="n">
-        <v>-7.86</v>
+        <v>-6.56</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.96</v>
+        <v>-7.79</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0017</v>
+        <v>-5.14</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="31">
@@ -12364,31 +12478,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>OTT_이용</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>35.09</v>
-      </c>
       <c r="E31" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F31" t="n">
         <v>11.06</v>
       </c>
-      <c r="F31" t="n">
-        <v>24.03</v>
-      </c>
       <c r="G31" t="n">
-        <v>22.25</v>
+        <v>24.04</v>
       </c>
       <c r="H31" t="n">
-        <v>25.8</v>
+        <v>22.27</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0017</v>
+        <v>25.62</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="32">
@@ -12402,31 +12519,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>유튜브_이용</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>1.49</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>12.85</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>-11.36</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H32" t="n">
-        <v>-10.43</v>
-      </c>
       <c r="I32" t="n">
-        <v>0.0017</v>
+        <v>-10.48</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="33">
@@ -12440,31 +12560,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>숏폼_이용</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>72.3</v>
-      </c>
       <c r="E33" t="n">
+        <v>72.31</v>
+      </c>
+      <c r="F33" t="n">
         <v>57.81</v>
       </c>
-      <c r="F33" t="n">
-        <v>14.48</v>
-      </c>
       <c r="G33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H33" t="n">
         <v>13.15</v>
       </c>
-      <c r="H33" t="n">
-        <v>15.89</v>
-      </c>
       <c r="I33" t="n">
-        <v>0.0017</v>
+        <v>15.98</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="34">
@@ -12478,31 +12601,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>SNS_이용</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>24.84</v>
-      </c>
       <c r="E34" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" t="n">
         <v>7.05</v>
       </c>
-      <c r="F34" t="n">
-        <v>17.8</v>
-      </c>
       <c r="G34" t="n">
-        <v>14.35</v>
+        <v>17.95</v>
       </c>
       <c r="H34" t="n">
-        <v>21.81</v>
+        <v>14.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0017</v>
+        <v>21.98</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="35">
@@ -12516,31 +12642,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>메신저_이용</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0.33</v>
-      </c>
       <c r="E35" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F35" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" t="n">
-        <v>-20.47</v>
-      </c>
       <c r="G35" t="n">
-        <v>-21.69</v>
+        <v>-20.48</v>
       </c>
       <c r="H35" t="n">
-        <v>-18.78</v>
+        <v>-21.73</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0017</v>
+        <v>-18.92</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="36">
@@ -12554,31 +12683,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>메타버스_이용</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>5.29</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.02</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>5.26</v>
       </c>
-      <c r="G36" t="n">
-        <v>2.9</v>
-      </c>
       <c r="H36" t="n">
-        <v>5.78</v>
+        <v>2.99</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0017</v>
+        <v>5.73</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0133</v>
+        <v>0.0033</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="37">
@@ -12592,31 +12724,34 @@
           <t>Gemini − EXAONE</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>콘텐츠구독_이용</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>10.31</v>
-      </c>
       <c r="E37" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F37" t="n">
         <v>12.1</v>
       </c>
-      <c r="F37" t="n">
-        <v>-1.79</v>
-      </c>
       <c r="G37" t="n">
-        <v>-3.54</v>
+        <v>-1.9</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.28</v>
+        <v>-3.35</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0267</v>
+        <v>-0.46</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0267</v>
+        <v>0.0233</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.0266</v>
       </c>
     </row>
   </sheetData>
@@ -12710,7 +12845,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.785, 0.804]</t>
+          <t>[0.785, 0.805]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12754,12 +12889,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.785, 0.805]</t>
+          <t>[0.786, 0.805]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[0.788, 0.808]</t>
+          <t>[0.789, 0.808]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -12803,7 +12938,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[0.908, 0.922]</t>
+          <t>[0.909, 0.922]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -12842,12 +12977,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0.681, 0.700]</t>
+          <t>[0.680, 0.701]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[0.755, 0.779]</t>
+          <t>[0.755, 0.778]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -22850,7 +22985,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="I2" t="n">
         <v>-0.5</v>
@@ -22867,7 +23002,7 @@
         <v>5.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="3">
@@ -22897,7 +23032,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.163</v>
+        <v>0.1639</v>
       </c>
       <c r="I3" t="n">
         <v>-0.7</v>
@@ -22914,7 +23049,7 @@
         <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.189</v>
+        <v>0.1919</v>
       </c>
     </row>
     <row r="4">
@@ -22944,7 +23079,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -22961,7 +23096,7 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.189</v>
+        <v>0.1919</v>
       </c>
     </row>
     <row r="5">
@@ -22991,7 +23126,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="I5" t="n">
         <v>-1.3</v>
@@ -23008,7 +23143,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="6">
@@ -23038,7 +23173,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="I6" t="n">
         <v>-2.8</v>
@@ -23055,7 +23190,7 @@
         <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="7">
@@ -23085,7 +23220,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23102,7 +23237,7 @@
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.189</v>
+        <v>0.1919</v>
       </c>
     </row>
     <row r="8">
@@ -23132,7 +23267,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I8" t="n">
         <v>0.2</v>
@@ -23149,7 +23284,7 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
@@ -23179,7 +23314,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="I9" t="n">
         <v>-1.2</v>
@@ -23196,7 +23331,7 @@
         <v>11.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
     </row>
   </sheetData>
@@ -25375,7 +25510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25721,7 +25856,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.45 (Gemini), 3.05 (EXAONE) (IV-C)</t>
+          <t>-(논문 미인용; IV-C 는 구성개념 사후층화 평균을 쓴다)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -25771,7 +25906,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.45 (Gemini), 3.05 (EXAONE) (IV-C)</t>
+          <t>-(논문 미인용; IV-C 는 구성개념 사후층화 평균을 쓴다)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25783,11 +25918,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 만 10세 이상)</t>
+          <t>Gemini 구성개념 8개 사후층화 평균(5점)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.84</v>
+        <v>2.535</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -25796,23 +25931,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.54 (Gemini), 3.03 (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>analysis_ready.csv 2024 만 10세 이상, 구성개념별 WT 가중평균의 단순평균</t>
+          <t>구성개념 시트의 모델 열 8개 값의 평균과 동일</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 전체 표본)</t>
+          <t>EXAONE 구성개념 8개 사후층화 평균(5점)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.828</v>
+        <v>3.034</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -25821,73 +25956,73 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.83 (IV-C)</t>
+          <t>2.54 (Gemini), 3.03 (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>analysis_ready.csv 2024 전체(n=8,693), 구성개념 시트의 실측_가중 8개 값의 평균</t>
+          <t>구성개념 시트의 모델 열 8개 값의 평균과 동일</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gemini 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 만 10세 이상)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.533</v>
+        <v>2.84</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>점</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.533 (Gemini), 0.582 (EXAONE) (IV-C; 진단_응답스타일 의 이진_예선택률과 동일 산식; v1.10 이전의 0.549/0.602는 산식 미기록으로 재현되지 않아 v1.11에서 정정)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>응답 65,344건</t>
+          <t>analysis_ready.csv 2024 만 10세 이상, 구성개념별 WT 가중평균의 단순평균</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gemini 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+          <t>실측 2024 5점 기준값(8개 구성개념 가중평균의 평균, 전체 표본)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.508</v>
+        <v>2.828</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>점</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.83 (IV-C)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>응답 68,824건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+          <t>analysis_ready.csv 2024 전체(n=8,693), 구성개념 시트의 실측_가중 8개 값의 평균</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gemini 이진 '예' 선택률(2택 문항 9개, 문항별 비율의 평균)</t>
+          <t>실측 2024 이진 '예' 선택률(8지표 가중 이용률의 평균, 전체 표본)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.478</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -25896,23 +26031,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>55.9% (IV-C)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>p__d31002=0.426; p__d31007=0.042; p__d26001=0.660; p__d26075=0.967; p__d26092=0.285; p__d11001=0.512; p__d22001=0.974; p__d28001=0.023; p__d29001=0.416</t>
+          <t>RQ1_전체일치도 의 실측_가중 8개 값의 평균</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAONE 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+          <t>Gemini 이진 '예' 선택률(8지표 사후층화 이용률의 평균)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.582</v>
+        <v>0.516</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -25921,23 +26056,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.533 (Gemini), 0.582 (EXAONE) (IV-C; 진단_응답스타일 의 이진_예선택률과 동일 산식; v1.10 이전의 0.549/0.602는 산식 미기록으로 재현되지 않아 v1.11에서 정정)</t>
+          <t>51.6% (Gemini), 57.5% (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>응답 65,320건</t>
+          <t>RQ1_전체일치도 의 모델 열 8개 값의 평균과 동일; 진단_응답스타일 의 이진_예선택률_사후층화</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXAONE 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+          <t>EXAONE 이진 '예' 선택률(8지표 사후층화 이용률의 평균)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -25946,35 +26081,160 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>51.6% (Gemini), 57.5% (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>응답 68,478건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+          <t>RQ1_전체일치도 의 모델 열 8개 값의 평균과 동일; 진단_응답스타일 의 이진_예선택률_사후층화</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Gemini 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-(논문 미인용; 참고용 비가중 산식. 진단_응답스타일 의 이진_예선택률_비가중)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>응답 65,344건</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gemini 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>응답 68,824건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gemini 이진 '예' 선택률(2택 문항 9개, 문항별 비율의 평균)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>p__d31002=0.426; p__d31007=0.042; p__d26001=0.660; p__d26075=0.967; p__d26092=0.285; p__d11001=0.512; p__d22001=0.974; p__d28001=0.023; p__d29001=0.416</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EXAONE 이진 '예' 선택률(8지표 원문항, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-(논문 미인용; 참고용 비가중 산식. 진단_응답스타일 의 이진_예선택률_비가중)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>응답 65,320건</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXAONE 이진 '예' 선택률(2024 문항셋의 2택 문항 9개 전체, 응답 합산)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>응답 68,478건; 문항: p__d31002, p__d31007, p__d26001, p__d26075, p__d26092, p__d11001, p__d22001, p__d28001, p__d29001</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>EXAONE 이진 '예' 선택률(2택 문항 9개, 문항별 비율의 평균)</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B29" t="n">
         <v>0.545</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>비율</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>p__d31002=0.387; p__d31007=0.253; p__d26001=0.840; p__d26075=0.869; p__d26092=0.522; p__d11001=0.753; p__d22001=0.703; p__d28001=0.139; p__d29001=0.443</t>
         </is>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -15411,7 +15411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15477,75 +15477,120 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>syn_eb%p</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>real_dir%p</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>real_dir_regfb%p</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>real_reg%p</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>real_eb%p</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>real_gm%p</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EB평균수축가중λ</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>Δ(syn_lin−최우수실측)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Δ(syn_lin)_CI</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>syn_lin&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Δ(syn_quad−최우수실측)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Δ(syn_quad)_CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>syn_quad&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Δ(syn_nested−최우수실측)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Δ(syn_nested)_CI</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>syn_nested&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Δ(중첩−실측EB)</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Δ(중첩−실측EB)_CI</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>중첩−실측EB&lt;0%</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Δ(합성EB−실측EB)</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Δ(합성EB−실측EB)_CI</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>합성EB−실측EB&lt;0%</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>nested선택: quad%</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>nested선택: lin%</t>
         </is>
@@ -15593,54 +15638,85 @@
         <v>9.6</v>
       </c>
       <c r="M2" t="n">
-        <v>13.39</v>
+        <v>10.55</v>
       </c>
       <c r="N2" t="n">
         <v>13.39</v>
       </c>
       <c r="O2" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="P2" t="n">
         <v>10.05</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="R2" t="n">
         <v>12.73</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="T2" t="n">
         <v>0.38</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>[-1.88, 2.41]</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>35.5</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>-1.36</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[-3.49, 1.14]</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>89</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>-0.45</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>[-3.16, 1.96]</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>66</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[-3.84, 1.42]</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>[-1.35, 0.85]</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI2" t="n">
         <v>40.9</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AJ2" t="n">
         <v>24.7</v>
       </c>
     </row>
@@ -15686,54 +15762,85 @@
         <v>8.51</v>
       </c>
       <c r="M3" t="n">
-        <v>13.39</v>
+        <v>10.16</v>
       </c>
       <c r="N3" t="n">
         <v>13.39</v>
       </c>
       <c r="O3" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="P3" t="n">
         <v>10.05</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="R3" t="n">
         <v>12.73</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="T3" t="n">
         <v>-1.41</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>[-3.70, 0.25]</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>92.5</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-1.93</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[-4.23, 0.33]</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>96</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>-1.54</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[-4.13, 0.49]</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>90.5</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[-4.49, 0.11]</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>[-1.54, 0.25]</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>37.4</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AJ3" t="n">
         <v>26.6</v>
       </c>
     </row>
@@ -15779,54 +15886,85 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>10.51</v>
+        <v>8.01</v>
       </c>
       <c r="N4" t="n">
         <v>10.51</v>
       </c>
       <c r="O4" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="P4" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="R4" t="n">
         <v>12.18</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.06</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>[-0.47, 2.26]</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>9.5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[-2.91, 0.36]</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>93.5</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>[-2.51, 1.11]</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>78.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[-1.98, 1.68]</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>[-1.30, 0.86]</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>52.6</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AJ4" t="n">
         <v>18.5</v>
       </c>
     </row>
@@ -15872,54 +16010,85 @@
         <v>7.34</v>
       </c>
       <c r="M5" t="n">
-        <v>10.51</v>
+        <v>7.6</v>
       </c>
       <c r="N5" t="n">
         <v>10.51</v>
       </c>
       <c r="O5" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="P5" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="R5" t="n">
         <v>12.18</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="T5" t="n">
         <v>-0.84</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>[-2.30, 0.42]</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>90</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-1.88</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>[-3.69, -0.29]</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
         <v>99</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>-1.36</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>[-3.01, 0.16]</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>96</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[-2.25, 0.89]</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>[-1.50, 0.13]</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AI5" t="n">
         <v>41.8</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AJ5" t="n">
         <v>25.9</v>
       </c>
     </row>
@@ -15965,54 +16134,85 @@
         <v>7.09</v>
       </c>
       <c r="M6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="N6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="O6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P6" t="n">
         <v>8.16</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R6" t="n">
         <v>11.98</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.27</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>[0.00, 2.29]</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>2.5</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-1.36</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>[-2.58, 0.27]</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>96</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>-0.99</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>[-2.25, 0.61]</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>87</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>[-1.23, 1.72]</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>[-0.97, 0.85]</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AI6" t="n">
         <v>57.6</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AJ6" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -16058,54 +16258,85 @@
         <v>6.49</v>
       </c>
       <c r="M7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="N7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="O7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P7" t="n">
         <v>8.16</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R7" t="n">
         <v>11.98</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="T7" t="n">
         <v>-0.64</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>[-1.60, 0.28]</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>90</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-2.06</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>[-3.35, -0.70]</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>100</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>-1.59</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>[-2.79, -0.29]</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>99</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>[-1.82, 0.97]</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>[-1.13, 0.14]</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>94</v>
+      </c>
+      <c r="AI7" t="n">
         <v>48.6</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AJ7" t="n">
         <v>22.4</v>
       </c>
     </row>
@@ -16151,54 +16382,85 @@
         <v>6.37</v>
       </c>
       <c r="M8" t="n">
-        <v>7.28</v>
+        <v>5.82</v>
       </c>
       <c r="N8" t="n">
         <v>7.28</v>
       </c>
       <c r="O8" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P8" t="n">
         <v>7.73</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="R8" t="n">
         <v>11.88</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.88</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>[0.77, 3.08]</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-0.99</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>[-2.08, 0.15]</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>96.5</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>[-1.84, 0.40]</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>90.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[-0.67, 1.50]</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>[-0.87, 0.58]</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>62</v>
+      </c>
+      <c r="AI8" t="n">
         <v>63.8</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AJ8" t="n">
         <v>18.8</v>
       </c>
     </row>
@@ -16244,54 +16506,85 @@
         <v>5.84</v>
       </c>
       <c r="M9" t="n">
-        <v>7.28</v>
+        <v>5.6</v>
       </c>
       <c r="N9" t="n">
         <v>7.28</v>
       </c>
       <c r="O9" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P9" t="n">
         <v>7.73</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="R9" t="n">
         <v>11.88</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="T9" t="n">
         <v>-0.04</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>[-1.05, 1.10]</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>51</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>-1.71</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>[-2.80, -0.53]</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>100</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>-1.34</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>[-2.52, -0.14]</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>98</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[-1.22, 1.08]</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>[-0.97, 0.18]</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>86</v>
+      </c>
+      <c r="AI9" t="n">
         <v>55.5</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AJ9" t="n">
         <v>20.7</v>
       </c>
     </row>
@@ -16337,54 +16630,85 @@
         <v>5.74</v>
       </c>
       <c r="M10" t="n">
-        <v>5.48</v>
+        <v>4.67</v>
       </c>
       <c r="N10" t="n">
         <v>5.48</v>
       </c>
       <c r="O10" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P10" t="n">
         <v>7.34</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R10" t="n">
         <v>11.78</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.32</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>[2.45, 4.22]</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>0.18</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>[-0.69, 1.03]</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>32.5</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>0.26</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>[-0.52, 1.07]</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>26</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[0.08, 1.83]</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>[-0.76, 0.40]</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI10" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AJ10" t="n">
         <v>16.4</v>
       </c>
     </row>
@@ -16430,54 +16754,85 @@
         <v>5.11</v>
       </c>
       <c r="M11" t="n">
-        <v>5.48</v>
+        <v>4.64</v>
       </c>
       <c r="N11" t="n">
         <v>5.48</v>
       </c>
       <c r="O11" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P11" t="n">
         <v>7.34</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R11" t="n">
         <v>11.78</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.39</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>[0.61, 2.17]</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>[-1.39, 0.33]</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>90.5</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>-0.37</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>[-1.19, 0.46]</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>79</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[-0.43, 1.36]</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>[-0.60, 0.23]</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>81</v>
+      </c>
+      <c r="AI11" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AJ11" t="n">
         <v>19.4</v>
       </c>
     </row>
@@ -16523,54 +16878,85 @@
         <v>5.34</v>
       </c>
       <c r="M12" t="n">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
         <v>4.18</v>
       </c>
       <c r="O12" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P12" t="n">
         <v>7.14</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R12" t="n">
         <v>11.75</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="T12" t="n">
         <v>4.46</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>[3.72, 5.24]</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>[0.48, 1.78]</t>
         </is>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>[0.42, 1.77]</t>
+          <t>[0.48, 1.78]</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>[0.42, 1.77]</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[0.74, 2.13]</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>[-0.74, 0.28]</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI12" t="n">
         <v>76.7</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AJ12" t="n">
         <v>13.8</v>
       </c>
     </row>
@@ -16616,54 +17002,85 @@
         <v>4.63</v>
       </c>
       <c r="M13" t="n">
-        <v>4.18</v>
+        <v>3.83</v>
       </c>
       <c r="N13" t="n">
         <v>4.18</v>
       </c>
       <c r="O13" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P13" t="n">
         <v>7.14</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R13" t="n">
         <v>11.75</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.54</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>[1.79, 3.17]</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>0.38</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>[-0.34, 1.00]</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>13</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>0.46</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>[-0.17, 1.17]</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>8.5</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[0.09, 1.40]</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>[-0.36, 0.20]</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI13" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AJ13" t="n">
         <v>15.7</v>
       </c>
     </row>
@@ -16709,54 +17126,85 @@
         <v>5.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
         <v>3.63</v>
       </c>
       <c r="O14" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P14" t="n">
         <v>7.1</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R14" t="n">
         <v>11.75</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="T14" t="n">
         <v>4.97</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>[4.28, 5.67]</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>[0.96, 2.14]</t>
         </is>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>[0.97, 2.15]</t>
+          <t>[0.96, 2.14]</t>
         </is>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>[0.97, 2.15]</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[1.10, 2.27]</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>[-0.56, 0.22]</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI14" t="n">
         <v>77.3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AJ14" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -16802,54 +17250,85 @@
         <v>4.47</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
         <v>3.63</v>
       </c>
       <c r="O15" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P15" t="n">
         <v>7.1</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R15" t="n">
         <v>11.75</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.06</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>[2.33, 3.66]</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>0.8</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>[0.20, 1.30]</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>0.5</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>0.84</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>[0.29, 1.43]</t>
         </is>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[0.44, 1.49]</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>[-0.27, 0.20]</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI15" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AJ15" t="n">
         <v>14.6</v>
       </c>
     </row>
@@ -16895,54 +17374,85 @@
         <v>9.98</v>
       </c>
       <c r="M16" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="N16" t="n">
         <v>13.21</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>13.24</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>10.08</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="R16" t="n">
         <v>12.99</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="T16" t="n">
         <v>0.8</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>[-2.14, 3.50]</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>25.5</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>-0.93</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>[-3.80, 2.04]</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>74.5</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>-0.09</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>[-3.52, 3.46]</t>
         </is>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>51</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[-4.28, 1.86]</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>[-0.99, 1.51]</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI16" t="n">
         <v>44.1</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AJ16" t="n">
         <v>23</v>
       </c>
     </row>
@@ -16988,54 +17498,85 @@
         <v>8.98</v>
       </c>
       <c r="M17" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="N17" t="n">
         <v>13.21</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>13.24</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>10.08</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="R17" t="n">
         <v>12.99</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="T17" t="n">
         <v>-0.93</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>[-3.45, 1.59]</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>80.5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>-1.51</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>[-4.34, 1.68]</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>84.5</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>-1.09</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>[-4.42, 2.11]</t>
         </is>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>77.5</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[-4.76, 0.55]</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>[-1.48, 0.89]</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI17" t="n">
         <v>39.9</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AJ17" t="n">
         <v>25.8</v>
       </c>
     </row>
@@ -17081,54 +17622,85 @@
         <v>8.289999999999999</v>
       </c>
       <c r="M18" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="N18" t="n">
         <v>10.45</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>10.46</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="R18" t="n">
         <v>12.36</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.11</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>[-0.62, 2.74]</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>9</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>-1.15</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>[-2.89, 0.86]</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>89.5</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>-0.53</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>[-2.57, 1.70]</t>
         </is>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>69.5</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[-2.07, 2.29]</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>[-1.02, 1.02]</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AI18" t="n">
         <v>50.4</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AJ18" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -17174,54 +17746,85 @@
         <v>7.49</v>
       </c>
       <c r="M19" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="N19" t="n">
         <v>10.45</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>10.46</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="R19" t="n">
         <v>12.36</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T19" t="n">
         <v>-0.71</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>[-2.30, 1.04]</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>81.5</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>-1.77</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>[-3.55, 0.30]</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>95.5</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>-1.33</v>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>[-3.12, 0.66]</t>
         </is>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>91.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[-2.74, 0.92]</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>81</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>[-1.22, 0.39]</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AI19" t="n">
         <v>44.1</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AJ19" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -17267,54 +17870,85 @@
         <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>9.01</v>
+        <v>7.2</v>
       </c>
       <c r="N20" t="n">
         <v>9.01</v>
       </c>
       <c r="O20" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="P20" t="n">
         <v>8.31</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R20" t="n">
         <v>12.13</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.37</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>[0.11, 2.58]</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>1.5</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>-1.14</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>[-2.46, 0.58]</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>93.5</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>-0.8</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>[-2.17, 0.94]</t>
         </is>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>83</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[-1.20, 1.88]</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>43</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>[-0.78, 0.86]</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI20" t="n">
         <v>56.6</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AJ20" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -17360,54 +17994,85 @@
         <v>6.87</v>
       </c>
       <c r="M21" t="n">
-        <v>9.01</v>
+        <v>6.86</v>
       </c>
       <c r="N21" t="n">
         <v>9.01</v>
       </c>
       <c r="O21" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="P21" t="n">
         <v>8.31</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R21" t="n">
         <v>12.13</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="T21" t="n">
         <v>-0.49</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>[-1.57, 0.80]</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>82.5</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>-1.79</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>[-2.99, -0.10]</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>98</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>-1.33</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>[-2.62, 0.23]</t>
         </is>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>97</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[-1.78, 1.08]</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>[-0.95, 0.29]</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI21" t="n">
         <v>47.4</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AJ21" t="n">
         <v>22.8</v>
       </c>
     </row>
@@ -17453,54 +18118,85 @@
         <v>6.56</v>
       </c>
       <c r="M22" t="n">
-        <v>7.36</v>
+        <v>6.01</v>
       </c>
       <c r="N22" t="n">
         <v>7.36</v>
       </c>
       <c r="O22" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="P22" t="n">
         <v>7.78</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="R22" t="n">
         <v>11.96</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.99</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>[0.93, 3.13]</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>-0.83</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>[-1.91, 0.27]</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>94</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>-0.66</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>[-1.66, 0.50]</t>
         </is>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>87</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[-0.50, 1.60]</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>[-0.71, 0.73]</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AI22" t="n">
         <v>61.9</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AJ22" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -17546,54 +18242,85 @@
         <v>6.04</v>
       </c>
       <c r="M23" t="n">
-        <v>7.36</v>
+        <v>5.78</v>
       </c>
       <c r="N23" t="n">
         <v>7.36</v>
       </c>
       <c r="O23" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="P23" t="n">
         <v>7.78</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="R23" t="n">
         <v>11.96</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="T23" t="n">
         <v>0.08</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>[-0.93, 1.23]</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>47.5</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>-1.55</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>[-2.49, -0.59]</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>99.5</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>-1.18</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>[-2.25, -0.10]</t>
         </is>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>98</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[-0.93, 1.14]</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>[-0.82, 0.33]</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>54.2</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AJ23" t="n">
         <v>21</v>
       </c>
     </row>
@@ -17639,54 +18366,85 @@
         <v>5.77</v>
       </c>
       <c r="M24" t="n">
-        <v>5.47</v>
+        <v>4.74</v>
       </c>
       <c r="N24" t="n">
         <v>5.47</v>
       </c>
       <c r="O24" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="P24" t="n">
         <v>7.38</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="R24" t="n">
         <v>11.82</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.36</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>[2.43, 4.21]</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>0</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>0.23</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>[-0.72, 1.01]</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>29.5</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>0.3</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>[-0.57, 1.07]</t>
         </is>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>23.5</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[0.08, 1.76]</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>[-0.69, 0.40]</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI24" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AJ24" t="n">
         <v>19.2</v>
       </c>
     </row>
@@ -17732,54 +18490,85 @@
         <v>5.15</v>
       </c>
       <c r="M25" t="n">
-        <v>5.47</v>
+        <v>4.72</v>
       </c>
       <c r="N25" t="n">
         <v>5.47</v>
       </c>
       <c r="O25" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="P25" t="n">
         <v>7.38</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="R25" t="n">
         <v>11.82</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.45</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>[0.57, 2.30]</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>-0.52</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>[-1.48, 0.23]</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>88.5</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>-0.32</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>[-1.25, 0.78]</t>
         </is>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>74</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[-0.51, 1.19]</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>[-0.65, 0.22]</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI25" t="n">
         <v>65.3</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AJ25" t="n">
         <v>19</v>
       </c>
     </row>
@@ -17825,54 +18614,85 @@
         <v>5.38</v>
       </c>
       <c r="M26" t="n">
-        <v>4.18</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
         <v>4.18</v>
       </c>
       <c r="O26" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P26" t="n">
         <v>7.2</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R26" t="n">
         <v>11.77</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="T26" t="n">
         <v>4.5</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>[3.77, 5.15]</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>[0.54, 1.86]</t>
         </is>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>[0.54, 1.86]</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.2</v>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>[0.57, 1.86]</t>
         </is>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[0.73, 2.14]</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>[-0.71, 0.30]</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AI26" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AJ26" t="n">
         <v>16.1</v>
       </c>
     </row>
@@ -17918,54 +18738,85 @@
         <v>4.68</v>
       </c>
       <c r="M27" t="n">
-        <v>4.18</v>
+        <v>3.89</v>
       </c>
       <c r="N27" t="n">
         <v>4.18</v>
       </c>
       <c r="O27" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="P27" t="n">
         <v>7.2</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R27" t="n">
         <v>11.77</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.6</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>[1.87, 3.29]</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>0.44</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>[-0.26, 1.15]</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>10.5</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>0.5</v>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>[-0.18, 1.13]</t>
         </is>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>8</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[0.04, 1.30]</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>[-0.43, 0.23]</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AI27" t="n">
         <v>72.5</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AJ27" t="n">
         <v>16.6</v>
       </c>
     </row>
@@ -18011,34 +18862,32 @@
         <v>5.27</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
         <v>3.68</v>
       </c>
       <c r="O28" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P28" t="n">
         <v>7.14</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R28" t="n">
         <v>11.76</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="T28" t="n">
         <v>4.98</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>[4.36, 5.60]</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>[0.93, 2.12]</t>
         </is>
       </c>
       <c r="V28" t="n">
@@ -18049,16 +18898,49 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>[1.04, 2.08]</t>
+          <t>[0.93, 2.12]</t>
         </is>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>[1.04, 2.08]</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[0.96, 2.37]</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>[-0.60, 0.31]</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>76</v>
+      </c>
+      <c r="AI28" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AJ28" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -18104,54 +18986,85 @@
         <v>4.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
         <v>3.68</v>
       </c>
       <c r="O29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P29" t="n">
         <v>7.14</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R29" t="n">
         <v>11.76</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.08</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>[2.45, 3.77]</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>[0.28, 1.45]</t>
         </is>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>[0.26, 1.44]</t>
+          <t>[0.28, 1.45]</t>
         </is>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>[0.26, 1.44]</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[0.46, 1.50]</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>[-0.32, 0.23]</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>75.7</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AJ29" t="n">
         <v>15.8</v>
       </c>
     </row>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -13159,13 +13159,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="D4" t="n">
-        <v>8.77</v>
+        <v>8.58</v>
       </c>
       <c r="E4" t="n">
-        <v>9.69</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="5">
@@ -13243,13 +13243,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="D8" t="n">
         <v>2.72</v>
       </c>
       <c r="E8" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="9">
@@ -13287,6 +13287,8 @@
       <c r="C10" t="n">
         <v>0.1</v>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13302,6 +13304,8 @@
       <c r="C11" t="n">
         <v>12.7</v>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13317,6 +13321,8 @@
       <c r="C12" t="n">
         <v>77.40000000000001</v>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13332,6 +13338,8 @@
       <c r="C13" t="n">
         <v>2.4</v>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13347,6 +13355,8 @@
       <c r="C14" t="n">
         <v>7.4</v>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13402,13 +13412,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.05</v>
+        <v>6.99</v>
       </c>
       <c r="D17" t="n">
-        <v>6.68</v>
+        <v>6.63</v>
       </c>
       <c r="E17" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="18">
@@ -13486,13 +13496,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="D21" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="E21" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -13530,6 +13540,8 @@
       <c r="C23" t="n">
         <v>0.6</v>
       </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13545,6 +13557,8 @@
       <c r="C24" t="n">
         <v>15.1</v>
       </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13560,6 +13574,8 @@
       <c r="C25" t="n">
         <v>74.90000000000001</v>
       </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13575,6 +13591,8 @@
       <c r="C26" t="n">
         <v>1.6</v>
       </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13590,6 +13608,8 @@
       <c r="C27" t="n">
         <v>7.8</v>
       </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15650,13 +15670,13 @@
         <v>10.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="R2" t="n">
         <v>12.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0.661</v>
+        <v>0.654</v>
       </c>
       <c r="T2" t="n">
         <v>0.38</v>
@@ -15692,26 +15712,26 @@
         <v>66</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.14</v>
+        <v>-1.1</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>[-3.84, 1.42]</t>
+          <t>[-3.79, 1.61]</t>
         </is>
       </c>
       <c r="AE2" t="n">
         <v>79</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[-1.35, 0.85]</t>
+          <t>[-1.34, 0.90]</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>65</v>
+        <v>61.5</v>
       </c>
       <c r="AI2" t="n">
         <v>40.9</v>
@@ -15762,7 +15782,7 @@
         <v>8.51</v>
       </c>
       <c r="M3" t="n">
-        <v>10.16</v>
+        <v>10.11</v>
       </c>
       <c r="N3" t="n">
         <v>13.39</v>
@@ -15774,13 +15794,13 @@
         <v>10.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="R3" t="n">
         <v>12.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0.638</v>
+        <v>0.63</v>
       </c>
       <c r="T3" t="n">
         <v>-1.41</v>
@@ -15816,26 +15836,26 @@
         <v>90.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.22</v>
+        <v>-2.19</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>[-4.49, 0.11]</t>
+          <t>[-4.47, 0.11]</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>96.5</v>
+        <v>96</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>[-1.54, 0.25]</t>
+          <t>[-1.59, 0.20]</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>90.5</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="n">
         <v>37.4</v>
@@ -15886,7 +15906,7 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>8.01</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>10.51</v>
@@ -15898,13 +15918,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="R4" t="n">
         <v>12.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="T4" t="n">
         <v>1.06</v>
@@ -15940,26 +15960,26 @@
         <v>78.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>[-1.98, 1.68]</t>
+          <t>[-1.90, 1.70]</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>54.5</v>
+        <v>52</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>[-1.30, 0.86]</t>
+          <t>[-1.21, 0.92]</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>58.5</v>
+        <v>50.5</v>
       </c>
       <c r="AI4" t="n">
         <v>52.6</v>
@@ -16010,7 +16030,7 @@
         <v>7.34</v>
       </c>
       <c r="M5" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="N5" t="n">
         <v>10.51</v>
@@ -16022,13 +16042,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.109999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="R5" t="n">
         <v>12.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0.555</v>
+        <v>0.545</v>
       </c>
       <c r="T5" t="n">
         <v>-0.84</v>
@@ -16064,22 +16084,22 @@
         <v>96</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>[-2.25, 0.89]</t>
+          <t>[-2.19, 0.91]</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>[-1.50, 0.13]</t>
+          <t>[-1.50, 0.14]</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -16134,7 +16154,7 @@
         <v>7.09</v>
       </c>
       <c r="M6" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="N6" t="n">
         <v>8.800000000000001</v>
@@ -16146,13 +16166,13 @@
         <v>8.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="R6" t="n">
         <v>11.98</v>
       </c>
       <c r="S6" t="n">
-        <v>0.578</v>
+        <v>0.569</v>
       </c>
       <c r="T6" t="n">
         <v>1.27</v>
@@ -16188,26 +16208,26 @@
         <v>87</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>[-1.23, 1.72]</t>
+          <t>[-1.19, 1.75]</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>47.5</v>
+        <v>45</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>[-0.97, 0.85]</t>
+          <t>[-0.94, 0.94]</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="AI6" t="n">
         <v>57.6</v>
@@ -16258,7 +16278,7 @@
         <v>6.49</v>
       </c>
       <c r="M7" t="n">
-        <v>6.47</v>
+        <v>6.43</v>
       </c>
       <c r="N7" t="n">
         <v>8.800000000000001</v>
@@ -16270,13 +16290,13 @@
         <v>8.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="R7" t="n">
         <v>11.98</v>
       </c>
       <c r="S7" t="n">
-        <v>0.535</v>
+        <v>0.523</v>
       </c>
       <c r="T7" t="n">
         <v>-0.64</v>
@@ -16312,26 +16332,26 @@
         <v>99</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>[-1.82, 0.97]</t>
+          <t>[-1.70, 0.90]</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>72.5</v>
+        <v>69.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>[-1.13, 0.14]</t>
+          <t>[-1.14, 0.14]</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="AI7" t="n">
         <v>48.6</v>
@@ -16382,7 +16402,7 @@
         <v>6.37</v>
       </c>
       <c r="M8" t="n">
-        <v>5.82</v>
+        <v>5.84</v>
       </c>
       <c r="N8" t="n">
         <v>7.28</v>
@@ -16394,13 +16414,13 @@
         <v>7.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="R8" t="n">
         <v>11.88</v>
       </c>
       <c r="S8" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="T8" t="n">
         <v>1.88</v>
@@ -16440,22 +16460,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>[-0.67, 1.50]</t>
+          <t>[-0.72, 1.49]</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>[-0.87, 0.58]</t>
+          <t>[-0.84, 0.61]</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AI8" t="n">
         <v>63.8</v>
@@ -16518,13 +16538,13 @@
         <v>7.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="R9" t="n">
         <v>11.88</v>
       </c>
       <c r="S9" t="n">
-        <v>0.53</v>
+        <v>0.517</v>
       </c>
       <c r="T9" t="n">
         <v>-0.04</v>
@@ -16564,7 +16584,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>[-1.22, 1.08]</t>
+          <t>[-1.15, 1.08]</t>
         </is>
       </c>
       <c r="AE9" t="n">
@@ -16575,11 +16595,11 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>[-0.97, 0.18]</t>
+          <t>[-0.97, 0.17]</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="AI9" t="n">
         <v>55.5</v>
@@ -16630,7 +16650,7 @@
         <v>5.74</v>
       </c>
       <c r="M10" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
         <v>5.48</v>
@@ -16642,13 +16662,13 @@
         <v>7.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="R10" t="n">
         <v>11.78</v>
       </c>
       <c r="S10" t="n">
-        <v>0.631</v>
+        <v>0.625</v>
       </c>
       <c r="T10" t="n">
         <v>3.32</v>
@@ -16684,26 +16704,26 @@
         <v>26</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>[0.08, 1.83]</t>
+          <t>[0.07, 1.82]</t>
         </is>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>[-0.76, 0.40]</t>
+          <t>[-0.76, 0.39]</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="AI10" t="n">
         <v>70.90000000000001</v>
@@ -16754,7 +16774,7 @@
         <v>5.11</v>
       </c>
       <c r="M11" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="N11" t="n">
         <v>5.48</v>
@@ -16766,13 +16786,13 @@
         <v>7.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="R11" t="n">
         <v>11.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.579</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>1.39</v>
@@ -16808,18 +16828,18 @@
         <v>79</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>[-0.43, 1.36]</t>
+          <t>[-0.43, 1.32]</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>27.5</v>
+        <v>29.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -16827,7 +16847,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="AI11" t="n">
         <v>64.40000000000001</v>
@@ -16878,7 +16898,7 @@
         <v>5.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
         <v>4.18</v>
@@ -16890,13 +16910,13 @@
         <v>7.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="R12" t="n">
         <v>11.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0.697</v>
+        <v>0.694</v>
       </c>
       <c r="T12" t="n">
         <v>4.46</v>
@@ -16932,11 +16952,11 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>[0.74, 2.13]</t>
+          <t>[0.72, 2.16]</t>
         </is>
       </c>
       <c r="AE12" t="n">
@@ -16947,11 +16967,11 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>[-0.74, 0.28]</t>
+          <t>[-0.75, 0.30]</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="n">
         <v>76.7</v>
@@ -17002,7 +17022,7 @@
         <v>4.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
         <v>4.18</v>
@@ -17014,13 +17034,13 @@
         <v>7.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="R13" t="n">
         <v>11.75</v>
       </c>
       <c r="S13" t="n">
-        <v>0.681</v>
+        <v>0.67</v>
       </c>
       <c r="T13" t="n">
         <v>2.54</v>
@@ -17056,11 +17076,11 @@
         <v>8.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>[0.09, 1.40]</t>
+          <t>[0.06, 1.38]</t>
         </is>
       </c>
       <c r="AE13" t="n">
@@ -17075,7 +17095,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>71</v>
+        <v>67.5</v>
       </c>
       <c r="AI13" t="n">
         <v>71.90000000000001</v>
@@ -17138,13 +17158,13 @@
         <v>7.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
         <v>11.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0.741</v>
+        <v>0.739</v>
       </c>
       <c r="T14" t="n">
         <v>4.97</v>
@@ -17180,18 +17200,18 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>[1.10, 2.27]</t>
+          <t>[1.09, 2.26]</t>
         </is>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -17250,7 +17270,7 @@
         <v>4.47</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="N15" t="n">
         <v>3.63</v>
@@ -17262,13 +17282,13 @@
         <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
         <v>11.75</v>
       </c>
       <c r="S15" t="n">
-        <v>0.75</v>
+        <v>0.742</v>
       </c>
       <c r="T15" t="n">
         <v>3.06</v>
@@ -17304,11 +17324,11 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>[0.44, 1.49]</t>
+          <t>[0.40, 1.45]</t>
         </is>
       </c>
       <c r="AE15" t="n">
@@ -17319,11 +17339,11 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>[-0.27, 0.20]</t>
+          <t>[-0.27, 0.22]</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>65</v>
+        <v>61.5</v>
       </c>
       <c r="AI15" t="n">
         <v>75.59999999999999</v>
@@ -17374,7 +17394,7 @@
         <v>9.98</v>
       </c>
       <c r="M16" t="n">
-        <v>11.14</v>
+        <v>11.15</v>
       </c>
       <c r="N16" t="n">
         <v>13.21</v>
@@ -17386,13 +17406,13 @@
         <v>10.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.09</v>
+        <v>11.04</v>
       </c>
       <c r="R16" t="n">
         <v>12.99</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="T16" t="n">
         <v>0.8</v>
@@ -17428,26 +17448,26 @@
         <v>51</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.11</v>
+        <v>-1.07</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>[-4.28, 1.86]</t>
+          <t>[-4.22, 1.86]</t>
         </is>
       </c>
       <c r="AE16" t="n">
         <v>79.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>[-0.99, 1.51]</t>
+          <t>[-0.97, 1.71]</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="n">
         <v>44.1</v>
@@ -17498,7 +17518,7 @@
         <v>8.98</v>
       </c>
       <c r="M17" t="n">
-        <v>10.72</v>
+        <v>10.67</v>
       </c>
       <c r="N17" t="n">
         <v>13.21</v>
@@ -17510,13 +17530,13 @@
         <v>10.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.09</v>
+        <v>11.04</v>
       </c>
       <c r="R17" t="n">
         <v>12.99</v>
       </c>
       <c r="S17" t="n">
-        <v>0.648</v>
+        <v>0.639</v>
       </c>
       <c r="T17" t="n">
         <v>-0.93</v>
@@ -17552,11 +17572,11 @@
         <v>77.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.11</v>
+        <v>-2.06</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>[-4.76, 0.55]</t>
+          <t>[-4.72, 0.55]</t>
         </is>
       </c>
       <c r="AE17" t="n">
@@ -17567,7 +17587,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>[-1.48, 0.89]</t>
+          <t>[-1.56, 0.89]</t>
         </is>
       </c>
       <c r="AH17" t="n">
@@ -17622,7 +17642,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>8.359999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>10.45</v>
@@ -17634,13 +17654,13 @@
         <v>8.859999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.34</v>
+        <v>8.31</v>
       </c>
       <c r="R18" t="n">
         <v>12.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -17676,26 +17696,26 @@
         <v>69.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>[-2.07, 2.29]</t>
+          <t>[-2.03, 2.30]</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>[-1.02, 1.02]</t>
+          <t>[-1.05, 1.05]</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>53.5</v>
+        <v>49.5</v>
       </c>
       <c r="AI18" t="n">
         <v>50.4</v>
@@ -17746,7 +17766,7 @@
         <v>7.49</v>
       </c>
       <c r="M19" t="n">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="N19" t="n">
         <v>10.45</v>
@@ -17758,13 +17778,13 @@
         <v>8.859999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.34</v>
+        <v>8.31</v>
       </c>
       <c r="R19" t="n">
         <v>12.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="T19" t="n">
         <v>-0.71</v>
@@ -17800,11 +17820,11 @@
         <v>91.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>[-2.74, 0.92]</t>
+          <t>[-2.65, 0.94]</t>
         </is>
       </c>
       <c r="AE19" t="n">
@@ -17815,11 +17835,11 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>[-1.22, 0.39]</t>
+          <t>[-1.21, 0.39]</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="AI19" t="n">
         <v>44.1</v>
@@ -17870,7 +17890,7 @@
         <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
       <c r="N20" t="n">
         <v>9.01</v>
@@ -17882,13 +17902,13 @@
         <v>8.31</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="R20" t="n">
         <v>12.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0.579</v>
+        <v>0.572</v>
       </c>
       <c r="T20" t="n">
         <v>1.37</v>
@@ -17924,26 +17944,26 @@
         <v>83</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>[-1.20, 1.88]</t>
+          <t>[-1.12, 1.97]</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>[-0.78, 0.86]</t>
+          <t>[-0.79, 0.95]</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>48</v>
+        <v>43.5</v>
       </c>
       <c r="AI20" t="n">
         <v>56.6</v>
@@ -17994,7 +18014,7 @@
         <v>6.87</v>
       </c>
       <c r="M21" t="n">
-        <v>6.86</v>
+        <v>6.83</v>
       </c>
       <c r="N21" t="n">
         <v>9.01</v>
@@ -18006,13 +18026,13 @@
         <v>8.31</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="R21" t="n">
         <v>12.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0.528</v>
+        <v>0.515</v>
       </c>
       <c r="T21" t="n">
         <v>-0.49</v>
@@ -18048,26 +18068,26 @@
         <v>97</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>[-1.78, 1.08]</t>
+          <t>[-1.74, 1.09]</t>
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>70.5</v>
+        <v>69</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>[-0.95, 0.29]</t>
+          <t>[-1.07, 0.29]</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>82</v>
+        <v>83.5</v>
       </c>
       <c r="AI21" t="n">
         <v>47.4</v>
@@ -18118,7 +18138,7 @@
         <v>6.56</v>
       </c>
       <c r="M22" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="N22" t="n">
         <v>7.36</v>
@@ -18130,13 +18150,13 @@
         <v>7.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="R22" t="n">
         <v>11.96</v>
       </c>
       <c r="S22" t="n">
-        <v>0.58</v>
+        <v>0.573</v>
       </c>
       <c r="T22" t="n">
         <v>1.99</v>
@@ -18172,26 +18192,26 @@
         <v>87</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>[-0.50, 1.60]</t>
+          <t>[-0.48, 1.61]</t>
         </is>
       </c>
       <c r="AE22" t="n">
         <v>17.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>[-0.71, 0.73]</t>
+          <t>[-0.71, 0.84]</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>51.5</v>
+        <v>48</v>
       </c>
       <c r="AI22" t="n">
         <v>61.9</v>
@@ -18242,7 +18262,7 @@
         <v>6.04</v>
       </c>
       <c r="M23" t="n">
-        <v>5.78</v>
+        <v>5.77</v>
       </c>
       <c r="N23" t="n">
         <v>7.36</v>
@@ -18254,13 +18274,13 @@
         <v>7.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="R23" t="n">
         <v>11.96</v>
       </c>
       <c r="S23" t="n">
-        <v>0.521</v>
+        <v>0.508</v>
       </c>
       <c r="T23" t="n">
         <v>0.08</v>
@@ -18300,7 +18320,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>[-0.93, 1.14]</t>
+          <t>[-0.93, 1.16]</t>
         </is>
       </c>
       <c r="AE23" t="n">
@@ -18311,11 +18331,11 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>[-0.82, 0.33]</t>
+          <t>[-0.85, 0.31]</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>81.5</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="n">
         <v>54.2</v>
@@ -18366,7 +18386,7 @@
         <v>5.77</v>
       </c>
       <c r="M24" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="N24" t="n">
         <v>5.47</v>
@@ -18378,13 +18398,13 @@
         <v>7.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="R24" t="n">
         <v>11.82</v>
       </c>
       <c r="S24" t="n">
-        <v>0.621</v>
+        <v>0.616</v>
       </c>
       <c r="T24" t="n">
         <v>3.36</v>
@@ -18420,26 +18440,26 @@
         <v>23.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>[0.08, 1.76]</t>
+          <t>[0.11, 1.71]</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>[-0.69, 0.40]</t>
+          <t>[-0.68, 0.42]</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>67.5</v>
+        <v>64</v>
       </c>
       <c r="AI24" t="n">
         <v>69.40000000000001</v>
@@ -18490,7 +18510,7 @@
         <v>5.15</v>
       </c>
       <c r="M25" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="N25" t="n">
         <v>5.47</v>
@@ -18502,13 +18522,13 @@
         <v>7.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="R25" t="n">
         <v>11.82</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="T25" t="n">
         <v>1.45</v>
@@ -18544,26 +18564,26 @@
         <v>74</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>[-0.51, 1.19]</t>
+          <t>[-0.55, 1.14]</t>
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>[-0.65, 0.22]</t>
+          <t>[-0.62, 0.22]</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>74</v>
+        <v>71.5</v>
       </c>
       <c r="AI25" t="n">
         <v>65.3</v>
@@ -18614,7 +18634,7 @@
         <v>5.38</v>
       </c>
       <c r="M26" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
         <v>4.18</v>
@@ -18626,13 +18646,13 @@
         <v>7.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R26" t="n">
         <v>11.77</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>4.5</v>
@@ -18668,11 +18688,11 @@
         <v>0.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>[0.73, 2.14]</t>
+          <t>[0.69, 2.13]</t>
         </is>
       </c>
       <c r="AE26" t="n">
@@ -18683,11 +18703,11 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>[-0.71, 0.30]</t>
+          <t>[-0.73, 0.30]</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="n">
         <v>75.09999999999999</v>
@@ -18738,7 +18758,7 @@
         <v>4.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="N27" t="n">
         <v>4.18</v>
@@ -18750,13 +18770,13 @@
         <v>7.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R27" t="n">
         <v>11.77</v>
       </c>
       <c r="S27" t="n">
-        <v>0.669</v>
+        <v>0.658</v>
       </c>
       <c r="T27" t="n">
         <v>2.6</v>
@@ -18792,11 +18812,11 @@
         <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>[0.04, 1.30]</t>
+          <t>[0.05, 1.35]</t>
         </is>
       </c>
       <c r="AE27" t="n">
@@ -18807,11 +18827,11 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>[-0.43, 0.23]</t>
+          <t>[-0.44, 0.23]</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="AI27" t="n">
         <v>72.5</v>
@@ -18862,7 +18882,7 @@
         <v>5.27</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="N28" t="n">
         <v>3.68</v>
@@ -18874,13 +18894,13 @@
         <v>7.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="R28" t="n">
         <v>11.76</v>
       </c>
       <c r="S28" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="T28" t="n">
         <v>4.98</v>
@@ -18916,11 +18936,11 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>[0.96, 2.37]</t>
+          <t>[0.96, 2.39]</t>
         </is>
       </c>
       <c r="AE28" t="n">
@@ -18931,7 +18951,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>[-0.60, 0.31]</t>
+          <t>[-0.62, 0.31]</t>
         </is>
       </c>
       <c r="AH28" t="n">
@@ -18986,7 +19006,7 @@
         <v>4.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="N29" t="n">
         <v>3.68</v>
@@ -18998,13 +19018,13 @@
         <v>7.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="R29" t="n">
         <v>11.76</v>
       </c>
       <c r="S29" t="n">
-        <v>0.743</v>
+        <v>0.735</v>
       </c>
       <c r="T29" t="n">
         <v>3.08</v>
@@ -19040,11 +19060,11 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>[0.46, 1.50]</t>
+          <t>[0.44, 1.49]</t>
         </is>
       </c>
       <c r="AE29" t="n">
@@ -19055,11 +19075,11 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>[-0.32, 0.23]</t>
+          <t>[-0.31, 0.24]</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>65.5</v>
+        <v>66</v>
       </c>
       <c r="AI29" t="n">
         <v>75.7</v>
@@ -23450,10 +23470,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.47</v>
+        <v>10.48</v>
       </c>
       <c r="D2" t="n">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="E2" t="n">
         <v>10.42</v>
@@ -23462,7 +23482,7 @@
         <v>13.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.666</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="3">
@@ -23475,10 +23495,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="E3" t="n">
         <v>8.6</v>
@@ -23487,7 +23507,7 @@
         <v>13.33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.634</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="4">
@@ -23500,10 +23520,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.01</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>8.02</v>
+        <v>7.98</v>
       </c>
       <c r="E4" t="n">
         <v>9.710000000000001</v>
@@ -23512,7 +23532,7 @@
         <v>10.51</v>
       </c>
       <c r="G4" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="5">
@@ -23525,10 +23545,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.53</v>
+        <v>7.48</v>
       </c>
       <c r="D5" t="n">
-        <v>8.02</v>
+        <v>7.98</v>
       </c>
       <c r="E5" t="n">
         <v>7.83</v>
@@ -23537,7 +23557,7 @@
         <v>10.51</v>
       </c>
       <c r="G5" t="n">
-        <v>0.546</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="6">
@@ -23550,10 +23570,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.85</v>
+        <v>6.87</v>
       </c>
       <c r="D6" t="n">
-        <v>6.86</v>
+        <v>6.84</v>
       </c>
       <c r="E6" t="n">
         <v>9.43</v>
@@ -23562,7 +23582,7 @@
         <v>8.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -23575,10 +23595,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.48</v>
+        <v>6.45</v>
       </c>
       <c r="D7" t="n">
-        <v>6.86</v>
+        <v>6.84</v>
       </c>
       <c r="E7" t="n">
         <v>7.49</v>
@@ -23587,7 +23607,7 @@
         <v>8.84</v>
       </c>
       <c r="G7" t="n">
-        <v>0.504</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">
@@ -23600,7 +23620,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.85</v>
+        <v>5.89</v>
       </c>
       <c r="D8" t="n">
         <v>5.87</v>
@@ -23612,7 +23632,7 @@
         <v>7.26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.579</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="9">
@@ -23637,7 +23657,7 @@
         <v>7.26</v>
       </c>
       <c r="G9" t="n">
-        <v>0.506</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="10">
@@ -23650,7 +23670,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="D10" t="n">
         <v>4.79</v>
@@ -23662,7 +23682,7 @@
         <v>5.42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.621</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="11">
@@ -23675,7 +23695,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="D11" t="n">
         <v>4.79</v>
@@ -23687,7 +23707,7 @@
         <v>5.42</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="12">
@@ -23700,10 +23720,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="E12" t="n">
         <v>8.630000000000001</v>
@@ -23712,7 +23732,7 @@
         <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -23725,10 +23745,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="E13" t="n">
         <v>6.72</v>
@@ -23737,7 +23757,7 @@
         <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.668</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="14">
@@ -23750,10 +23770,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="D14" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="E14" t="n">
         <v>8.6</v>
@@ -23762,7 +23782,7 @@
         <v>3.59</v>
       </c>
       <c r="G14" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="15">
@@ -23775,10 +23795,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="D15" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="E15" t="n">
         <v>6.7</v>
@@ -23787,7 +23807,7 @@
         <v>3.59</v>
       </c>
       <c r="G15" t="n">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -8885,7 +8885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9129,6 +9129,54 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>live calls; 1차 실패 개별 기록 없음(logs/run_exaone*.log, recover_exaone.log)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EXAONE 2024 temperature 0.7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8168</v>
+      </c>
+      <c r="H8" t="n">
+        <v>73</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>live calls; outputs/synthetic_exaone_t07.csv 의 _error 행</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXAONE 2024 demographic-only ablation</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8168</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>live calls; outputs/synthetic_demo_exaone.csv 의 _error 행</t>
         </is>
       </c>
     </row>
@@ -13287,8 +13335,6 @@
       <c r="C10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13304,8 +13350,6 @@
       <c r="C11" t="n">
         <v>12.7</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13321,8 +13365,6 @@
       <c r="C12" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13338,8 +13380,6 @@
       <c r="C13" t="n">
         <v>2.4</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13355,8 +13395,6 @@
       <c r="C14" t="n">
         <v>7.4</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13540,8 +13578,6 @@
       <c r="C23" t="n">
         <v>0.6</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13557,8 +13593,6 @@
       <c r="C24" t="n">
         <v>15.1</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13574,8 +13608,6 @@
       <c r="C25" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13591,8 +13623,6 @@
       <c r="C26" t="n">
         <v>1.6</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13608,8 +13638,6 @@
       <c r="C27" t="n">
         <v>7.8</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -9176,7 +9176,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>live calls; outputs/synthetic_demo_exaone.csv 의 _error 행</t>
+          <t>live calls; outputs/synth_demo_exaone.csv 의 _error 행</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AK29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15555,90 +15555,95 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>EB평균수축가중λ</t>
+          <t>EB평균수축가중λ(합성표적)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>EB평균수축가중λ(실측표적)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>Δ(syn_lin−최우수실측)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Δ(syn_lin)_CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>syn_lin&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Δ(syn_quad−최우수실측)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Δ(syn_quad)_CI</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>syn_quad&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Δ(syn_nested−최우수실측)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Δ(syn_nested)_CI</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>syn_nested&lt;최우수실측%</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Δ(중첩−실측EB)</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Δ(중첩−실측EB)_CI</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>중첩−실측EB&lt;0%</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Δ(합성EB−실측EB)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Δ(합성EB−실측EB)_CI</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>합성EB−실측EB&lt;0%</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>nested선택: quad%</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>nested선택: lin%</t>
         </is>
@@ -15707,64 +15712,67 @@
         <v>0.654</v>
       </c>
       <c r="T2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="U2" t="n">
         <v>0.38</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>[-1.88, 2.41]</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>35.5</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-1.36</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[-3.49, 1.14]</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>89</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>[-3.16, 1.96]</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>66</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[-3.79, 1.61]</t>
         </is>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>79</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>[-1.34, 0.90]</t>
         </is>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>61.5</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>40.9</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>24.7</v>
       </c>
     </row>
@@ -15831,64 +15839,67 @@
         <v>0.63</v>
       </c>
       <c r="T3" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="U3" t="n">
         <v>-1.41</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>[-3.70, 0.25]</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>92.5</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-1.93</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[-4.23, 0.33]</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>96</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>-1.54</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[-4.13, 0.49]</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>90.5</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>-2.19</v>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[-4.47, 0.11]</t>
         </is>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>96</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>[-1.59, 0.20]</t>
         </is>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>91</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>37.4</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>26.6</v>
       </c>
     </row>
@@ -15955,64 +15966,67 @@
         <v>0.583</v>
       </c>
       <c r="T4" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.06</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>[-0.47, 2.26]</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>9.5</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[-2.91, 0.36]</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>93.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>[-2.51, 1.11]</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>78.5</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>[-1.90, 1.70]</t>
         </is>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>52</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>[-1.21, 0.92]</t>
         </is>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>50.5</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>52.6</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>18.5</v>
       </c>
     </row>
@@ -16079,64 +16093,67 @@
         <v>0.545</v>
       </c>
       <c r="T5" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="U5" t="n">
         <v>-0.84</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>[-2.30, 0.42]</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>90</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-1.88</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>[-3.69, -0.29]</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>99</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-1.36</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>[-3.01, 0.16]</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>96</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>[-2.19, 0.91]</t>
         </is>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>78</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>-0.53</v>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>[-1.50, 0.14]</t>
         </is>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>93</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>41.8</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>25.9</v>
       </c>
     </row>
@@ -16203,64 +16220,67 @@
         <v>0.569</v>
       </c>
       <c r="T6" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.27</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>[0.00, 2.29]</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>2.5</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-1.36</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>[-2.58, 0.27]</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>96</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.99</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>[-2.25, 0.61]</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>87</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>0.21</v>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>[-1.19, 1.75]</t>
         </is>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>45</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>[-0.94, 0.94]</t>
         </is>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>50</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>57.6</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -16327,64 +16347,67 @@
         <v>0.523</v>
       </c>
       <c r="T7" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="U7" t="n">
         <v>-0.64</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>[-1.60, 0.28]</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>90</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>-2.06</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>[-3.35, -0.70]</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>100</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-1.59</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>[-2.79, -0.29]</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>99</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-0.39</v>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>[-1.70, 0.90]</t>
         </is>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>69.5</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>[-1.14, 0.14]</t>
         </is>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>94.5</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>48.6</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>22.4</v>
       </c>
     </row>
@@ -16451,64 +16474,67 @@
         <v>0.589</v>
       </c>
       <c r="T8" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.88</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>[0.77, 3.08]</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.99</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>[-2.08, 0.15]</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>96.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>[-1.84, 0.40]</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>90.5</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>0.46</v>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>[-0.72, 1.49]</t>
         </is>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[-0.84, 0.61]</t>
         </is>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>58</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>63.8</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>18.8</v>
       </c>
     </row>
@@ -16575,64 +16601,67 @@
         <v>0.517</v>
       </c>
       <c r="T9" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="U9" t="n">
         <v>-0.04</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>[-1.05, 1.10]</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>51</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>-1.71</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>[-2.80, -0.53]</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>100</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-1.34</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>[-2.52, -0.14]</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>98</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>[-1.15, 1.08]</t>
         </is>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>55</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>[-0.97, 0.17]</t>
         </is>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>86.5</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>55.5</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>20.7</v>
       </c>
     </row>
@@ -16699,64 +16728,67 @@
         <v>0.625</v>
       </c>
       <c r="T10" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.32</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>[2.45, 4.22]</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.18</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>[-0.69, 1.03]</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>32.5</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.26</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>[-0.52, 1.07]</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>26</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>[0.07, 1.82]</t>
         </is>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>1</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>[-0.76, 0.39]</t>
         </is>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>63.5</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>16.4</v>
       </c>
     </row>
@@ -16823,64 +16855,67 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="T11" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.39</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>[0.61, 2.17]</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>[-1.39, 0.33]</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>90.5</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-0.37</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>[-1.19, 0.46]</t>
         </is>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>79</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>0.27</v>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>[-0.43, 1.32]</t>
         </is>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>29.5</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>[-0.60, 0.23]</t>
         </is>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>81.5</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>19.4</v>
       </c>
     </row>
@@ -16947,64 +16982,67 @@
         <v>0.694</v>
       </c>
       <c r="T12" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="U12" t="n">
         <v>4.46</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>[3.72, 5.24]</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1.14</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>[0.48, 1.78]</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>1.16</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>[0.42, 1.77]</t>
         </is>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>1.41</v>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>[0.72, 2.16]</t>
         </is>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>[-0.75, 0.30]</t>
         </is>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>76</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>76.7</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>13.8</v>
       </c>
     </row>
@@ -17071,64 +17109,67 @@
         <v>0.67</v>
       </c>
       <c r="T13" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.54</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>[1.79, 3.17]</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.38</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[-0.34, 1.00]</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>13</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>0.46</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>[-0.17, 1.17]</t>
         </is>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>8.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>0.7</v>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>[0.06, 1.38]</t>
         </is>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>[-0.36, 0.20]</t>
         </is>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>67.5</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>15.7</v>
       </c>
     </row>
@@ -17195,64 +17236,67 @@
         <v>0.739</v>
       </c>
       <c r="T14" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="U14" t="n">
         <v>4.97</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>[4.28, 5.67]</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>1.57</v>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>[0.96, 2.14]</t>
         </is>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>[0.97, 2.15]</t>
         </is>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>[1.09, 2.26]</t>
         </is>
       </c>
-      <c r="AE14" t="n">
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>[-0.56, 0.22]</t>
         </is>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>78</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>77.3</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -17319,64 +17363,67 @@
         <v>0.742</v>
       </c>
       <c r="T15" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="U15" t="n">
         <v>3.06</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>[2.33, 3.66]</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.8</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>[0.20, 1.30]</t>
         </is>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>0.84</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>[0.29, 1.43]</t>
         </is>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>0.97</v>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>[0.40, 1.45]</t>
         </is>
       </c>
-      <c r="AE15" t="n">
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AG15" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>[-0.27, 0.22]</t>
         </is>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>61.5</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
         <v>14.6</v>
       </c>
     </row>
@@ -17443,64 +17490,67 @@
         <v>0.676</v>
       </c>
       <c r="T16" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="U16" t="n">
         <v>0.8</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>[-2.14, 3.50]</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>25.5</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>-0.93</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>[-3.80, 2.04]</t>
         </is>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>74.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>[-3.52, 3.46]</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>51</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>-1.07</v>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>[-4.22, 1.86]</t>
         </is>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>79.5</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>[-0.97, 1.71]</t>
         </is>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>44</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
         <v>44.1</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AK16" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17567,64 +17617,67 @@
         <v>0.639</v>
       </c>
       <c r="T17" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="U17" t="n">
         <v>-0.93</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>[-3.45, 1.59]</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>80.5</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>-1.51</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>[-4.34, 1.68]</t>
         </is>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>84.5</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-1.09</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>[-4.42, 2.11]</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>77.5</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>-2.06</v>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>[-4.72, 0.55]</t>
         </is>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>95.5</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>-0.37</v>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>[-1.56, 0.89]</t>
         </is>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>78.5</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
         <v>39.9</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AK17" t="n">
         <v>25.8</v>
       </c>
     </row>
@@ -17691,64 +17744,67 @@
         <v>0.589</v>
       </c>
       <c r="T18" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.11</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>[-0.62, 2.74]</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>9</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>-1.15</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>[-2.89, 0.86]</t>
         </is>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>89.5</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>-0.53</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>[-2.57, 1.70]</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>69.5</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>[-2.03, 2.30]</t>
         </is>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>51.5</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>[-1.05, 1.05]</t>
         </is>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>49.5</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>50.4</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AK18" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -17815,64 +17871,67 @@
         <v>0.547</v>
       </c>
       <c r="T19" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="U19" t="n">
         <v>-0.71</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>[-2.30, 1.04]</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>81.5</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>-1.77</v>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>[-3.55, 0.30]</t>
         </is>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>95.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-1.33</v>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>[-3.12, 0.66]</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>91.5</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>-0.82</v>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>[-2.65, 0.94]</t>
         </is>
       </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
         <v>81</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AG19" t="n">
         <v>-0.42</v>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>[-1.21, 0.39]</t>
         </is>
       </c>
-      <c r="AH19" t="n">
+      <c r="AI19" t="n">
         <v>80.5</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
         <v>44.1</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AK19" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -17939,64 +17998,67 @@
         <v>0.572</v>
       </c>
       <c r="T20" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.37</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>[0.11, 2.58]</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>1.5</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>-1.14</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>[-2.46, 0.58]</t>
         </is>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>93.5</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>[-2.17, 0.94]</t>
         </is>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>83</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>0.23</v>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>[-1.12, 1.97]</t>
         </is>
       </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
         <v>41</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>[-0.79, 0.95]</t>
         </is>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>43.5</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
         <v>56.6</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -18063,64 +18125,67 @@
         <v>0.515</v>
       </c>
       <c r="T21" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="U21" t="n">
         <v>-0.49</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>[-1.57, 0.80]</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>82.5</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>-1.79</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>[-2.99, -0.10]</t>
         </is>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>98</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>-1.33</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>[-2.62, 0.23]</t>
         </is>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>97</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>[-1.74, 1.09]</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AF21" t="n">
         <v>69</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AG21" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>[-1.07, 0.29]</t>
         </is>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>83.5</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
         <v>47.4</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AK21" t="n">
         <v>22.8</v>
       </c>
     </row>
@@ -18187,64 +18252,67 @@
         <v>0.573</v>
       </c>
       <c r="T22" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.99</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>[0.93, 3.13]</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>-0.83</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>[-1.91, 0.27]</t>
         </is>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>94</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>[-1.66, 0.50]</t>
         </is>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>87</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>0.55</v>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>[-0.48, 1.61]</t>
         </is>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>17.5</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>[-0.71, 0.84]</t>
         </is>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>48</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
         <v>61.9</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AK22" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -18311,64 +18379,67 @@
         <v>0.508</v>
       </c>
       <c r="T23" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="U23" t="n">
         <v>0.08</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>[-0.93, 1.23]</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>47.5</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>-1.55</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>[-2.49, -0.59]</t>
         </is>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>99.5</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>-1.18</v>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>[-2.25, -0.10]</t>
         </is>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>98</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>0.02</v>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>[-0.93, 1.16]</t>
         </is>
       </c>
-      <c r="AE23" t="n">
+      <c r="AF23" t="n">
         <v>53.5</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>[-0.85, 0.31]</t>
         </is>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>80</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>54.2</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>21</v>
       </c>
     </row>
@@ -18435,64 +18506,67 @@
         <v>0.616</v>
       </c>
       <c r="T24" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="U24" t="n">
         <v>3.36</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>[2.43, 4.21]</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>0</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.23</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>[-0.72, 1.01]</t>
         </is>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>29.5</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>0.3</v>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>[-0.57, 1.07]</t>
         </is>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>23.5</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>0.88</v>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>[0.11, 1.71]</t>
         </is>
       </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>1</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>[-0.68, 0.42]</t>
         </is>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>64</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>19.2</v>
       </c>
     </row>
@@ -18559,64 +18633,67 @@
         <v>0.556</v>
       </c>
       <c r="T25" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.45</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>[0.57, 2.30]</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>0</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>-0.52</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>[-1.48, 0.23]</t>
         </is>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>88.5</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>[-1.25, 0.78]</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>74</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>0.26</v>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>[-0.55, 1.14]</t>
         </is>
       </c>
-      <c r="AE25" t="n">
+      <c r="AF25" t="n">
         <v>27</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>[-0.62, 0.22]</t>
         </is>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>71.5</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>65.3</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>19</v>
       </c>
     </row>
@@ -18683,64 +18760,67 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="T26" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="U26" t="n">
         <v>4.5</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>[3.77, 5.15]</t>
         </is>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>0</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1.17</v>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>[0.54, 1.86]</t>
         </is>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>1.2</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>[0.57, 1.86]</t>
         </is>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>1.39</v>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>[0.69, 2.13]</t>
         </is>
       </c>
-      <c r="AE26" t="n">
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AG26" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>[-0.73, 0.30]</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>77</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>16.1</v>
       </c>
     </row>
@@ -18807,64 +18887,67 @@
         <v>0.658</v>
       </c>
       <c r="T27" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="U27" t="n">
         <v>2.6</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>[1.87, 3.29]</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.44</v>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>[-0.26, 1.15]</t>
         </is>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>[-0.18, 1.13]</t>
         </is>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>8</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>[0.05, 1.35]</t>
         </is>
       </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AG27" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>[-0.44, 0.23]</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>70</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>72.5</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>16.6</v>
       </c>
     </row>
@@ -18931,64 +19014,67 @@
         <v>0.732</v>
       </c>
       <c r="T28" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="U28" t="n">
         <v>4.98</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>[4.36, 5.60]</t>
         </is>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>0</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.6</v>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>[0.93, 2.12]</t>
         </is>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>[1.04, 2.08]</t>
         </is>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>1.69</v>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>[0.96, 2.39]</t>
         </is>
       </c>
-      <c r="AE28" t="n">
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>[-0.62, 0.31]</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>76</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -19055,64 +19141,67 @@
         <v>0.735</v>
       </c>
       <c r="T29" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="U29" t="n">
         <v>3.08</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>[2.45, 3.77]</t>
         </is>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>0.86</v>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>[0.28, 1.45]</t>
         </is>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>0.87</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>[0.26, 1.44]</t>
         </is>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>0.96</v>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>[0.44, 1.49]</t>
         </is>
       </c>
-      <c r="AE29" t="n">
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AG29" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>[-0.31, 0.24]</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>66</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>75.7</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>15.8</v>
       </c>
     </row>
@@ -23484,7 +23573,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>평균수축가중λ</t>
+          <t>평균수축가중λ(합성표적)</t>
         </is>
       </c>
     </row>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -23938,7 +23938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23984,25 +23984,45 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>F3%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Δ(F2−F1)%p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ΔFF_CI</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Δ(F3−F1)%p</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Δ(F3−F2)%p</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>고정쌍최대차이%p</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>불일치율_F1vsR1%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>불일치율_F1vsF2%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Holm_p</t>
         </is>
@@ -24038,20 +24058,32 @@
         <v>0.001</v>
       </c>
       <c r="I2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>[-1.8, 0.8]</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" t="n">
         <v>11.1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>5.3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -24085,20 +24117,32 @@
         <v>0.1639</v>
       </c>
       <c r="I3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="J3" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>[-2.3, 0.9]</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O3" t="n">
         <v>10.3</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>6.2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0.1919</v>
       </c>
     </row>
@@ -24132,20 +24176,32 @@
         <v>0.064</v>
       </c>
       <c r="I4" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>[-0.6, 0.7]</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.4</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1.2</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0.1919</v>
       </c>
     </row>
@@ -24179,20 +24235,32 @@
         <v>0.001</v>
       </c>
       <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="n">
         <v>-1.3</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>[-3.1, 0.4]</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O5" t="n">
         <v>22.6</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -24226,20 +24294,32 @@
         <v>0.003</v>
       </c>
       <c r="I6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J6" t="n">
         <v>-2.8</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>[-4.4, -1.0]</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
         <v>10.5</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>7.1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0.012</v>
       </c>
     </row>
@@ -24273,20 +24353,32 @@
         <v>0.076</v>
       </c>
       <c r="I7" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>[-0.6, 0.6]</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>1.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0.1919</v>
       </c>
     </row>
@@ -24320,20 +24412,32 @@
         <v>0.002</v>
       </c>
       <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.2</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>[-0.6, 1.0]</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -24367,20 +24471,32 @@
         <v>0.001</v>
       </c>
       <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>[-3.2, 0.7]</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O9" t="n">
         <v>14.7</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -24635,7 +24751,7 @@
         <v>0.191</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -13123,7 +13123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13152,6 +13152,11 @@
           <t>분할분위_상한</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>검정MAE%p_클리핑[0,1]</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13173,6 +13178,9 @@
       <c r="E2" t="n">
         <v>15.03</v>
       </c>
+      <c r="F2" t="n">
+        <v>10.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13194,6 +13202,9 @@
       <c r="E3" t="n">
         <v>8.99</v>
       </c>
+      <c r="F3" t="n">
+        <v>7.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13215,6 +13226,9 @@
       <c r="E4" t="n">
         <v>9.42</v>
       </c>
+      <c r="F4" t="n">
+        <v>8.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13236,6 +13250,9 @@
       <c r="E5" t="n">
         <v>5.64</v>
       </c>
+      <c r="F5" t="n">
+        <v>4.69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13257,6 +13274,9 @@
       <c r="E6" t="n">
         <v>8.91</v>
       </c>
+      <c r="F6" t="n">
+        <v>7.81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13278,6 +13298,9 @@
       <c r="E7" t="n">
         <v>8.93</v>
       </c>
+      <c r="F7" t="n">
+        <v>7.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13299,6 +13322,9 @@
       <c r="E8" t="n">
         <v>3.89</v>
       </c>
+      <c r="F8" t="n">
+        <v>3.32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13320,6 +13346,9 @@
       <c r="E9" t="n">
         <v>5.62</v>
       </c>
+      <c r="F9" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13416,6 +13445,9 @@
       <c r="E15" t="n">
         <v>9.109999999999999</v>
       </c>
+      <c r="F15" t="n">
+        <v>7.87</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13437,6 +13469,9 @@
       <c r="E16" t="n">
         <v>7.06</v>
       </c>
+      <c r="F16" t="n">
+        <v>6.41</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13458,6 +13493,9 @@
       <c r="E17" t="n">
         <v>7.37</v>
       </c>
+      <c r="F17" t="n">
+        <v>6.36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13479,6 +13517,9 @@
       <c r="E18" t="n">
         <v>4.88</v>
       </c>
+      <c r="F18" t="n">
+        <v>4.06</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13500,6 +13541,9 @@
       <c r="E19" t="n">
         <v>7.13</v>
       </c>
+      <c r="F19" t="n">
+        <v>6.37</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13521,6 +13565,9 @@
       <c r="E20" t="n">
         <v>7.08</v>
       </c>
+      <c r="F20" t="n">
+        <v>6.37</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13542,6 +13589,9 @@
       <c r="E21" t="n">
         <v>4</v>
       </c>
+      <c r="F21" t="n">
+        <v>3.46</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13562,6 +13612,9 @@
       </c>
       <c r="E22" t="n">
         <v>5.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.14</v>
       </c>
     </row>
     <row r="23">
@@ -15402,16 +15455,16 @@
         <v>15.11</v>
       </c>
       <c r="C3" t="n">
-        <v>14.6</v>
+        <v>14.49</v>
       </c>
       <c r="D3" t="n">
-        <v>15.83</v>
+        <v>15.71</v>
       </c>
       <c r="E3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -24751,7 +24804,7 @@
         <v>0.191</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -24857,13 +24910,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="C3" t="n">
-        <v>17.43</v>
+        <v>17.79</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
@@ -26258,7 +26311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26324,6 +26377,16 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>제외민감도_차이하한%p</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>제외민감도_차이상한%p</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Holm_p</t>
         </is>
       </c>
@@ -26368,6 +26431,12 @@
         <v>79.59999999999999</v>
       </c>
       <c r="M2" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="O2" t="n">
         <v>2.908488420455043e-101</v>
       </c>
     </row>
@@ -26411,6 +26480,12 @@
         <v>92.59999999999999</v>
       </c>
       <c r="M3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="O3" t="n">
         <v>4.352803174439392e-41</v>
       </c>
     </row>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3159</v>
+        <v>0.3168</v>
       </c>
       <c r="C2" t="n">
         <v>0.3686</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E2" t="n">
         <v>0.4327</v>
       </c>
       <c r="F2" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="3">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9093</v>
+        <v>0.9092</v>
       </c>
       <c r="C3" t="n">
         <v>0.5583</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9558</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9999</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4</v>
+        <v>4.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8273</v>
+        <v>0.9241</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.8</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="5">
@@ -852,19 +852,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8649</v>
+        <v>0.8659</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1429</v>
+        <v>0.1714</v>
       </c>
       <c r="D5" t="n">
-        <v>-72.2</v>
+        <v>-69.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2877</v>
+        <v>0.3198</v>
       </c>
       <c r="F5" t="n">
-        <v>-57.7</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="6">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6424</v>
+        <v>0.6486</v>
       </c>
       <c r="C6" t="n">
         <v>0.4001</v>
       </c>
       <c r="D6" t="n">
-        <v>-24.2</v>
+        <v>-24.8</v>
       </c>
       <c r="E6" t="n">
         <v>0.7191</v>
       </c>
       <c r="F6" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409</v>
       </c>
       <c r="C7" t="n">
         <v>0.9442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="n">
         <v>0.7329</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.5</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="8">
@@ -918,19 +918,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0735</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>0.0166</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.7</v>
+        <v>-5.3</v>
       </c>
       <c r="E8" t="n">
         <v>0.0697</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -940,19 +940,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2226</v>
+        <v>0.2247</v>
       </c>
       <c r="C9" t="n">
         <v>0.3278</v>
       </c>
       <c r="D9" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="E9" t="n">
         <v>0.3457</v>
       </c>
       <c r="F9" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
     </row>
   </sheetData>
@@ -1001,10 +1001,10 @@
         <v>0.887</v>
       </c>
       <c r="C2" t="n">
-        <v>0.759</v>
+        <v>0.769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.427</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="3">
@@ -1017,10 +1017,10 @@
         <v>0.947</v>
       </c>
       <c r="C3" t="n">
-        <v>0.432</v>
+        <v>0.437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.391</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="4">
@@ -1033,10 +1033,10 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.109</v>
+        <v>0.113</v>
       </c>
       <c r="D4" t="n">
-        <v>0.344</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="5">
@@ -1049,10 +1049,10 @@
         <v>0.889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="D5" t="n">
-        <v>0.301</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="6">
@@ -1065,10 +1065,10 @@
         <v>0.831</v>
       </c>
       <c r="C6" t="n">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="D6" t="n">
-        <v>0.254</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="7">
@@ -1081,10 +1081,10 @@
         <v>0.783</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="D7" t="n">
-        <v>0.211</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="8">
@@ -1097,10 +1097,10 @@
         <v>0.766</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.172</v>
+        <v>0.226</v>
       </c>
     </row>
   </sheetData>
@@ -1159,10 +1159,10 @@
         <v>0.696</v>
       </c>
       <c r="D2" t="n">
-        <v>0.285</v>
+        <v>0.425</v>
       </c>
       <c r="E2" t="n">
-        <v>0.522</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="3">
@@ -1180,10 +1180,10 @@
         <v>0.731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.294</v>
+        <v>0.425</v>
       </c>
       <c r="E3" t="n">
-        <v>0.576</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="4">
@@ -1201,10 +1201,10 @@
         <v>0.865</v>
       </c>
       <c r="D4" t="n">
-        <v>0.159</v>
+        <v>0.271</v>
       </c>
       <c r="E4" t="n">
-        <v>0.292</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="5">
@@ -1222,10 +1222,10 @@
         <v>0.892</v>
       </c>
       <c r="D5" t="n">
-        <v>0.169</v>
+        <v>0.271</v>
       </c>
       <c r="E5" t="n">
-        <v>0.334</v>
+        <v>0.339</v>
       </c>
     </row>
   </sheetData>
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-12.8</v>
+        <v>-11.8</v>
       </c>
       <c r="D3" t="n">
-        <v>-76.3</v>
+        <v>-69.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.6</v>
+        <v>-7.9</v>
       </c>
       <c r="F3" t="n">
-        <v>67.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1373,49 +1373,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>유튜브_이용</t>
+          <t>AI_이용여부</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXAONE</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.2</v>
+        <v>43.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-36.5</v>
+        <v>1.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="F6" t="n">
-        <v>11.8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI_이용여부</t>
+          <t>메신저_이용</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>EXAONE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43.6</v>
+        <v>-9.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9</v>
+        <v>-16.6</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.4</v>
+        <v>-3.6</v>
       </c>
       <c r="F7" t="n">
-        <v>9.699999999999999</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="8">
@@ -1426,44 +1426,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>EXAONE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.8</v>
+        <v>-17.2</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3</v>
+        <v>-3.3</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>메신저_이용</t>
+          <t>메타버스_이용</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EXAONE</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-9.4</v>
+        <v>-10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-16.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6</v>
+        <v>2.8</v>
       </c>
       <c r="F9" t="n">
-        <v>19.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1474,26 +1474,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>EXAONE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-10.1</v>
+        <v>-13.8</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>메타버스_이용</t>
+          <t>콘텐츠구독_이용</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1502,22 +1502,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-13.8</v>
+        <v>15.7</v>
       </c>
       <c r="D11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.6</v>
       </c>
-      <c r="E11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="F11" t="n">
-        <v>5.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>콘텐츠구독_이용</t>
+          <t>SNS_이용</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.7</v>
+        <v>24.8</v>
       </c>
       <c r="D12" t="n">
-        <v>19.3</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SNS_이용</t>
+          <t>OTT_이용</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1550,22 +1550,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.8</v>
+        <v>-13.2</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OTT_이용</t>
+          <t>숏폼_이용</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,22 +1574,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-13.2</v>
+        <v>-44</v>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>-54</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>숏폼_이용</t>
+          <t>AI_이용여부</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1598,46 +1598,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-46</v>
+        <v>21.2</v>
       </c>
       <c r="D15" t="n">
-        <v>-59.3</v>
+        <v>13.1</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5</v>
+        <v>0.6</v>
       </c>
       <c r="F15" t="n">
-        <v>56.3</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI_이용여부</t>
+          <t>메신저_이용</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXAONE</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>11.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>메신저_이용</t>
+          <t>유튜브_이용</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="C2" t="n">
         <v>2.45</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>이진_예선택률_사후층화 = 8개 이진 지표의 사후층화 이용률 평균(RQ1_전체일치도 와 동일 산식). 실측 비교값 0.559 와 같은 기준이다. 비가중 열은 원문항 응답 합산 비율. v1.10 이전에 옮겨 적힌 0.549/0.602 는 산식이 기록되지 않아 재현되지 않았으며 v1.12에서 정정함. 5점_평균 2.45/3.05 는 원문항 24개 비가중 평균이고, 논문 IV-C 가 인용하는 값은 구성개념 8개 사후층화 평균 2.54/3.03(구성개념 시트)이다.</t>
+          <t>이진_예선택률_사후층화 = 8개 이진 지표의 사후층화 이용률 평균(RQ1_전체일치도 와 동일 산식). 실측 비교값 0.559 와 같은 기준이다. 비가중 열은 원문항 응답 합산 비율. v1.10 이전에 옮겨 적힌 0.549/0.602 는 산식이 기록되지 않아 재현되지 않았으며 v1.12에서 정정함. v1.20에서 OTT 스킵 로직 적용 후 0.525/0.595 로 갱신. 5점_평균 2.45/3.05 는 원문항 24개 비가중 평균이고, 논문 IV-C 가 인용하는 값은 구성개념 8개 사후층화 평균 2.54/3.03(구성개념 시트)이다.</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.575</v>
+        <v>0.595</v>
       </c>
       <c r="C3" t="n">
         <v>3.05</v>
@@ -1806,6 +1806,7 @@
       <c r="I3" t="n">
         <v>38</v>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>0.582</v>
       </c>
@@ -1923,18 +1924,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.4</v>
+        <v>9.6</v>
       </c>
       <c r="D4" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>남성·70대이상</t>
+          <t>여성·40대</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-19.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="5">
@@ -1949,10 +1950,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77.7</v>
+        <v>77.2</v>
       </c>
       <c r="D5" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1960,7 +1961,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-65.40000000000001</v>
+        <v>-64.5</v>
       </c>
     </row>
     <row r="6">
@@ -2177,18 +2178,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>19.2</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>여성·70대이상</t>
+          <t>여성·20대</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-29.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -2203,10 +2204,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>41.2</v>
       </c>
       <c r="D5" t="n">
-        <v>9.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2214,7 +2215,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-29</v>
+        <v>-26.9</v>
       </c>
     </row>
     <row r="6">
@@ -2364,7 +2365,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="3">
@@ -2379,7 +2380,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9</v>
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>
@@ -2435,19 +2436,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="C2" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E2" t="n">
-        <v>4.300000000000001</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2457,19 +2458,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="C3" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="D3" t="n">
         <v>6.6</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>9.4</v>
+        <v>8.700000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2604,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2623,7 +2624,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2643,7 +2644,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2663,7 +2664,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.7</v>
+        <v>15.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2683,7 +2684,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2703,7 +2704,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2723,7 +2724,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.3</v>
+        <v>14.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2743,7 +2744,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2814,13 +2815,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="C2" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
@@ -2846,13 +2847,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="C3" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -2939,22 +2940,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="C2" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="F2" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2974,22 +2975,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D3" t="n">
         <v>6.7</v>
       </c>
       <c r="E3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G3" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -3335,13 +3336,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E2" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="G2" t="n">
         <v>13.3</v>
@@ -3353,11 +3354,11 @@
         <v>12.7</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[-4.9, -0.4]</t>
+          <t>[-5.1, -0.6]</t>
         </is>
       </c>
     </row>
@@ -3376,10 +3377,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="E3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>8.6</v>
@@ -3394,11 +3395,11 @@
         <v>12.7</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[-6.8, -2.6]</t>
+          <t>[-6.8, -2.7]</t>
         </is>
       </c>
     </row>
@@ -3417,13 +3418,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F4" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>7.4</v>
@@ -3435,11 +3436,11 @@
         <v>11.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[0.5, 2.7]</t>
+          <t>[0.2, 2.5]</t>
         </is>
       </c>
     </row>
@@ -3458,10 +3459,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="F5" t="n">
         <v>7.1</v>
@@ -3476,7 +3477,7 @@
         <v>11.9</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3499,13 +3500,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="F6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
         <v>5.4</v>
@@ -3517,11 +3518,11 @@
         <v>11.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[2.2, 4.2]</t>
+          <t>[1.9, 3.9]</t>
         </is>
       </c>
     </row>
@@ -3540,10 +3541,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F7" t="n">
         <v>6.8</v>
@@ -3581,13 +3582,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="F8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>4.1</v>
@@ -3599,11 +3600,11 @@
         <v>11.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[3.7, 5.3]</t>
+          <t>[3.3, 5.0]</t>
         </is>
       </c>
     </row>
@@ -3622,10 +3623,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F9" t="n">
         <v>6.7</v>
@@ -3644,7 +3645,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[1.8, 3.3]</t>
+          <t>[1.7, 3.3]</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3664,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E10" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="F10" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>3.6</v>
@@ -3681,11 +3682,11 @@
         <v>11.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[4.3, 5.6]</t>
+          <t>[4.0, 5.3]</t>
         </is>
       </c>
     </row>
@@ -3704,13 +3705,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="G11" t="n">
         <v>3.6</v>
@@ -3722,7 +3723,7 @@
         <v>11.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3745,13 +3746,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E12" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="F12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G12" t="n">
         <v>13.3</v>
@@ -3763,11 +3764,11 @@
         <v>12.9</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[-5.0, 0.6]</t>
+          <t>[-5.2, 0.4]</t>
         </is>
       </c>
     </row>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="E13" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>9.1</v>
@@ -3808,7 +3809,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[-6.5, -1.2]</t>
+          <t>[-6.6, -1.3]</t>
         </is>
       </c>
     </row>
@@ -3827,13 +3828,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="F14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G14" t="n">
         <v>7.3</v>
@@ -3845,11 +3846,11 @@
         <v>11.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[0.4, 3.0]</t>
+          <t>[0.2, 2.8]</t>
         </is>
       </c>
     </row>
@@ -3868,10 +3869,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="F15" t="n">
         <v>7.2</v>
@@ -3909,13 +3910,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G16" t="n">
         <v>5.5</v>
@@ -3927,11 +3928,11 @@
         <v>11.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[2.4, 4.3]</t>
+          <t>[2.1, 4.0]</t>
         </is>
       </c>
     </row>
@@ -3950,10 +3951,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="F17" t="n">
         <v>6.9</v>
@@ -3972,7 +3973,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[0.4, 2.4]</t>
+          <t>[0.4, 2.3]</t>
         </is>
       </c>
     </row>
@@ -3991,13 +3992,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="E18" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="F18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G18" t="n">
         <v>4.2</v>
@@ -4009,11 +4010,11 @@
         <v>11.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[3.6, 5.1]</t>
+          <t>[3.3, 4.8]</t>
         </is>
       </c>
     </row>
@@ -4032,10 +4033,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F19" t="n">
         <v>6.7</v>
@@ -4054,7 +4055,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[1.6, 3.3]</t>
+          <t>[1.6, 3.2]</t>
         </is>
       </c>
     </row>
@@ -4073,13 +4074,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="F20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G20" t="n">
         <v>3.7</v>
@@ -4091,11 +4092,11 @@
         <v>11.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[4.3, 5.5]</t>
+          <t>[4.0, 5.2]</t>
         </is>
       </c>
     </row>
@@ -4114,13 +4115,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="E21" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="F21" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="G21" t="n">
         <v>3.7</v>
@@ -4136,7 +4137,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[2.3, 3.6]</t>
+          <t>[2.3, 3.5]</t>
         </is>
       </c>
     </row>
@@ -4198,13 +4199,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="C2" t="n">
-        <v>15.7</v>
+        <v>15.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>8.699999999999999</v>
@@ -4225,13 +4226,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="C3" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="E3" t="n">
         <v>8.6</v>
@@ -4321,19 +4322,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944</v>
+        <v>0.949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.116</v>
+        <v>0.189</v>
       </c>
       <c r="G2" t="n">
         <v>0.029</v>
       </c>
       <c r="H2" t="n">
-        <v>0.795</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0.788</v>
@@ -4354,19 +4355,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.14</v>
+        <v>0.205</v>
       </c>
       <c r="G3" t="n">
         <v>0.033</v>
       </c>
       <c r="H3" t="n">
-        <v>0.785</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
         <v>0.777</v>
@@ -4387,19 +4388,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.968</v>
+        <v>0.971</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="G4" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="H4" t="n">
-        <v>0.903</v>
+        <v>0.912</v>
       </c>
       <c r="I4" t="n">
         <v>0.5</v>
@@ -4420,19 +4421,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.968</v>
+        <v>0.971</v>
       </c>
       <c r="F5" t="n">
-        <v>0.074</v>
+        <v>0.066</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="H5" t="n">
-        <v>0.908</v>
+        <v>0.916</v>
       </c>
       <c r="I5" t="n">
         <v>0.538</v>
@@ -4456,16 +4457,16 @@
         <v>19.4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.911</v>
+        <v>0.914</v>
       </c>
       <c r="F6" t="n">
-        <v>0.227</v>
+        <v>0.234</v>
       </c>
       <c r="G6" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="7">
@@ -4486,16 +4487,16 @@
         <v>20.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.891</v>
+        <v>0.894</v>
       </c>
       <c r="F7" t="n">
-        <v>0.305</v>
+        <v>0.329</v>
       </c>
       <c r="G7" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.666</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="8">
@@ -4513,19 +4514,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.949</v>
+        <v>0.953</v>
       </c>
       <c r="F8" t="n">
-        <v>0.134</v>
+        <v>0.114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.765</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="9">
@@ -4543,19 +4544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.9</v>
+        <v>15.2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.948</v>
+        <v>0.953</v>
       </c>
       <c r="F9" t="n">
-        <v>0.14</v>
+        <v>0.119</v>
       </c>
       <c r="G9" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.768</v>
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -4616,16 +4617,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="D2" t="n">
-        <v>52.3</v>
+        <v>49.6</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="F2" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="3">
@@ -4640,16 +4641,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="D3" t="n">
-        <v>42.2</v>
+        <v>39.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6</v>
+        <v>16.5</v>
       </c>
       <c r="F3" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="4">
@@ -4664,16 +4665,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="D4" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="5">
@@ -4688,16 +4689,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="E5" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="F5" t="n">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>
@@ -4758,13 +4759,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>3.6</v>
@@ -4782,13 +4783,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="F3" t="n">
         <v>3.2</v>
@@ -4806,10 +4807,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="D4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="E4" t="n">
         <v>6.7</v>
@@ -4830,10 +4831,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>5.7</v>
@@ -4942,16 +4943,16 @@
         <v>0.9319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9696</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8659</v>
+        <v>0.9613</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -4964,16 +4965,16 @@
         <v>0.696</v>
       </c>
       <c r="C5" t="n">
-        <v>0.252</v>
+        <v>0.2764</v>
       </c>
       <c r="D5" t="n">
-        <v>-44.4</v>
+        <v>-42</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5139</v>
+        <v>0.5588</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.2</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="6">
@@ -5122,10 +5123,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
@@ -5146,10 +5147,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="E3" t="n">
         <v>12.9</v>
@@ -5170,10 +5171,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
@@ -5194,10 +5195,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="E5" t="n">
         <v>12.9</v>
@@ -5263,7 +5264,7 @@
         <v>22.3</v>
       </c>
       <c r="E2" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="3">
@@ -5282,7 +5283,7 @@
         <v>20.3</v>
       </c>
       <c r="E3" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
     </row>
   </sheetData>
@@ -5338,7 +5339,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.6</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="3">
@@ -5358,7 +5359,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="4">
@@ -5378,7 +5379,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -5398,7 +5399,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="6">
@@ -5418,7 +5419,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="7">
@@ -5438,7 +5439,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>15.8</v>
       </c>
     </row>
   </sheetData>
@@ -5499,16 +5500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.3</v>
+        <v>49.6</v>
       </c>
       <c r="D2" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="F2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="3">
@@ -5523,16 +5524,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.2</v>
+        <v>39.5</v>
       </c>
       <c r="D3" t="n">
-        <v>40.7</v>
+        <v>39.6</v>
       </c>
       <c r="E3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="F3" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="4">
@@ -5547,16 +5548,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3</v>
+        <v>29.7</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="5">
@@ -5571,16 +5572,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="D5" t="n">
-        <v>30.9</v>
+        <v>28.3</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
     </row>
   </sheetData>
@@ -5716,23 +5717,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>남성 70대이상</t>
+          <t>여성 40대</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-19.5</v>
+        <v>11.9</v>
       </c>
       <c r="E4" t="n">
-        <v>31.4</v>
+        <v>9.6</v>
       </c>
       <c r="F4" t="n">
-        <v>19.5</v>
+        <v>11.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -5752,16 +5753,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-65.40000000000001</v>
+        <v>-64.5</v>
       </c>
       <c r="E5" t="n">
-        <v>77.7</v>
+        <v>77.2</v>
       </c>
       <c r="F5" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G5" t="n">
-        <v>40.1</v>
+        <v>37.9</v>
       </c>
       <c r="H5" t="n">
         <v>26.2</v>
@@ -5972,23 +5973,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>여성 70대이상</t>
+          <t>여성 20대</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-29.1</v>
+        <v>10.7</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>19.2</v>
       </c>
       <c r="F12" t="n">
-        <v>29.1</v>
+        <v>10.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.1</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>12.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -6008,19 +6009,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-29</v>
+        <v>-26.9</v>
       </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>41.2</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="H13" t="n">
-        <v>9.699999999999999</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="14">
@@ -6219,10 +6220,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="F2" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="G2" t="n">
         <v>36</v>
@@ -6245,7 +6246,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="F3" t="n">
         <v>12.1</v>
@@ -6358,7 +6359,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>80.2</v>
@@ -6503,10 +6504,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="F12" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="G12" t="n">
         <v>75</v>
@@ -6529,10 +6530,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="G13" t="n">
         <v>36</v>
@@ -6639,7 +6640,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95.8</v>
+        <v>99</v>
       </c>
       <c r="E17" t="n">
         <v>91.09999999999999</v>
@@ -6668,7 +6669,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68.8</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
         <v>80.2</v>
@@ -6813,10 +6814,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="F23" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="G23" t="n">
         <v>75</v>
@@ -11358,19 +11359,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17.11</v>
+        <v>16.95</v>
       </c>
       <c r="F2" t="n">
-        <v>14.92</v>
+        <v>13.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>1.53</v>
+        <v>2.51</v>
       </c>
       <c r="I2" t="n">
-        <v>2.93</v>
+        <v>3.77</v>
       </c>
       <c r="J2" t="n">
         <v>0.0033</v>
@@ -11478,25 +11479,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.73</v>
+        <v>6.76</v>
       </c>
       <c r="F5" t="n">
-        <v>6.65</v>
+        <v>3.41</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.92</v>
+        <v>3.35</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.24</v>
+        <v>2.93</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.44</v>
+        <v>3.79</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0333</v>
+        <v>0.0033</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0266</v>
       </c>
     </row>
     <row r="6">
@@ -11519,19 +11520,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.56</v>
+        <v>40.21</v>
       </c>
       <c r="F6" t="n">
-        <v>18.38</v>
+        <v>12.72</v>
       </c>
       <c r="G6" t="n">
-        <v>26.18</v>
+        <v>27.49</v>
       </c>
       <c r="H6" t="n">
-        <v>24.65</v>
+        <v>25.71</v>
       </c>
       <c r="I6" t="n">
-        <v>27.56</v>
+        <v>29.35</v>
       </c>
       <c r="J6" t="n">
         <v>0.0033</v>
@@ -11724,22 +11725,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.11</v>
+        <v>16.95</v>
       </c>
       <c r="F11" t="n">
-        <v>17.01</v>
+        <v>16.88</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2496</v>
+        <v>0.4626</v>
       </c>
     </row>
     <row r="12">
@@ -11844,25 +11845,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.73</v>
+        <v>6.76</v>
       </c>
       <c r="F14" t="n">
-        <v>3.61</v>
+        <v>6.76</v>
       </c>
       <c r="G14" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3195</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4592</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -11885,25 +11886,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>44.57</v>
+        <v>40.22</v>
       </c>
       <c r="F15" t="n">
-        <v>44.12</v>
+        <v>39.92</v>
       </c>
       <c r="G15" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.13</v>
+        <v>-0.65</v>
       </c>
       <c r="I15" t="n">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1198</v>
+        <v>0.5524</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3594</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -12067,7 +12068,7 @@
         <v>0.2296</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4592</v>
+        <v>0.6889</v>
       </c>
     </row>
     <row r="20">
@@ -12090,19 +12091,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14.91</v>
+        <v>13.81</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99</v>
+        <v>11.7</v>
       </c>
       <c r="G20" t="n">
-        <v>2.93</v>
+        <v>2.11</v>
       </c>
       <c r="H20" t="n">
-        <v>2.51</v>
+        <v>1.72</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="J20" t="n">
         <v>0.0033</v>
@@ -12210,19 +12211,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.59</v>
+        <v>3.43</v>
       </c>
       <c r="F23" t="n">
-        <v>2.27</v>
+        <v>5.63</v>
       </c>
       <c r="G23" t="n">
-        <v>4.31</v>
+        <v>-2.21</v>
       </c>
       <c r="H23" t="n">
-        <v>3.41</v>
+        <v>-2.72</v>
       </c>
       <c r="I23" t="n">
-        <v>5.19</v>
+        <v>-1.69</v>
       </c>
       <c r="J23" t="n">
         <v>0.0033</v>
@@ -12251,19 +12252,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>18.36</v>
+        <v>12.73</v>
       </c>
       <c r="F24" t="n">
-        <v>15.65</v>
+        <v>10.01</v>
       </c>
       <c r="G24" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="H24" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="I24" t="n">
-        <v>4.06</v>
+        <v>4.33</v>
       </c>
       <c r="J24" t="n">
         <v>0.0033</v>
@@ -12456,19 +12457,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>19.34</v>
+        <v>19.36</v>
       </c>
       <c r="F29" t="n">
-        <v>16.66</v>
+        <v>15.05</v>
       </c>
       <c r="G29" t="n">
-        <v>2.68</v>
+        <v>4.31</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>3.57</v>
       </c>
       <c r="I29" t="n">
-        <v>3.29</v>
+        <v>4.93</v>
       </c>
       <c r="J29" t="n">
         <v>0.0033</v>
@@ -12576,25 +12577,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.49</v>
+        <v>4.4</v>
       </c>
       <c r="F32" t="n">
-        <v>12.85</v>
+        <v>3.17</v>
       </c>
       <c r="G32" t="n">
-        <v>-11.36</v>
+        <v>1.23</v>
       </c>
       <c r="H32" t="n">
-        <v>-12.3</v>
+        <v>-0.55</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.48</v>
+        <v>3.28</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0033</v>
+        <v>0.2263</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0266</v>
+        <v>0.2263</v>
       </c>
     </row>
     <row r="33">
@@ -12617,19 +12618,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>72.31</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>57.81</v>
+        <v>54.6</v>
       </c>
       <c r="G33" t="n">
-        <v>14.5</v>
+        <v>14.93</v>
       </c>
       <c r="H33" t="n">
-        <v>13.15</v>
+        <v>12.84</v>
       </c>
       <c r="I33" t="n">
-        <v>15.98</v>
+        <v>16.96</v>
       </c>
       <c r="J33" t="n">
         <v>0.0033</v>
@@ -12799,7 +12800,7 @@
         <v>0.0233</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0266</v>
+        <v>0.0466</v>
       </c>
     </row>
   </sheetData>
@@ -12880,25 +12881,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.795</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.904</v>
+        <v>0.913</v>
       </c>
       <c r="F2" t="n">
         <v>0.881</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.785, 0.805]</t>
+          <t>[0.802, 0.821]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[0.896, 0.912]</t>
+          <t>[0.906, 0.920]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -12924,25 +12925,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.795</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.798</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.786, 0.805]</t>
+          <t>[0.802, 0.822]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[0.789, 0.808]</t>
+          <t>[0.805, 0.824]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -12968,25 +12969,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.904</v>
+        <v>0.913</v>
       </c>
       <c r="D4" t="n">
         <v>0.881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.916</v>
+        <v>0.926</v>
       </c>
       <c r="F4" t="n">
         <v>0.881</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.896, 0.912]</t>
+          <t>[0.906, 0.920]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[0.909, 0.922]</t>
+          <t>[0.920, 0.931]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -13012,30 +13013,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="D5" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="E5" t="n">
-        <v>0.767</v>
+        <v>0.789</v>
       </c>
       <c r="F5" t="n">
         <v>0.833</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0.680, 0.701]</t>
+          <t>[0.692, 0.716]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[0.755, 0.778]</t>
+          <t>[0.778, 0.799]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0.833, 0.857]</t>
+          <t>[0.857, 0.857]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -13170,16 +13171,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.62</v>
+        <v>14.24</v>
       </c>
       <c r="D2" t="n">
-        <v>14.29</v>
+        <v>13.95</v>
       </c>
       <c r="E2" t="n">
-        <v>15.03</v>
+        <v>14.58</v>
       </c>
       <c r="F2" t="n">
-        <v>10.83</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="3">
@@ -13194,16 +13195,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>8.26</v>
+        <v>7.93</v>
       </c>
       <c r="E3" t="n">
-        <v>8.99</v>
+        <v>8.69</v>
       </c>
       <c r="F3" t="n">
-        <v>7.99</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4">
@@ -13218,16 +13219,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.98</v>
+        <v>8.67</v>
       </c>
       <c r="D4" t="n">
-        <v>8.58</v>
+        <v>8.26</v>
       </c>
       <c r="E4" t="n">
-        <v>9.42</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>8.01</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="5">
@@ -13242,16 +13243,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.86</v>
+        <v>4.68</v>
       </c>
       <c r="E5" t="n">
-        <v>5.64</v>
+        <v>5.43</v>
       </c>
       <c r="F5" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="6">
@@ -13266,16 +13267,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="D6" t="n">
-        <v>8.050000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="E6" t="n">
-        <v>8.91</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>7.81</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="7">
@@ -13290,16 +13291,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.449999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>7.98</v>
+        <v>7.67</v>
       </c>
       <c r="E7" t="n">
-        <v>8.93</v>
+        <v>8.57</v>
       </c>
       <c r="F7" t="n">
-        <v>7.85</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="8">
@@ -13314,16 +13315,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="D8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="F8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -13338,16 +13339,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.21</v>
+        <v>4.92</v>
       </c>
       <c r="D9" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="E9" t="n">
-        <v>5.62</v>
+        <v>5.41</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="10">
@@ -13362,7 +13363,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -13377,7 +13378,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="12">
@@ -13392,7 +13393,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>77.40000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -13407,7 +13408,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="14">
@@ -13422,7 +13423,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15">
@@ -13437,16 +13438,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.83</v>
+        <v>8.41</v>
       </c>
       <c r="D15" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>9.109999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="F15" t="n">
-        <v>7.87</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="16">
@@ -13461,16 +13462,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.69</v>
+        <v>6.66</v>
       </c>
       <c r="D16" t="n">
-        <v>6.34</v>
+        <v>6.29</v>
       </c>
       <c r="E16" t="n">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="F16" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="17">
@@ -13485,16 +13486,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.99</v>
+        <v>6.95</v>
       </c>
       <c r="D17" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="E17" t="n">
-        <v>7.37</v>
+        <v>7.32</v>
       </c>
       <c r="F17" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="18">
@@ -13509,16 +13510,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="D18" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="E18" t="n">
         <v>4.88</v>
       </c>
       <c r="F18" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="19">
@@ -13533,16 +13534,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.69</v>
+        <v>6.59</v>
       </c>
       <c r="D19" t="n">
-        <v>6.3</v>
+        <v>6.22</v>
       </c>
       <c r="E19" t="n">
-        <v>7.13</v>
+        <v>7.03</v>
       </c>
       <c r="F19" t="n">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="20">
@@ -13557,16 +13558,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="D20" t="n">
-        <v>6.31</v>
+        <v>6.19</v>
       </c>
       <c r="E20" t="n">
-        <v>7.08</v>
+        <v>7.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="21">
@@ -13581,16 +13582,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="D21" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="F21" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="22">
@@ -13605,16 +13606,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="D22" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="E22" t="n">
-        <v>5.01</v>
+        <v>4.91</v>
       </c>
       <c r="F22" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="23">
@@ -13644,7 +13645,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="25">
@@ -13659,7 +13660,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -13674,7 +13675,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="27">
@@ -13689,7 +13690,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -13886,37 +13887,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13.26</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>9.720000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="E4" t="n">
-        <v>16.83</v>
+        <v>12.96</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.28</v>
+        <v>-0.92</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.07</v>
+        <v>-1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.58</v>
+        <v>-0.22</v>
       </c>
       <c r="I4" t="n">
-        <v>13.1</v>
+        <v>9.23</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.25</v>
+        <v>-0.89</v>
       </c>
       <c r="K4" t="n">
-        <v>7.42</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>13.16</v>
+        <v>5.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.37</v>
+        <v>0.84</v>
       </c>
       <c r="N4" t="n">
         <v>2.05</v>
@@ -13934,37 +13935,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-16.27</v>
+        <v>-16.83</v>
       </c>
       <c r="D5" t="n">
-        <v>-20.95</v>
+        <v>-21.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.7</v>
+        <v>-11.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.94</v>
+        <v>-5.96</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.369999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.66</v>
+        <v>-4.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.5</v>
+        <v>-17.05</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.91</v>
+        <v>-5.93</v>
       </c>
       <c r="K5" t="n">
-        <v>21.98</v>
+        <v>23.12</v>
       </c>
       <c r="L5" t="n">
-        <v>30.67</v>
+        <v>33.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N5" t="n">
         <v>3.46</v>
@@ -14270,37 +14271,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.21</v>
+        <v>10.22</v>
       </c>
       <c r="D12" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
       <c r="E12" t="n">
-        <v>13.78</v>
+        <v>13.79</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.48</v>
+        <v>-2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.27</v>
+        <v>-3.23</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.78</v>
+        <v>-1.74</v>
       </c>
       <c r="I12" t="n">
         <v>10.06</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.44</v>
+        <v>-2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.53</v>
+        <v>3.77</v>
       </c>
       <c r="L12" t="n">
-        <v>9.449999999999999</v>
+        <v>7.29</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N12" t="n">
         <v>2.05</v>
@@ -14318,37 +14319,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-21.41</v>
+        <v>-20.77</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.09</v>
+        <v>-25.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.84</v>
+        <v>-15.2</v>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>3.49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.83</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>3.54</v>
+        <v>4.78</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.64</v>
+        <v>-21</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="K13" t="n">
-        <v>8.44</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>12.91</v>
+        <v>14.19</v>
       </c>
       <c r="M13" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N13" t="n">
         <v>3.46</v>
@@ -14692,7 +14693,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>10.42</v>
+        <v>10.23</v>
       </c>
       <c r="I2" t="n">
         <v>13.33</v>
@@ -14707,32 +14708,32 @@
         <v>12.75</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.91</v>
+        <v>-3.11</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[-4.95, -0.42]</t>
+          <t>[-5.14, -0.61]</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[-2.38, 2.32]</t>
+          <t>[-2.40, 2.12]</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>31</v>
+        <v>40.5</v>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>40.5</v>
       </c>
       <c r="T2" t="n">
-        <v>10.42</v>
+        <v>10.23</v>
       </c>
       <c r="U2" t="n">
         <v>13.33</v>
@@ -14763,7 +14764,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="I3" t="n">
         <v>13.33</v>
@@ -14778,19 +14779,19 @@
         <v>12.75</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.73</v>
+        <v>-4.75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[-6.75, -2.58]</t>
+          <t>[-6.76, -2.66]</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-1.39</v>
+        <v>-1.42</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[-3.91, 0.16]</t>
+          <t>[-3.94, 0.18]</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -14803,7 +14804,7 @@
         <v>93.5</v>
       </c>
       <c r="T3" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="U3" t="n">
         <v>13.33</v>
@@ -14834,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="I4" t="n">
         <v>10.51</v>
@@ -14849,32 +14850,32 @@
         <v>12.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8</v>
+        <v>-1.03</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[-2.62, 0.92]</t>
+          <t>[-2.89, 0.65]</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[-0.41, 2.63]</t>
+          <t>[-0.54, 2.27]</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>78</v>
+        <v>84.5</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="S4" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="T4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="U4" t="n">
         <v>10.51</v>
@@ -14905,7 +14906,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
         <v>10.51</v>
@@ -14920,32 +14921,32 @@
         <v>12.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.68</v>
+        <v>-2.71</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[-4.46, -0.90]</t>
+          <t>[-4.49, -1.02]</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-0.78</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[-2.14, 0.41]</t>
+          <t>[-2.12, 0.39]</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>88.5</v>
+        <v>89</v>
       </c>
       <c r="S5" t="n">
-        <v>88.5</v>
+        <v>89</v>
       </c>
       <c r="T5" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="U5" t="n">
         <v>10.51</v>
@@ -14976,7 +14977,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9.43</v>
+        <v>9.17</v>
       </c>
       <c r="I6" t="n">
         <v>8.84</v>
@@ -14991,32 +14992,32 @@
         <v>12.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[-1.07, 2.00]</t>
+          <t>[-1.29, 1.71]</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[0.25, 2.49]</t>
+          <t>[0.07, 2.19]</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>31.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>9.43</v>
+        <v>9.17</v>
       </c>
       <c r="U6" t="n">
         <v>8.84</v>
@@ -15047,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
       <c r="I7" t="n">
         <v>8.84</v>
@@ -15062,32 +15063,32 @@
         <v>12.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.35</v>
+        <v>-1.38</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[-3.02, 0.01]</t>
+          <t>[-2.98, -0.04]</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[-1.50, 0.25]</t>
+          <t>[-1.55, 0.19]</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="S7" t="n">
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="T7" t="n">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
       <c r="U7" t="n">
         <v>8.84</v>
@@ -15118,7 +15119,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9.119999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="I8" t="n">
         <v>7.26</v>
@@ -15133,32 +15134,32 @@
         <v>11.88</v>
       </c>
       <c r="M8" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[0.62, 2.81]</t>
+          <t>[0.31, 2.57]</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[0.71, 2.31]</t>
+          <t>[0.36, 2.08]</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>9.119999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="U8" t="n">
         <v>7.26</v>
@@ -15189,7 +15190,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.18</v>
+        <v>7.14</v>
       </c>
       <c r="I9" t="n">
         <v>7.26</v>
@@ -15204,32 +15205,32 @@
         <v>11.88</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[-1.40, 0.82]</t>
+          <t>[-1.43, 0.79]</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-0.5</v>
+        <v>-0.53</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[-1.34, 0.26]</t>
+          <t>[-1.38, 0.23]</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>49.5</v>
+        <v>52</v>
       </c>
       <c r="R9" t="n">
-        <v>90.5</v>
+        <v>92.5</v>
       </c>
       <c r="S9" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="T9" t="n">
-        <v>7.18</v>
+        <v>7.14</v>
       </c>
       <c r="U9" t="n">
         <v>7.26</v>
@@ -15260,7 +15261,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="I10" t="n">
         <v>5.42</v>
@@ -15275,19 +15276,19 @@
         <v>11.78</v>
       </c>
       <c r="M10" t="n">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[2.30, 4.25]</t>
+          <t>[1.94, 3.94]</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[0.92, 2.10]</t>
+          <t>[0.61, 1.86]</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -15300,7 +15301,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="U10" t="n">
         <v>5.42</v>
@@ -15331,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="I11" t="n">
         <v>5.42</v>
@@ -15346,19 +15347,19 @@
         <v>11.78</v>
       </c>
       <c r="M11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[0.45, 2.29]</t>
+          <t>[0.44, 2.26]</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[-0.96, 0.13]</t>
+          <t>[-1.00, 0.10]</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -15371,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="U11" t="n">
         <v>5.42</v>
@@ -15430,19 +15431,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.91</v>
+        <v>13.8</v>
       </c>
       <c r="C2" t="n">
-        <v>14.28</v>
+        <v>13.23</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5</v>
+        <v>14.41</v>
       </c>
       <c r="E2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="F2" t="n">
-        <v>0.318</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="3">
@@ -15452,19 +15453,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.11</v>
+        <v>13.71</v>
       </c>
       <c r="C3" t="n">
-        <v>14.49</v>
+        <v>13.17</v>
       </c>
       <c r="D3" t="n">
-        <v>15.71</v>
+        <v>14.34</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="F3" t="n">
-        <v>0.32</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="4">
@@ -15474,19 +15475,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.11</v>
+        <v>13.69</v>
       </c>
       <c r="C4" t="n">
-        <v>14.52</v>
+        <v>13.18</v>
       </c>
       <c r="D4" t="n">
-        <v>15.65</v>
+        <v>14.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="F4" t="n">
-        <v>0.286</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="5">
@@ -15497,7 +15498,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.91/15.33/15.08</t>
+          <t>13.80/13.66/13.67</t>
         </is>
       </c>
     </row>
@@ -15729,22 +15730,22 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I2" t="n">
-        <v>15.1</v>
+        <v>14.73</v>
       </c>
       <c r="J2" t="n">
-        <v>10.43</v>
+        <v>10.24</v>
       </c>
       <c r="K2" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="L2" t="n">
-        <v>9.6</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>10.55</v>
+        <v>10.46</v>
       </c>
       <c r="N2" t="n">
         <v>13.39</v>
@@ -15762,71 +15763,71 @@
         <v>12.73</v>
       </c>
       <c r="S2" t="n">
-        <v>0.654</v>
+        <v>0.627</v>
       </c>
       <c r="T2" t="n">
         <v>0.592</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[-1.88, 2.41]</t>
+          <t>[-2.17, 2.22]</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>35.5</v>
+        <v>42.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.36</v>
+        <v>-1.48</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[-3.49, 1.14]</t>
+          <t>[-3.59, 1.03]</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.45</v>
+        <v>-0.76</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[-3.16, 1.96]</t>
+          <t>[-3.25, 1.53]</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>66</v>
+        <v>73.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.1</v>
+        <v>-1.42</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[-3.79, 1.61]</t>
+          <t>[-3.96, 1.07]</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.16</v>
+        <v>-0.24</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[-1.34, 0.90]</t>
+          <t>[-1.35, 0.78]</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>61.5</v>
+        <v>70.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40.9</v>
+        <v>38.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="3">
@@ -15856,22 +15857,22 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>15.89</v>
+        <v>15.14</v>
       </c>
       <c r="I3" t="n">
-        <v>9.68</v>
+        <v>9.27</v>
       </c>
       <c r="J3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>8.119999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>8.51</v>
+        <v>8.48</v>
       </c>
       <c r="M3" t="n">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="N3" t="n">
         <v>13.39</v>
@@ -15889,71 +15890,71 @@
         <v>12.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0.63</v>
+        <v>0.616</v>
       </c>
       <c r="T3" t="n">
         <v>0.592</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.41</v>
+        <v>-1.44</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[-3.70, 0.25]</t>
+          <t>[-3.71, 0.22]</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="X3" t="n">
         <v>-1.93</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[-4.23, 0.33]</t>
+          <t>[-4.21, 0.35]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>96</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.54</v>
+        <v>-1.57</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[-4.13, 0.49]</t>
+          <t>[-4.19, 0.68]</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>90.5</v>
+        <v>93.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2.19</v>
+        <v>-2.22</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[-4.47, 0.11]</t>
+          <t>[-4.59, 0.10]</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.6</v>
+        <v>-0.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[-1.59, 0.20]</t>
+          <t>[-1.60, 0.11]</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>91</v>
+        <v>93.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>37.4</v>
+        <v>35.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="4">
@@ -15983,22 +15984,22 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I4" t="n">
-        <v>14.89</v>
+        <v>14.52</v>
       </c>
       <c r="J4" t="n">
-        <v>9.76</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>7.46</v>
+        <v>7.32</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="M4" t="n">
-        <v>8.029999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="N4" t="n">
         <v>10.51</v>
@@ -16016,71 +16017,71 @@
         <v>12.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0.583</v>
+        <v>0.556</v>
       </c>
       <c r="T4" t="n">
         <v>0.521</v>
       </c>
       <c r="U4" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[-0.47, 2.26]</t>
+          <t>[-0.66, 2.03]</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.23</v>
+        <v>-1.38</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[-2.91, 0.36]</t>
+          <t>[-3.02, 0.18]</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[-2.51, 1.11]</t>
+          <t>[-2.65, 0.95]</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>78.5</v>
+        <v>86.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.08</v>
+        <v>-0.38</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[-1.90, 1.70]</t>
+          <t>[-2.12, 1.54]</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>52</v>
+        <v>66.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[-1.21, 0.92]</t>
+          <t>[-1.29, 0.89]</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>50.5</v>
+        <v>62.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>52.6</v>
+        <v>49.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="5">
@@ -16110,22 +16111,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15.89</v>
+        <v>15.14</v>
       </c>
       <c r="I5" t="n">
-        <v>9.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="K5" t="n">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="L5" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="M5" t="n">
-        <v>7.55</v>
+        <v>7.53</v>
       </c>
       <c r="N5" t="n">
         <v>10.51</v>
@@ -16143,71 +16144,71 @@
         <v>12.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0.545</v>
+        <v>0.537</v>
       </c>
       <c r="T5" t="n">
         <v>0.521</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.84</v>
+        <v>-0.86</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>[-2.30, 0.42]</t>
+          <t>[-2.19, 0.36]</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.88</v>
+        <v>-1.86</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[-3.69, -0.29]</t>
+          <t>[-3.67, -0.28]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>99</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.36</v>
+        <v>-1.35</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[-3.01, 0.16]</t>
+          <t>[-2.89, 0.03]</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[-2.19, 0.91]</t>
+          <t>[-2.22, 0.76]</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.53</v>
+        <v>-0.54</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[-1.50, 0.14]</t>
+          <t>[-1.57, 0.11]</t>
         </is>
       </c>
       <c r="AI5" t="n">
         <v>93</v>
       </c>
       <c r="AJ5" t="n">
-        <v>41.8</v>
+        <v>39.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="6">
@@ -16237,22 +16238,22 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>18.89</v>
+        <v>18.35</v>
       </c>
       <c r="I6" t="n">
-        <v>14.79</v>
+        <v>14.41</v>
       </c>
       <c r="J6" t="n">
-        <v>9.35</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="L6" t="n">
-        <v>7.09</v>
+        <v>6.77</v>
       </c>
       <c r="M6" t="n">
-        <v>6.86</v>
+        <v>6.74</v>
       </c>
       <c r="N6" t="n">
         <v>8.800000000000001</v>
@@ -16270,71 +16271,71 @@
         <v>11.98</v>
       </c>
       <c r="S6" t="n">
-        <v>0.569</v>
+        <v>0.537</v>
       </c>
       <c r="T6" t="n">
         <v>0.502</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>[0.00, 2.29]</t>
+          <t>[-0.23, 2.11]</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.36</v>
+        <v>-1.51</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[-2.58, 0.27]</t>
+          <t>[-2.74, 0.09]</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.99</v>
+        <v>-1.31</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[-2.25, 0.61]</t>
+          <t>[-2.51, 0.48]</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>87</v>
+        <v>95.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[-1.19, 1.75]</t>
+          <t>[-1.42, 1.48]</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[-0.94, 0.94]</t>
+          <t>[-1.07, 0.80]</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>63.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>57.6</v>
+        <v>54</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.6</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7">
@@ -16364,22 +16365,22 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>15.89</v>
+        <v>15.15</v>
       </c>
       <c r="I7" t="n">
-        <v>9.09</v>
+        <v>8.68</v>
       </c>
       <c r="J7" t="n">
-        <v>7.44</v>
+        <v>7.41</v>
       </c>
       <c r="K7" t="n">
-        <v>6.02</v>
+        <v>6.04</v>
       </c>
       <c r="L7" t="n">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
       <c r="N7" t="n">
         <v>8.800000000000001</v>
@@ -16397,71 +16398,71 @@
         <v>11.98</v>
       </c>
       <c r="S7" t="n">
-        <v>0.523</v>
+        <v>0.51</v>
       </c>
       <c r="T7" t="n">
         <v>0.502</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.64</v>
+        <v>-0.67</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>[-1.60, 0.28]</t>
+          <t>[-1.66, 0.26]</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.06</v>
+        <v>-2.04</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[-3.35, -0.70]</t>
+          <t>[-3.34, -0.66]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>100</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.59</v>
+        <v>-1.58</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[-2.79, -0.29]</t>
+          <t>[-2.78, -0.34]</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>99</v>
+        <v>98.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[-1.70, 0.90]</t>
+          <t>[-1.65, 1.01]</t>
         </is>
       </c>
       <c r="AF7" t="n">
         <v>69.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[-1.14, 0.14]</t>
+          <t>[-1.29, 0.01]</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>94.5</v>
+        <v>96.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>48.6</v>
+        <v>46.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="8">
@@ -16491,22 +16492,22 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I8" t="n">
-        <v>14.7</v>
+        <v>14.33</v>
       </c>
       <c r="J8" t="n">
-        <v>9.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>6.19</v>
+        <v>6.02</v>
       </c>
       <c r="L8" t="n">
-        <v>6.37</v>
+        <v>6.11</v>
       </c>
       <c r="M8" t="n">
-        <v>5.84</v>
+        <v>5.72</v>
       </c>
       <c r="N8" t="n">
         <v>7.28</v>
@@ -16524,71 +16525,71 @@
         <v>11.88</v>
       </c>
       <c r="S8" t="n">
-        <v>0.589</v>
+        <v>0.55</v>
       </c>
       <c r="T8" t="n">
         <v>0.503</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>[0.77, 3.08]</t>
+          <t>[0.59, 2.81]</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.99</v>
+        <v>-1.16</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[-2.08, 0.15]</t>
+          <t>[-2.26, -0.04]</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>96.5</v>
+        <v>98</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[-1.84, 0.40]</t>
+          <t>[-2.06, 0.18]</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>90.5</v>
+        <v>96</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[-0.72, 1.49]</t>
+          <t>[-0.91, 1.23]</t>
         </is>
       </c>
       <c r="AF8" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[-0.98, 0.48]</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="AK8" t="n">
         <v>20</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[-0.84, 0.61]</t>
-        </is>
-      </c>
-      <c r="AI8" t="n">
-        <v>58</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>18.8</v>
       </c>
     </row>
     <row r="9">
@@ -16618,22 +16619,22 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>15.89</v>
+        <v>15.15</v>
       </c>
       <c r="I9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="K9" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="L9" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="N9" t="n">
         <v>7.28</v>
@@ -16651,39 +16652,39 @@
         <v>11.88</v>
       </c>
       <c r="S9" t="n">
-        <v>0.517</v>
+        <v>0.506</v>
       </c>
       <c r="T9" t="n">
         <v>0.503</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>[-1.05, 1.10]</t>
+          <t>[-1.11, 1.06]</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>51</v>
+        <v>53.5</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.71</v>
+        <v>-1.69</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[-2.80, -0.53]</t>
+          <t>[-2.81, -0.52]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.34</v>
+        <v>-1.35</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[-2.52, -0.14]</t>
+          <t>[-2.54, -0.16]</t>
         </is>
       </c>
       <c r="AC9" t="n">
@@ -16694,28 +16695,28 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[-1.15, 1.08]</t>
+          <t>[-1.31, 1.08]</t>
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[-0.97, 0.17]</t>
+          <t>[-1.01, 0.17]</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>86.5</v>
+        <v>89</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55.5</v>
+        <v>53.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="10">
@@ -16745,22 +16746,22 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>18.88</v>
+        <v>18.33</v>
       </c>
       <c r="I10" t="n">
-        <v>14.63</v>
+        <v>14.25</v>
       </c>
       <c r="J10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="K10" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="L10" t="n">
-        <v>5.74</v>
+        <v>5.48</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="N10" t="n">
         <v>5.48</v>
@@ -16778,71 +16779,71 @@
         <v>11.78</v>
       </c>
       <c r="S10" t="n">
-        <v>0.625</v>
+        <v>0.576</v>
       </c>
       <c r="T10" t="n">
         <v>0.555</v>
       </c>
       <c r="U10" t="n">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>[2.45, 4.22]</t>
+          <t>[2.16, 3.89]</t>
         </is>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[-0.69, 1.03]</t>
+          <t>[-0.81, 0.83]</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>[-0.52, 1.07]</t>
+          <t>[-0.82, 0.83]</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>26</v>
+        <v>49.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9</v>
+        <v>0.64</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[0.07, 1.82]</t>
+          <t>[-0.20, 1.50]</t>
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.14</v>
+        <v>-0.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[-0.76, 0.39]</t>
+          <t>[-0.88, 0.30]</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>63.5</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="11">
@@ -16872,22 +16873,22 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>15.9</v>
+        <v>15.16</v>
       </c>
       <c r="I11" t="n">
-        <v>8.84</v>
+        <v>8.43</v>
       </c>
       <c r="J11" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="K11" t="n">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
       <c r="L11" t="n">
-        <v>5.11</v>
+        <v>5.09</v>
       </c>
       <c r="M11" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="N11" t="n">
         <v>5.48</v>
@@ -16905,57 +16906,57 @@
         <v>11.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="T11" t="n">
         <v>0.555</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>[0.61, 2.17]</t>
+          <t>[0.55, 2.11]</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[-1.39, 0.33]</t>
+          <t>[-1.40, 0.34]</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>90.5</v>
+        <v>89</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>[-1.19, 0.46]</t>
+          <t>[-1.25, 0.51]</t>
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[-0.43, 1.32]</t>
+          <t>[-0.55, 1.38]</t>
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>29.5</v>
+        <v>33.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -16963,13 +16964,13 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>64.40000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="12">
@@ -16999,22 +17000,22 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>18.88</v>
+        <v>18.33</v>
       </c>
       <c r="I12" t="n">
-        <v>14.6</v>
+        <v>14.22</v>
       </c>
       <c r="J12" t="n">
-        <v>8.630000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="K12" t="n">
-        <v>5.32</v>
+        <v>5.13</v>
       </c>
       <c r="L12" t="n">
-        <v>5.34</v>
+        <v>5.08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="N12" t="n">
         <v>4.18</v>
@@ -17032,71 +17033,71 @@
         <v>11.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0.694</v>
+        <v>0.638</v>
       </c>
       <c r="T12" t="n">
         <v>0.642</v>
       </c>
       <c r="U12" t="n">
-        <v>4.46</v>
+        <v>4.15</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>[3.72, 5.24]</t>
+          <t>[3.37, 4.95]</t>
         </is>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[0.48, 1.78]</t>
+          <t>[0.29, 1.61]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>[0.42, 1.77]</t>
+          <t>[0.15, 1.52]</t>
         </is>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[0.72, 2.16]</t>
+          <t>[0.38, 1.89]</t>
         </is>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[-0.75, 0.30]</t>
+          <t>[-0.79, 0.32]</t>
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="n">
-        <v>76.7</v>
+        <v>66.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -17126,19 +17127,19 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>15.92</v>
+        <v>15.18</v>
       </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="K13" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="L13" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="M13" t="n">
         <v>3.85</v>
@@ -17159,50 +17160,50 @@
         <v>11.75</v>
       </c>
       <c r="S13" t="n">
-        <v>0.67</v>
+        <v>0.653</v>
       </c>
       <c r="T13" t="n">
         <v>0.642</v>
       </c>
       <c r="U13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>[1.79, 3.17]</t>
+          <t>[1.76, 3.16]</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[-0.34, 1.00]</t>
+          <t>[-0.32, 1.03]</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>[-0.17, 1.17]</t>
+          <t>[-0.24, 1.01]</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[0.06, 1.38]</t>
+          <t>[0.03, 1.31]</t>
         </is>
       </c>
       <c r="AF13" t="n">
@@ -17213,17 +17214,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[-0.36, 0.20]</t>
+          <t>[-0.38, 0.18]</t>
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>67.5</v>
+        <v>72</v>
       </c>
       <c r="AJ13" t="n">
-        <v>71.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="14">
@@ -17253,22 +17254,22 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I14" t="n">
-        <v>14.6</v>
+        <v>14.22</v>
       </c>
       <c r="J14" t="n">
-        <v>8.59</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>4.93</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="N14" t="n">
         <v>3.63</v>
@@ -17286,71 +17287,71 @@
         <v>11.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0.739</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.97</v>
+        <v>4.65</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>[4.28, 5.67]</t>
+          <t>[3.97, 5.30]</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[0.96, 2.14]</t>
+          <t>[0.78, 1.93]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>[0.97, 2.15]</t>
+          <t>[0.74, 1.86]</t>
         </is>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[1.09, 2.26]</t>
+          <t>[0.79, 2.04]</t>
         </is>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[-0.56, 0.22]</t>
+          <t>[-0.59, 0.18]</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="n">
-        <v>77.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AK14" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="15">
@@ -17380,19 +17381,19 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>15.95</v>
+        <v>15.2</v>
       </c>
       <c r="I15" t="n">
-        <v>8.81</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>6.69</v>
+        <v>6.65</v>
       </c>
       <c r="K15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L15" t="n">
         <v>4.43</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.47</v>
       </c>
       <c r="M15" t="n">
         <v>3.46</v>
@@ -17413,71 +17414,71 @@
         <v>11.75</v>
       </c>
       <c r="S15" t="n">
-        <v>0.742</v>
+        <v>0.724</v>
       </c>
       <c r="T15" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>[2.33, 3.66]</t>
+          <t>[2.31, 3.64]</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[0.20, 1.30]</t>
+          <t>[0.26, 1.31]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>0.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>[0.29, 1.43]</t>
+          <t>[0.26, 1.38]</t>
         </is>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[0.40, 1.45]</t>
+          <t>[0.34, 1.40]</t>
         </is>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[-0.27, 0.22]</t>
+          <t>[-0.29, 0.20]</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="AK15" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="16">
@@ -17507,22 +17508,22 @@
         <v>23.5</v>
       </c>
       <c r="H16" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I16" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="J16" t="n">
-        <v>10.87</v>
+        <v>10.67</v>
       </c>
       <c r="K16" t="n">
-        <v>9.140000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="L16" t="n">
-        <v>9.98</v>
+        <v>9.67</v>
       </c>
       <c r="M16" t="n">
-        <v>11.15</v>
+        <v>11.08</v>
       </c>
       <c r="N16" t="n">
         <v>13.21</v>
@@ -17540,71 +17541,71 @@
         <v>12.99</v>
       </c>
       <c r="S16" t="n">
-        <v>0.676</v>
+        <v>0.642</v>
       </c>
       <c r="T16" t="n">
         <v>0.599</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>[-2.14, 3.50]</t>
+          <t>[-2.41, 3.28]</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.93</v>
+        <v>-1.05</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[-3.80, 2.04]</t>
+          <t>[-3.99, 1.98]</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>74.5</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>[-3.52, 3.46]</t>
+          <t>[-3.76, 3.17]</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.07</v>
+        <v>-1.37</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[-4.22, 1.86]</t>
+          <t>[-4.64, 1.58]</t>
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>79.5</v>
+        <v>86.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[-0.97, 1.71]</t>
+          <t>[-1.20, 1.59]</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AJ16" t="n">
-        <v>44.1</v>
+        <v>39.7</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="17">
@@ -17634,22 +17635,22 @@
         <v>23.5</v>
       </c>
       <c r="H17" t="n">
-        <v>15.88</v>
+        <v>15.14</v>
       </c>
       <c r="I17" t="n">
-        <v>10.09</v>
+        <v>9.67</v>
       </c>
       <c r="J17" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K17" t="n">
         <v>8.56</v>
       </c>
       <c r="L17" t="n">
-        <v>8.98</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>10.67</v>
+        <v>10.65</v>
       </c>
       <c r="N17" t="n">
         <v>13.21</v>
@@ -17667,71 +17668,71 @@
         <v>12.99</v>
       </c>
       <c r="S17" t="n">
-        <v>0.639</v>
+        <v>0.623</v>
       </c>
       <c r="T17" t="n">
         <v>0.599</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.93</v>
+        <v>-0.97</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>[-3.45, 1.59]</t>
+          <t>[-3.52, 1.49]</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[-4.34, 1.68]</t>
+          <t>[-4.35, 1.67]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>84.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>[-4.42, 2.11]</t>
+          <t>[-4.40, 2.18]</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>-2.06</v>
+        <v>-2.07</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[-4.72, 0.55]</t>
+          <t>[-4.60, 0.55]</t>
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[-1.56, 0.89]</t>
+          <t>[-1.57, 0.81]</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="n">
-        <v>39.9</v>
+        <v>37.8</v>
       </c>
       <c r="AK17" t="n">
-        <v>25.8</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="18">
@@ -17761,22 +17762,22 @@
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>18.89</v>
+        <v>18.35</v>
       </c>
       <c r="I18" t="n">
-        <v>14.96</v>
+        <v>14.57</v>
       </c>
       <c r="J18" t="n">
-        <v>9.93</v>
+        <v>9.73</v>
       </c>
       <c r="K18" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="L18" t="n">
-        <v>8.289999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="M18" t="n">
-        <v>8.380000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="N18" t="n">
         <v>10.45</v>
@@ -17794,71 +17795,71 @@
         <v>12.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0.589</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>0.528</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>[-0.62, 2.74]</t>
+          <t>[-0.70, 2.61]</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.15</v>
+        <v>-1.28</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[-2.89, 0.86]</t>
+          <t>[-2.93, 0.76]</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>89.5</v>
+        <v>92.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.53</v>
+        <v>-0.85</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>[-2.57, 1.70]</t>
+          <t>[-2.87, 1.60]</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>69.5</v>
+        <v>77.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[-2.03, 2.30]</t>
+          <t>[-2.25, 2.15]</t>
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>51.5</v>
+        <v>62.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[-1.05, 1.05]</t>
+          <t>[-1.05, 0.94]</t>
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>49.5</v>
+        <v>58</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50.4</v>
+        <v>46.6</v>
       </c>
       <c r="AK18" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="19">
@@ -17888,22 +17889,22 @@
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>15.89</v>
+        <v>15.14</v>
       </c>
       <c r="I19" t="n">
-        <v>9.49</v>
+        <v>9.08</v>
       </c>
       <c r="J19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="K19" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="L19" t="n">
-        <v>7.49</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="N19" t="n">
         <v>10.45</v>
@@ -17921,71 +17922,71 @@
         <v>12.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0.547</v>
+        <v>0.537</v>
       </c>
       <c r="T19" t="n">
         <v>0.528</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.71</v>
+        <v>-0.74</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>[-2.30, 1.04]</t>
+          <t>[-2.25, 0.94]</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[-3.55, 0.30]</t>
+          <t>[-3.53, 0.29]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>95.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>[-3.12, 0.66]</t>
+          <t>[-3.27, 0.66]</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>91.5</v>
+        <v>90</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[-2.65, 0.94]</t>
+          <t>[-2.74, 0.99]</t>
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[-1.21, 0.39]</t>
+          <t>[-1.19, 0.24]</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>80.5</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -18015,22 +18016,22 @@
         <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I20" t="n">
-        <v>14.86</v>
+        <v>14.48</v>
       </c>
       <c r="J20" t="n">
-        <v>9.57</v>
+        <v>9.35</v>
       </c>
       <c r="K20" t="n">
-        <v>7.06</v>
+        <v>6.92</v>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>7.12</v>
       </c>
       <c r="M20" t="n">
-        <v>7.22</v>
+        <v>7.09</v>
       </c>
       <c r="N20" t="n">
         <v>9.01</v>
@@ -18048,71 +18049,71 @@
         <v>12.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0.572</v>
+        <v>0.54</v>
       </c>
       <c r="T20" t="n">
         <v>0.499</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>[0.11, 2.58]</t>
+          <t>[-0.16, 2.31]</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.14</v>
+        <v>-1.28</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[-2.46, 0.58]</t>
+          <t>[-2.54, 0.47]</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>93.5</v>
+        <v>95</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.8</v>
+        <v>-1.08</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>[-2.17, 0.94]</t>
+          <t>[-2.38, 0.67]</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[-1.12, 1.97]</t>
+          <t>[-1.43, 1.55]</t>
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>41</v>
+        <v>55.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[-0.79, 0.95]</t>
+          <t>[-0.92, 0.77]</t>
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>56.6</v>
+        <v>52.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.9</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="21">
@@ -18142,22 +18143,22 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>15.89</v>
+        <v>15.14</v>
       </c>
       <c r="I21" t="n">
-        <v>9.289999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="K21" t="n">
-        <v>6.4</v>
+        <v>6.41</v>
       </c>
       <c r="L21" t="n">
         <v>6.87</v>
       </c>
       <c r="M21" t="n">
-        <v>6.83</v>
+        <v>6.81</v>
       </c>
       <c r="N21" t="n">
         <v>9.01</v>
@@ -18175,71 +18176,71 @@
         <v>12.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0.515</v>
+        <v>0.503</v>
       </c>
       <c r="T21" t="n">
         <v>0.499</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>[-1.57, 0.80]</t>
+          <t>[-1.57, 0.67]</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.79</v>
+        <v>-1.78</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[-2.99, -0.10]</t>
+          <t>[-2.98, -0.09]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>98</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>[-2.62, 0.23]</t>
+          <t>[-2.66, 0.11]</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[-1.74, 1.09]</t>
+          <t>[-1.74, 1.20]</t>
         </is>
       </c>
       <c r="AF21" t="n">
         <v>69</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[-1.07, 0.29]</t>
+          <t>[-1.07, 0.25]</t>
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>83.5</v>
+        <v>85.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>47.4</v>
+        <v>45.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="22">
@@ -18269,22 +18270,22 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I22" t="n">
-        <v>14.76</v>
+        <v>14.37</v>
       </c>
       <c r="J22" t="n">
-        <v>9.210000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>6.39</v>
+        <v>6.23</v>
       </c>
       <c r="L22" t="n">
-        <v>6.56</v>
+        <v>6.28</v>
       </c>
       <c r="M22" t="n">
-        <v>6.03</v>
+        <v>5.9</v>
       </c>
       <c r="N22" t="n">
         <v>7.36</v>
@@ -18302,71 +18303,71 @@
         <v>11.96</v>
       </c>
       <c r="S22" t="n">
-        <v>0.573</v>
+        <v>0.531</v>
       </c>
       <c r="T22" t="n">
         <v>0.489</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>[0.93, 3.13]</t>
+          <t>[0.70, 2.87]</t>
         </is>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.83</v>
+        <v>-1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[-1.91, 0.27]</t>
+          <t>[-2.02, 0.03]</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.66</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>[-1.66, 0.50]</t>
+          <t>[-2.05, 0.16]</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[-0.48, 1.61]</t>
+          <t>[-0.73, 1.39]</t>
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>17.5</v>
+        <v>31.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[-0.71, 0.84]</t>
+          <t>[-0.77, 0.62]</t>
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>62.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>61.9</v>
+        <v>56.4</v>
       </c>
       <c r="AK22" t="n">
-        <v>19.9</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="23">
@@ -18396,22 +18397,22 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>15.89</v>
+        <v>15.15</v>
       </c>
       <c r="I23" t="n">
-        <v>9.08</v>
+        <v>8.66</v>
       </c>
       <c r="J23" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="K23" t="n">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="L23" t="n">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="M23" t="n">
-        <v>5.77</v>
+        <v>5.74</v>
       </c>
       <c r="N23" t="n">
         <v>7.36</v>
@@ -18429,39 +18430,39 @@
         <v>11.96</v>
       </c>
       <c r="S23" t="n">
-        <v>0.508</v>
+        <v>0.496</v>
       </c>
       <c r="T23" t="n">
         <v>0.489</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>[-0.93, 1.23]</t>
+          <t>[-0.97, 1.14]</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.55</v>
+        <v>-1.53</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[-2.49, -0.59]</t>
+          <t>[-2.48, -0.56]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>99.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1.18</v>
+        <v>-1.19</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>[-2.25, -0.10]</t>
+          <t>[-2.28, -0.05]</t>
         </is>
       </c>
       <c r="AC23" t="n">
@@ -18472,28 +18473,28 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[-0.93, 1.16]</t>
+          <t>[-1.03, 1.21]</t>
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[-0.85, 0.31]</t>
+          <t>[-0.88, 0.26]</t>
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>83.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>54.2</v>
+        <v>51.6</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="24">
@@ -18523,22 +18524,22 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="I24" t="n">
-        <v>14.66</v>
+        <v>14.28</v>
       </c>
       <c r="J24" t="n">
-        <v>8.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7</v>
+        <v>5.52</v>
       </c>
       <c r="L24" t="n">
-        <v>5.77</v>
+        <v>5.52</v>
       </c>
       <c r="M24" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="N24" t="n">
         <v>5.47</v>
@@ -18556,71 +18557,71 @@
         <v>11.82</v>
       </c>
       <c r="S24" t="n">
-        <v>0.616</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>0.544</v>
       </c>
       <c r="U24" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>[2.43, 4.21]</t>
+          <t>[2.14, 3.94]</t>
         </is>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[-0.72, 1.01]</t>
+          <t>[-0.84, 0.79]</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>29.5</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>[-0.57, 1.07]</t>
+          <t>[-0.77, 0.84]</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>23.5</v>
+        <v>44.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[0.11, 1.71]</t>
+          <t>[-0.16, 1.42]</t>
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.13</v>
+        <v>-0.21</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[-0.68, 0.42]</t>
+          <t>[-0.69, 0.35]</t>
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>64</v>
+        <v>75.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>69.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="25">
@@ -18650,22 +18651,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>15.9</v>
+        <v>15.16</v>
       </c>
       <c r="I25" t="n">
-        <v>8.91</v>
+        <v>8.49</v>
       </c>
       <c r="J25" t="n">
-        <v>6.93</v>
+        <v>6.89</v>
       </c>
       <c r="K25" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="L25" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="M25" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="N25" t="n">
         <v>5.47</v>
@@ -18683,71 +18684,71 @@
         <v>11.82</v>
       </c>
       <c r="S25" t="n">
-        <v>0.556</v>
+        <v>0.541</v>
       </c>
       <c r="T25" t="n">
         <v>0.544</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>[0.57, 2.30]</t>
+          <t>[0.53, 2.27]</t>
         </is>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[-1.48, 0.23]</t>
+          <t>[-1.47, 0.29]</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>88.5</v>
+        <v>87</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>[-1.25, 0.78]</t>
+          <t>[-1.28, 0.73]</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[-0.55, 1.14]</t>
+          <t>[-0.55, 1.23]</t>
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>27</v>
+        <v>29.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[-0.62, 0.22]</t>
+          <t>[-0.65, 0.20]</t>
         </is>
       </c>
       <c r="AI25" t="n">
-        <v>71.5</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
-        <v>65.3</v>
+        <v>61.2</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="26">
@@ -18777,22 +18778,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>18.9</v>
+        <v>18.35</v>
       </c>
       <c r="I26" t="n">
-        <v>14.63</v>
+        <v>14.25</v>
       </c>
       <c r="J26" t="n">
-        <v>8.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>5.35</v>
+        <v>5.16</v>
       </c>
       <c r="L26" t="n">
-        <v>5.38</v>
+        <v>5.12</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
         <v>4.18</v>
@@ -18810,71 +18811,71 @@
         <v>11.77</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="T26" t="n">
         <v>0.629</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>[3.77, 5.15]</t>
+          <t>[3.50, 4.79]</t>
         </is>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[0.54, 1.86]</t>
+          <t>[0.37, 1.64]</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>[0.57, 1.86]</t>
+          <t>[0.30, 1.55]</t>
         </is>
       </c>
       <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[0.47, 1.88]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[0.69, 2.13]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[-0.73, 0.30]</t>
+          <t>[-0.76, 0.30]</t>
         </is>
       </c>
       <c r="AI26" t="n">
-        <v>77</v>
+        <v>76.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -18904,19 +18905,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>15.92</v>
+        <v>15.18</v>
       </c>
       <c r="I27" t="n">
-        <v>8.85</v>
+        <v>8.43</v>
       </c>
       <c r="J27" t="n">
-        <v>6.77</v>
+        <v>6.73</v>
       </c>
       <c r="K27" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="L27" t="n">
-        <v>4.68</v>
+        <v>4.64</v>
       </c>
       <c r="M27" t="n">
         <v>3.91</v>
@@ -18937,71 +18938,71 @@
         <v>11.77</v>
       </c>
       <c r="S27" t="n">
-        <v>0.658</v>
+        <v>0.637</v>
       </c>
       <c r="T27" t="n">
         <v>0.629</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>[1.87, 3.29]</t>
+          <t>[1.87, 3.28]</t>
         </is>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[-0.26, 1.15]</t>
+          <t>[-0.23, 1.15]</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>[-0.18, 1.13]</t>
+          <t>[-0.23, 1.10]</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>[0.05, 1.35]</t>
+          <t>[0.01, 1.34]</t>
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
         <v>-0.08</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[-0.44, 0.23]</t>
+          <t>[-0.41, 0.22]</t>
         </is>
       </c>
       <c r="AI27" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>72.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="28">
@@ -19031,22 +19032,22 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>18.91</v>
+        <v>18.36</v>
       </c>
       <c r="I28" t="n">
-        <v>14.63</v>
+        <v>14.25</v>
       </c>
       <c r="J28" t="n">
-        <v>8.66</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>5.28</v>
+        <v>5.09</v>
       </c>
       <c r="L28" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
         <v>3.68</v>
@@ -19064,71 +19065,71 @@
         <v>11.76</v>
       </c>
       <c r="S28" t="n">
-        <v>0.732</v>
+        <v>0.669</v>
       </c>
       <c r="T28" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>4.98</v>
+        <v>4.68</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>[4.36, 5.60]</t>
+          <t>[4.03, 5.27]</t>
         </is>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[0.93, 2.12]</t>
+          <t>[0.76, 1.92]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>[1.04, 2.08]</t>
+          <t>[0.75, 1.86]</t>
         </is>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[0.96, 2.39]</t>
+          <t>[0.75, 2.13]</t>
         </is>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[-0.62, 0.31]</t>
+          <t>[-0.69, 0.32]</t>
         </is>
       </c>
       <c r="AI28" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="n">
-        <v>77.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AK28" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="29">
@@ -19158,19 +19159,19 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>15.94</v>
+        <v>15.19</v>
       </c>
       <c r="I29" t="n">
-        <v>8.859999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="J29" t="n">
-        <v>6.76</v>
+        <v>6.72</v>
       </c>
       <c r="K29" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="L29" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="M29" t="n">
         <v>3.54</v>
@@ -19191,50 +19192,50 @@
         <v>11.76</v>
       </c>
       <c r="S29" t="n">
-        <v>0.735</v>
+        <v>0.714</v>
       </c>
       <c r="T29" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="U29" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>[2.45, 3.77]</t>
+          <t>[2.43, 3.71]</t>
         </is>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[0.28, 1.45]</t>
+          <t>[0.31, 1.47]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>[0.26, 1.44]</t>
+          <t>[0.25, 1.41]</t>
         </is>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[0.44, 1.49]</t>
+          <t>[0.39, 1.43]</t>
         </is>
       </c>
       <c r="AF29" t="n">
@@ -19245,17 +19246,17 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[-0.31, 0.24]</t>
+          <t>[-0.31, 0.25]</t>
         </is>
       </c>
       <c r="AI29" t="n">
-        <v>66</v>
+        <v>67.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>75.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AK29" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
     </row>
   </sheetData>
@@ -19316,16 +19317,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="C2" t="n">
-        <v>10.03</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>6.21</v>
+        <v>5.95</v>
       </c>
       <c r="E2" t="n">
-        <v>6.68</v>
+        <v>6.16</v>
       </c>
       <c r="F2" t="n">
         <v>8.640000000000001</v>
@@ -19341,16 +19342,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.88</v>
+        <v>15.14</v>
       </c>
       <c r="C3" t="n">
-        <v>7.76</v>
+        <v>7.71</v>
       </c>
       <c r="D3" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="E3" t="n">
-        <v>5.77</v>
+        <v>5.68</v>
       </c>
       <c r="F3" t="n">
         <v>8.609999999999999</v>
@@ -20414,13 +20415,13 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9456</v>
+        <v>0.9861</v>
       </c>
       <c r="G34" t="n">
         <v>6.6</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="35">
@@ -20466,13 +20467,13 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9583</v>
+        <v>0.991</v>
       </c>
       <c r="G36" t="n">
         <v>4.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="37">
@@ -20498,13 +20499,13 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9417</v>
+        <v>0.9908</v>
       </c>
       <c r="G37" t="n">
         <v>2.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -20527,16 +20528,16 @@
         <v>0.9419</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9983</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.977</v>
       </c>
       <c r="G38" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H38" t="n">
-        <v>-4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="39">
@@ -20559,16 +20560,16 @@
         <v>0.9539</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9933</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.855</v>
+        <v>0.9499</v>
       </c>
       <c r="G39" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="H39" t="n">
-        <v>-9.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="40">
@@ -20591,16 +20592,16 @@
         <v>0.9778</v>
       </c>
       <c r="E40" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7983</v>
+        <v>0.9371</v>
       </c>
       <c r="G40" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H40" t="n">
-        <v>-17.9</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="41">
@@ -20623,16 +20624,16 @@
         <v>0.9755</v>
       </c>
       <c r="E41" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8905</v>
       </c>
       <c r="G41" t="n">
-        <v>-19.5</v>
+        <v>2.5</v>
       </c>
       <c r="H41" t="n">
-        <v>-28.5</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="42">
@@ -20658,13 +20659,13 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9694</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="G42" t="n">
         <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>7.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="43">
@@ -20710,13 +20711,13 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9913</v>
       </c>
       <c r="G44" t="n">
         <v>11.5</v>
       </c>
       <c r="H44" t="n">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="45">
@@ -20742,13 +20743,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9448</v>
+        <v>0.9908</v>
       </c>
       <c r="G45" t="n">
         <v>10.6</v>
       </c>
       <c r="H45" t="n">
-        <v>5.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -20774,13 +20775,13 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9132</v>
+        <v>0.9829</v>
       </c>
       <c r="G46" t="n">
         <v>11.9</v>
       </c>
       <c r="H46" t="n">
-        <v>3.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="47">
@@ -20806,13 +20807,13 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.88</v>
+        <v>0.9645</v>
       </c>
       <c r="G47" t="n">
         <v>7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="48">
@@ -20835,16 +20836,16 @@
         <v>0.9226</v>
       </c>
       <c r="E48" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7483</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H48" t="n">
-        <v>-17.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="49">
@@ -20867,16 +20868,16 @@
         <v>0.9725</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7883</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6817</v>
+        <v>0.908</v>
       </c>
       <c r="G49" t="n">
-        <v>-18.4</v>
+        <v>2.7</v>
       </c>
       <c r="H49" t="n">
-        <v>-29.1</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="50">
@@ -20899,16 +20900,16 @@
         <v>0.7949000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8724</v>
+        <v>0.8809</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6548</v>
+        <v>0.679</v>
       </c>
       <c r="G50" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="H50" t="n">
-        <v>-14</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="51">
@@ -20951,16 +20952,16 @@
         <v>0.8468</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6667</v>
+        <v>0.6711</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6567</v>
+        <v>0.6756</v>
       </c>
       <c r="G52" t="n">
-        <v>-18</v>
+        <v>-17.6</v>
       </c>
       <c r="H52" t="n">
-        <v>-19</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="53">
@@ -20983,16 +20984,16 @@
         <v>0.8106</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3333</v>
+        <v>0.3467</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6</v>
+        <v>0.6232</v>
       </c>
       <c r="G53" t="n">
-        <v>-47.7</v>
+        <v>-46.4</v>
       </c>
       <c r="H53" t="n">
-        <v>-21.1</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="54">
@@ -21015,16 +21016,16 @@
         <v>0.751</v>
       </c>
       <c r="E54" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1064</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5017</v>
+        <v>0.5402</v>
       </c>
       <c r="G54" t="n">
-        <v>-65.40000000000001</v>
+        <v>-64.5</v>
       </c>
       <c r="H54" t="n">
-        <v>-24.9</v>
+        <v>-21.1</v>
       </c>
     </row>
     <row r="55">
@@ -21047,16 +21048,16 @@
         <v>0.678</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0467</v>
+        <v>0.0767</v>
       </c>
       <c r="F55" t="n">
-        <v>0.46</v>
+        <v>0.493</v>
       </c>
       <c r="G55" t="n">
-        <v>-63.1</v>
+        <v>-60.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-21.8</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="56">
@@ -21079,16 +21080,16 @@
         <v>0.5565</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02</v>
+        <v>0.0446</v>
       </c>
       <c r="F56" t="n">
-        <v>0.415</v>
+        <v>0.4642</v>
       </c>
       <c r="G56" t="n">
-        <v>-53.6</v>
+        <v>-51.2</v>
       </c>
       <c r="H56" t="n">
-        <v>-14.1</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -21111,16 +21112,16 @@
         <v>0.2827</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3333</v>
+        <v>0.4254</v>
       </c>
       <c r="G57" t="n">
-        <v>-27.3</v>
+        <v>-19.4</v>
       </c>
       <c r="H57" t="n">
-        <v>5.1</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="58">
@@ -21143,16 +21144,16 @@
         <v>0.8083</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9306</v>
+        <v>0.9362</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7204</v>
+        <v>0.7402</v>
       </c>
       <c r="G58" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H58" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="59">
@@ -21195,16 +21196,16 @@
         <v>0.8439</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7117</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>0.675</v>
+        <v>0.6906</v>
       </c>
       <c r="G60" t="n">
-        <v>-13.2</v>
+        <v>-12.7</v>
       </c>
       <c r="H60" t="n">
-        <v>-16.9</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="61">
@@ -21227,16 +21228,16 @@
         <v>0.8899</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3267</v>
+        <v>0.3356</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6206</v>
       </c>
       <c r="G61" t="n">
-        <v>-56.3</v>
+        <v>-55.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-29</v>
+        <v>-26.9</v>
       </c>
     </row>
     <row r="62">
@@ -21259,16 +21260,16 @@
         <v>0.7344000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1367</v>
+        <v>0.152</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5359</v>
+        <v>0.5655</v>
       </c>
       <c r="G62" t="n">
-        <v>-59.8</v>
+        <v>-58.2</v>
       </c>
       <c r="H62" t="n">
-        <v>-19.9</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="63">
@@ -21291,16 +21292,16 @@
         <v>0.6471</v>
       </c>
       <c r="E63" t="n">
-        <v>0.04</v>
+        <v>0.0578</v>
       </c>
       <c r="F63" t="n">
-        <v>0.51</v>
+        <v>0.572</v>
       </c>
       <c r="G63" t="n">
-        <v>-60.7</v>
+        <v>-58.9</v>
       </c>
       <c r="H63" t="n">
-        <v>-13.7</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="64">
@@ -21323,16 +21324,16 @@
         <v>0.4982</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0283</v>
+        <v>0.0629</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3783</v>
+        <v>0.4537</v>
       </c>
       <c r="G64" t="n">
-        <v>-47</v>
+        <v>-43.5</v>
       </c>
       <c r="H64" t="n">
-        <v>-12</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="65">
@@ -21355,16 +21356,16 @@
         <v>0.2914</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0033</v>
+        <v>0.08</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3283</v>
+        <v>0.4328</v>
       </c>
       <c r="G65" t="n">
-        <v>-28.8</v>
+        <v>-21.1</v>
       </c>
       <c r="H65" t="n">
-        <v>3.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="66">
@@ -23387,19 +23388,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96</v>
+        <v>20.24</v>
       </c>
       <c r="C2" t="n">
-        <v>18.35</v>
+        <v>17.78</v>
       </c>
       <c r="D2" t="n">
-        <v>14.52</v>
+        <v>13.94</v>
       </c>
       <c r="E2" t="n">
-        <v>12.41</v>
+        <v>12.02</v>
       </c>
       <c r="F2" t="n">
-        <v>12.37</v>
+        <v>11.97</v>
       </c>
       <c r="G2" t="n">
         <v>12.01</v>
@@ -23409,7 +23410,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'global': 0, 'age_lin': 0, 'age_quad': 7, 'age_sex': 0, 'age_sex_x': 1}</t>
+          <t>{'global': 0, 'age_lin': 0, 'age_quad': 6, 'age_sex': 0, 'age_sex_x': 2}</t>
         </is>
       </c>
     </row>
@@ -23420,19 +23421,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.32</v>
+        <v>17.25</v>
       </c>
       <c r="C3" t="n">
-        <v>14.76</v>
+        <v>14.65</v>
       </c>
       <c r="D3" t="n">
-        <v>14.03</v>
+        <v>14.26</v>
       </c>
       <c r="E3" t="n">
-        <v>12.65</v>
+        <v>13.02</v>
       </c>
       <c r="F3" t="n">
-        <v>12.7</v>
+        <v>13.07</v>
       </c>
       <c r="G3" t="n">
         <v>12.01</v>
@@ -23442,7 +23443,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'global': 0, 'age_lin': 0, 'age_quad': 7, 'age_sex': 0, 'age_sex_x': 1}</t>
+          <t>{'global': 0, 'age_lin': 0, 'age_quad': 6, 'age_sex': 1, 'age_sex_x': 1}</t>
         </is>
       </c>
     </row>
@@ -23504,16 +23505,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.29</v>
+        <v>17.63</v>
       </c>
       <c r="C2" t="n">
-        <v>7.89</v>
+        <v>7.55</v>
       </c>
       <c r="D2" t="n">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="E2" t="n">
-        <v>5.06</v>
+        <v>4.8</v>
       </c>
       <c r="F2" t="n">
         <v>3.23</v>
@@ -23526,16 +23527,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.94</v>
+        <v>15.05</v>
       </c>
       <c r="C3" t="n">
         <v>5.65</v>
       </c>
       <c r="D3" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="E3" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="F3" t="n">
         <v>3.23</v>
@@ -23548,13 +23549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.51</v>
+        <v>9.08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.32</v>
+        <v>6.09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.19</v>
+        <v>6.72</v>
       </c>
       <c r="G4" t="n">
         <v>6.21</v>
@@ -23567,13 +23568,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="D5" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="E5" t="n">
-        <v>4.92</v>
+        <v>4.83</v>
       </c>
       <c r="G5" t="n">
         <v>6.18</v>
@@ -23640,19 +23641,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.48</v>
+        <v>10.39</v>
       </c>
       <c r="D2" t="n">
         <v>10.57</v>
       </c>
       <c r="E2" t="n">
-        <v>10.42</v>
+        <v>10.23</v>
       </c>
       <c r="F2" t="n">
         <v>13.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.658</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="3">
@@ -23665,19 +23666,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="D3" t="n">
         <v>10.57</v>
       </c>
       <c r="E3" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="F3" t="n">
         <v>13.33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.624</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="4">
@@ -23690,19 +23691,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.029999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="D4" t="n">
         <v>7.98</v>
       </c>
       <c r="E4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="F4" t="n">
         <v>10.51</v>
       </c>
       <c r="G4" t="n">
-        <v>0.583</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="5">
@@ -23715,19 +23716,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.48</v>
+        <v>7.45</v>
       </c>
       <c r="D5" t="n">
         <v>7.98</v>
       </c>
       <c r="E5" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="F5" t="n">
         <v>10.51</v>
       </c>
       <c r="G5" t="n">
-        <v>0.534</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="6">
@@ -23740,19 +23741,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.87</v>
+        <v>6.72</v>
       </c>
       <c r="D6" t="n">
         <v>6.84</v>
       </c>
       <c r="E6" t="n">
-        <v>9.43</v>
+        <v>9.17</v>
       </c>
       <c r="F6" t="n">
         <v>8.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="7">
@@ -23765,19 +23766,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="D7" t="n">
         <v>6.84</v>
       </c>
       <c r="E7" t="n">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
       <c r="F7" t="n">
         <v>8.84</v>
       </c>
       <c r="G7" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="8">
@@ -23790,19 +23791,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.89</v>
+        <v>5.73</v>
       </c>
       <c r="D8" t="n">
         <v>5.87</v>
       </c>
       <c r="E8" t="n">
-        <v>9.119999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="F8" t="n">
         <v>7.26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.572</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="9">
@@ -23815,19 +23816,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="D9" t="n">
         <v>5.87</v>
       </c>
       <c r="E9" t="n">
-        <v>7.18</v>
+        <v>7.14</v>
       </c>
       <c r="F9" t="n">
         <v>7.26</v>
       </c>
       <c r="G9" t="n">
-        <v>0.493</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="10">
@@ -23840,19 +23841,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
       <c r="D10" t="n">
         <v>4.79</v>
       </c>
       <c r="E10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="F10" t="n">
         <v>5.42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.615</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -23865,19 +23866,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="D11" t="n">
         <v>4.79</v>
       </c>
       <c r="E11" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="F11" t="n">
         <v>5.42</v>
       </c>
       <c r="G11" t="n">
-        <v>0.554</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="12">
@@ -23890,19 +23891,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="D12" t="n">
         <v>3.91</v>
       </c>
       <c r="E12" t="n">
-        <v>8.630000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="F12" t="n">
         <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="13">
@@ -23921,13 +23922,13 @@
         <v>3.91</v>
       </c>
       <c r="E13" t="n">
-        <v>6.72</v>
+        <v>6.68</v>
       </c>
       <c r="F13" t="n">
         <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.657</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="14">
@@ -23940,19 +23941,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="D14" t="n">
         <v>3.52</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>3.59</v>
       </c>
       <c r="G14" t="n">
-        <v>0.728</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="15">
@@ -23971,13 +23972,13 @@
         <v>3.52</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="F15" t="n">
         <v>3.59</v>
       </c>
       <c r="G15" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
     </row>
   </sheetData>
@@ -24196,7 +24197,7 @@
         <v>6.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1919</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="4">
@@ -24209,53 +24210,53 @@
         <v>93.2</v>
       </c>
       <c r="C4" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-1.6, 0.0]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.064</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[-0.6, 0.7]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -24268,50 +24269,50 @@
         <v>69.8</v>
       </c>
       <c r="C5" t="n">
-        <v>28.5</v>
+        <v>33.4</v>
       </c>
       <c r="D5" t="n">
-        <v>27.2</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="n">
-        <v>45.2</v>
+        <v>60.1</v>
       </c>
       <c r="F5" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[14.2, 19.2]</t>
+          <t>[21.6, 31.0]</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0.001</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>32.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[-3.1, 0.4]</t>
+          <t>[-5.1, 1.5]</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
       <c r="P5" t="n">
-        <v>9.300000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0.008</v>
@@ -24432,7 +24433,7 @@
         <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1919</v>
+        <v>0.2279</v>
       </c>
     </row>
     <row r="8">
@@ -24586,7 +24587,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.01</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="3">
@@ -24596,7 +24597,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.37</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="4">
@@ -24606,7 +24607,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.92</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="5">
@@ -24616,7 +24617,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="6">
@@ -24626,7 +24627,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.1</v>
+        <v>16.83</v>
       </c>
     </row>
   </sheetData>
@@ -24894,13 +24895,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.29</v>
+        <v>16.17</v>
       </c>
       <c r="C2" t="n">
-        <v>17.67</v>
+        <v>17.74</v>
       </c>
       <c r="D2" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -24910,13 +24911,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.4</v>
+        <v>16.19</v>
       </c>
       <c r="C3" t="n">
-        <v>17.79</v>
+        <v>17.86</v>
       </c>
       <c r="D3" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4">
@@ -24926,13 +24927,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.48</v>
+        <v>16.22</v>
       </c>
       <c r="C4" t="n">
-        <v>17.71</v>
+        <v>17.76</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -25003,19 +25004,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9443</v>
+        <v>0.9493</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1164</v>
+        <v>0.1891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.029</v>
+        <v>0.0291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.795</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>0.788</v>
@@ -25033,19 +25034,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9679</v>
+        <v>0.971</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0716</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0193</v>
+        <v>0.0178</v>
       </c>
       <c r="G3" t="n">
-        <v>0.903</v>
+        <v>0.912</v>
       </c>
       <c r="H3" t="n">
         <v>0.5</v>
@@ -25066,16 +25067,16 @@
         <v>19.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9107</v>
+        <v>0.9142</v>
       </c>
       <c r="E4" t="n">
-        <v>0.227</v>
+        <v>0.2345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0529</v>
+        <v>0.0517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="5">
@@ -25090,19 +25091,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.949</v>
+        <v>0.9534</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1337</v>
+        <v>0.1144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0349</v>
+        <v>0.03</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765</v>
+        <v>0.787</v>
       </c>
     </row>
   </sheetData>
@@ -25174,7 +25175,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[16.6, 17.6]</t>
+          <t>[16.5, 17.4]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25191,7 +25192,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[14.4, 15.6]</t>
+          <t>[13.3, 14.4]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25560,10 +25561,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="C2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="3">
@@ -25573,10 +25574,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="4">
@@ -25655,19 +25656,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D2" t="n">
         <v>17</v>
       </c>
-      <c r="C2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.1</v>
-      </c>
       <c r="E2" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="F2" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="3">
@@ -25677,19 +25678,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.7</v>
+        <v>13.7</v>
       </c>
       <c r="C3" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="D3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="E3" t="n">
         <v>15</v>
       </c>
-      <c r="E3" t="n">
-        <v>15.6</v>
-      </c>
       <c r="F3" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
@@ -26153,13 +26154,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="C2" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="3">
@@ -26169,7 +26170,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="C3" t="n">
         <v>22.1</v>
@@ -26185,13 +26186,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="C4" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="D4" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="5">
@@ -26201,13 +26202,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
     </row>
   </sheetData>
@@ -26263,10 +26264,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.795</v>
+        <v>0.804</v>
       </c>
       <c r="C2" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="D2" t="n">
         <v>0.97</v>
@@ -26285,10 +26286,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.903</v>
+        <v>0.91</v>
       </c>
       <c r="C3" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="D3" t="n">
         <v>0.99</v>
@@ -26555,19 +26556,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>14.4</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="H2" t="n">
         <v>12.7</v>
@@ -26583,19 +26584,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.1</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7</v>
+        <v>12.5</v>
       </c>
       <c r="F3" t="n">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="G3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
         <v>13.7</v>
@@ -26614,19 +26615,19 @@
         <v>19.4</v>
       </c>
       <c r="D4" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="F4" t="n">
         <v>22.1</v>
       </c>
       <c r="G4" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="5">
@@ -26639,22 +26640,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="F5" t="n">
-        <v>19.1</v>
+        <v>17.2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="H5" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>
@@ -26705,10 +26706,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="C2" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -26726,7 +26727,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="C3" t="n">
         <v>6.7</v>
@@ -26788,7 +26789,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -26802,7 +26803,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>outputs/synthetic_recoded_gemini.csv, 유튜브_이용 단순평균 n=8168</t>
+          <t>outputs/synthetic_recoded_gemini.csv, 유튜브_이용 단순평균 n=5389</t>
         </is>
       </c>
     </row>
@@ -26813,7 +26814,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -26838,7 +26839,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -26852,7 +26853,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>outputs/synthetic_recoded_2025_gemini.csv, 유튜브_이용 단순평균 n=7938</t>
+          <t>outputs/synthetic_recoded_2025_gemini.csv, 유튜브_이용 단순평균 n=4614</t>
         </is>
       </c>
     </row>
@@ -26863,7 +26864,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -26913,7 +26914,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -26927,7 +26928,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>outputs/synthetic_recoded_gemini.csv vs outputs/synthetic_recoded_gemini_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=0.6, OTT_이용=1.4, 유튜브_이용=0.1, 숏폼_이용=0.4, SNS_이용=0.6, 메신저_이용=0.2, 메타버스_이용=0.5, 콘텐츠구독_이용=0.4</t>
+          <t>outputs/synthetic_recoded_gemini.csv vs outputs/synthetic_recoded_gemini_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=0.6, OTT_이용=1.4, 유튜브_이용=0.0, 숏폼_이용=0.3, SNS_이용=0.6, 메신저_이용=0.2, 메타버스_이용=0.5, 콘텐츠구독_이용=0.4</t>
         </is>
       </c>
     </row>
@@ -26938,7 +26939,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -26952,7 +26953,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>outputs/synthetic_recoded_exaone.csv vs outputs/synthetic_recoded_exaone_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=1.8, OTT_이용=6.1, 유튜브_이용=4.4, 숏폼_이용=2.7, SNS_이용=3.6, 메신저_이용=5.2, 메타버스_이용=6.8, 콘텐츠구독_이용=1.1</t>
+          <t>outputs/synthetic_recoded_exaone.csv vs outputs/synthetic_recoded_exaone_t07.csv; 2024 만 10세 이상 실측 셀 점유율; 지표별 |차|: AI_이용여부=1.8, OTT_이용=6.1, 유튜브_이용=2.2, 숏폼_이용=2.7, SNS_이용=3.6, 메신저_이용=5.2, 메타버스_이용=6.8, 콘텐츠구독_이용=1.1</t>
         </is>
       </c>
     </row>
@@ -27288,7 +27289,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -27313,7 +27314,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.575</v>
+        <v>0.595</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -27581,16 +27582,16 @@
         <v>0.9319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9696</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8659</v>
+        <v>0.9665</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -27603,16 +27604,16 @@
         <v>0.696</v>
       </c>
       <c r="C5" t="n">
-        <v>0.252</v>
+        <v>0.2955</v>
       </c>
       <c r="D5" t="n">
-        <v>-44.4</v>
+        <v>-40</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5139</v>
+        <v>0.5705</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.2</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="6">
@@ -28213,16 +28214,16 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>99.92</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>99.67</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>78.42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -28251,16 +28252,16 @@
         <v>6.34</v>
       </c>
       <c r="G14" t="n">
-        <v>8.68</v>
+        <v>8.76</v>
       </c>
       <c r="H14" t="n">
-        <v>5.93</v>
+        <v>6.27</v>
       </c>
       <c r="I14" t="n">
-        <v>4.56</v>
+        <v>5.06</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.98</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -28289,16 +28290,16 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>99.91</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>99.66</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
-        <v>78.41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -28327,16 +28328,16 @@
         <v>6.34</v>
       </c>
       <c r="G16" t="n">
-        <v>8.67</v>
+        <v>8.76</v>
       </c>
       <c r="H16" t="n">
-        <v>5.93</v>
+        <v>6.27</v>
       </c>
       <c r="I16" t="n">
-        <v>4.56</v>
+        <v>5.06</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.99</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -28394,25 +28395,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90.19</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>68.92</v>
+        <v>69.41</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>34.11</v>
       </c>
       <c r="G18" t="n">
-        <v>11.67</v>
+        <v>12.95</v>
       </c>
       <c r="H18" t="n">
-        <v>4.33</v>
+        <v>6.74</v>
       </c>
       <c r="I18" t="n">
-        <v>2.42</v>
+        <v>5.33</v>
       </c>
       <c r="J18" t="n">
-        <v>0.67</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="19">
@@ -28432,25 +28433,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.01</v>
+        <v>10.72</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.63</v>
+        <v>-15.13</v>
       </c>
       <c r="F19" t="n">
-        <v>-51.84</v>
+        <v>-50.73</v>
       </c>
       <c r="G19" t="n">
-        <v>-62.62</v>
+        <v>-61.34</v>
       </c>
       <c r="H19" t="n">
-        <v>-61.93</v>
+        <v>-59.53</v>
       </c>
       <c r="I19" t="n">
-        <v>-50.23</v>
+        <v>-47.31</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.03</v>
+        <v>-20.13</v>
       </c>
     </row>
     <row r="20">
@@ -28470,25 +28471,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>90.22</v>
+        <v>90.92</v>
       </c>
       <c r="E20" t="n">
-        <v>68.78</v>
+        <v>69.27</v>
       </c>
       <c r="F20" t="n">
-        <v>33.02</v>
+        <v>34.14</v>
       </c>
       <c r="G20" t="n">
-        <v>11.62</v>
+        <v>12.86</v>
       </c>
       <c r="H20" t="n">
-        <v>4.34</v>
+        <v>6.73</v>
       </c>
       <c r="I20" t="n">
-        <v>2.43</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.67</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -28508,25 +28509,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.04</v>
+        <v>10.74</v>
       </c>
       <c r="E21" t="n">
-        <v>-15.76</v>
+        <v>-15.27</v>
       </c>
       <c r="F21" t="n">
-        <v>-51.82</v>
+        <v>-50.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-62.67</v>
+        <v>-61.43</v>
       </c>
       <c r="H21" t="n">
-        <v>-61.93</v>
+        <v>-59.53</v>
       </c>
       <c r="I21" t="n">
-        <v>-50.21</v>
+        <v>-47.24</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.03</v>
+        <v>-20.25</v>
       </c>
     </row>
     <row r="22">
@@ -29724,25 +29725,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>95.76000000000001</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>96.58</v>
+        <v>99.12</v>
       </c>
       <c r="F53" t="n">
-        <v>94.31999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="G53" t="n">
-        <v>90.73999999999999</v>
+        <v>98</v>
       </c>
       <c r="H53" t="n">
-        <v>86.75</v>
+        <v>95.73</v>
       </c>
       <c r="I53" t="n">
-        <v>77.33</v>
+        <v>93.17</v>
       </c>
       <c r="J53" t="n">
-        <v>68.58</v>
+        <v>89.93000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -29762,25 +29763,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.62</v>
+        <v>7.85</v>
       </c>
       <c r="E54" t="n">
-        <v>4.34</v>
+        <v>6.87</v>
       </c>
       <c r="F54" t="n">
-        <v>0.66</v>
+        <v>5.42</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.5</v>
+        <v>6.76</v>
       </c>
       <c r="H54" t="n">
-        <v>-6.98</v>
+        <v>1.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-17.6</v>
+        <v>-1.77</v>
       </c>
       <c r="J54" t="n">
-        <v>-28.82</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="55">
@@ -29800,25 +29801,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>95.78</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>96.54000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="F55" t="n">
-        <v>94.31999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="G55" t="n">
-        <v>90.73</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>86.73999999999999</v>
+        <v>95.72</v>
       </c>
       <c r="I55" t="n">
-        <v>77.26000000000001</v>
+        <v>93.13</v>
       </c>
       <c r="J55" t="n">
-        <v>68.59</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="56">
@@ -29838,25 +29839,25 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.64</v>
+        <v>7.85</v>
       </c>
       <c r="E56" t="n">
-        <v>4.29</v>
+        <v>6.87</v>
       </c>
       <c r="F56" t="n">
-        <v>0.65</v>
+        <v>5.42</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.51</v>
+        <v>6.75</v>
       </c>
       <c r="H56" t="n">
-        <v>-6.99</v>
+        <v>1.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-17.68</v>
+        <v>-1.8</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.81</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="57">
@@ -29914,25 +29915,25 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>68.8</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>66.58</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>60.02</v>
+        <v>62.19</v>
       </c>
       <c r="G58" t="n">
-        <v>51.88</v>
+        <v>55.29</v>
       </c>
       <c r="H58" t="n">
-        <v>48.5</v>
+        <v>53.28</v>
       </c>
       <c r="I58" t="n">
-        <v>39.67</v>
+        <v>45.91</v>
       </c>
       <c r="J58" t="n">
-        <v>33.08</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="59">
@@ -29952,25 +29953,25 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-11.37</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-17.96</v>
+        <v>-16.22</v>
       </c>
       <c r="F59" t="n">
-        <v>-24.82</v>
+        <v>-22.65</v>
       </c>
       <c r="G59" t="n">
-        <v>-22.41</v>
+        <v>-19</v>
       </c>
       <c r="H59" t="n">
-        <v>-17.76</v>
+        <v>-12.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-12.98</v>
+        <v>-6.73</v>
       </c>
       <c r="J59" t="n">
-        <v>4.39</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="60">
@@ -29990,25 +29991,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>68.84</v>
+        <v>71.03</v>
       </c>
       <c r="E60" t="n">
-        <v>66.53</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>60.02</v>
+        <v>62.2</v>
       </c>
       <c r="G60" t="n">
-        <v>51.84</v>
+        <v>55.25</v>
       </c>
       <c r="H60" t="n">
-        <v>48.49</v>
+        <v>53.23</v>
       </c>
       <c r="I60" t="n">
-        <v>39.61</v>
+        <v>45.88</v>
       </c>
       <c r="J60" t="n">
-        <v>33.09</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="61">
@@ -30028,25 +30029,25 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-11.34</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>-18.02</v>
+        <v>-16.28</v>
       </c>
       <c r="F61" t="n">
-        <v>-24.82</v>
+        <v>-22.64</v>
       </c>
       <c r="G61" t="n">
-        <v>-22.45</v>
+        <v>-19.04</v>
       </c>
       <c r="H61" t="n">
-        <v>-17.77</v>
+        <v>-13.03</v>
       </c>
       <c r="I61" t="n">
-        <v>-13.03</v>
+        <v>-6.76</v>
       </c>
       <c r="J61" t="n">
-        <v>4.39</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="62">
@@ -30909,16 +30910,16 @@
         <v>0.9550999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9676</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8628</v>
+        <v>0.9654</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.199999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -30931,16 +30932,16 @@
         <v>0.8649</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2415</v>
+        <v>0.2845</v>
       </c>
       <c r="D5" t="n">
-        <v>-62.3</v>
+        <v>-58</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5097</v>
+        <v>0.5668</v>
       </c>
       <c r="F5" t="n">
-        <v>-35.5</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="6">
@@ -31082,10 +31083,10 @@
         <v>2024</v>
       </c>
       <c r="B2" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="C2" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="D2" t="n">
         <v>13.7</v>
@@ -31102,10 +31103,10 @@
         <v>2025</v>
       </c>
       <c r="B3" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="C3" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
       <c r="D3" t="n">
         <v>31.6</v>

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3168</v>
+        <v>0.3159</v>
       </c>
       <c r="C2" t="n">
         <v>0.3686</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="E2" t="n">
         <v>0.4327</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="3">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9092</v>
+        <v>0.9093</v>
       </c>
       <c r="C3" t="n">
         <v>0.5583</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9558</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>0.9999</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
         <v>0.9241</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="5">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8659</v>
+        <v>0.8649</v>
       </c>
       <c r="C5" t="n">
         <v>0.1714</v>
@@ -864,7 +864,7 @@
         <v>0.3198</v>
       </c>
       <c r="F5" t="n">
-        <v>-54.6</v>
+        <v>-54.5</v>
       </c>
     </row>
     <row r="6">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6486</v>
+        <v>0.6424</v>
       </c>
       <c r="C6" t="n">
         <v>0.4001</v>
       </c>
       <c r="D6" t="n">
-        <v>-24.8</v>
+        <v>-24.2</v>
       </c>
       <c r="E6" t="n">
         <v>0.7191</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9409</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="C7" t="n">
         <v>0.9442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
         <v>0.7329</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.8</v>
+        <v>-20.5</v>
       </c>
     </row>
     <row r="8">
@@ -918,19 +918,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0735</v>
       </c>
       <c r="C8" t="n">
         <v>0.0166</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.3</v>
+        <v>-5.7</v>
       </c>
       <c r="E8" t="n">
         <v>0.0697</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
@@ -940,19 +940,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2247</v>
+        <v>0.2226</v>
       </c>
       <c r="C9" t="n">
         <v>0.3278</v>
       </c>
       <c r="D9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="E9" t="n">
         <v>0.3457</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>
@@ -1806,7 +1806,6 @@
       <c r="I3" t="n">
         <v>38</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>0.582</v>
       </c>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="3">
@@ -2524,10 +2523,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="4">
@@ -2537,10 +2536,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.4</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="5">
@@ -3207,10 +3206,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.4</v>
+        <v>49.6</v>
       </c>
       <c r="C2" t="n">
-        <v>42.2</v>
+        <v>39.5</v>
       </c>
       <c r="D2" t="n">
         <v>-10.6</v>
@@ -3232,10 +3231,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="C3" t="n">
-        <v>32.6</v>
+        <v>31.2</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -3348,7 +3347,7 @@
         <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="I2" t="n">
         <v>12.7</v>
@@ -3389,7 +3388,7 @@
         <v>13.3</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="I3" t="n">
         <v>12.7</v>
@@ -3758,7 +3757,7 @@
         <v>13.3</v>
       </c>
       <c r="H12" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I12" t="n">
         <v>12.9</v>
@@ -3799,7 +3798,7 @@
         <v>13.3</v>
       </c>
       <c r="H13" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I13" t="n">
         <v>12.9</v>
@@ -4086,7 +4085,7 @@
         <v>3.7</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I20" t="n">
         <v>11.8</v>
@@ -4127,7 +4126,7 @@
         <v>3.7</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I21" t="n">
         <v>11.8</v>
@@ -4949,10 +4948,10 @@
         <v>6.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9613</v>
+        <v>0.9665</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -4965,16 +4964,16 @@
         <v>0.696</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2764</v>
+        <v>0.2955</v>
       </c>
       <c r="D5" t="n">
-        <v>-42</v>
+        <v>-40</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5588</v>
+        <v>0.5705</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.7</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="6">
@@ -10950,10 +10949,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="D4" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -10968,10 +10967,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.1</v>
+        <v>37.9</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -11094,10 +11093,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.1</v>
+        <v>5.6</v>
       </c>
       <c r="D12" t="n">
-        <v>13.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="13">
@@ -11112,10 +11111,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="D13" t="n">
-        <v>17.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="14">
@@ -11151,7 +11150,7 @@
         <v>21.6</v>
       </c>
       <c r="D15" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="16">
@@ -13815,7 +13814,7 @@
         <v>-11.32</v>
       </c>
       <c r="K2" t="n">
-        <v>5.85</v>
+        <v>5.851</v>
       </c>
       <c r="L2" t="n">
         <v>9.68</v>
@@ -13824,7 +13823,7 @@
         <v>-0.18</v>
       </c>
       <c r="N2" t="n">
-        <v>2.26</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="3">
@@ -13863,7 +13862,7 @@
         <v>-10.61</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07</v>
+        <v>12.074</v>
       </c>
       <c r="L3" t="n">
         <v>22.2</v>
@@ -13872,7 +13871,7 @@
         <v>0.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.72</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="4">
@@ -13911,7 +13910,7 @@
         <v>-0.89</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.097</v>
       </c>
       <c r="L4" t="n">
         <v>5.28</v>
@@ -13920,7 +13919,7 @@
         <v>0.84</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="5">
@@ -13959,7 +13958,7 @@
         <v>-5.93</v>
       </c>
       <c r="K5" t="n">
-        <v>23.12</v>
+        <v>23.122</v>
       </c>
       <c r="L5" t="n">
         <v>33.23</v>
@@ -13968,7 +13967,7 @@
         <v>0.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.46</v>
+        <v>3.455</v>
       </c>
     </row>
     <row r="6">
@@ -14007,7 +14006,7 @@
         <v>-7.33</v>
       </c>
       <c r="K6" t="n">
-        <v>19.7</v>
+        <v>19.704</v>
       </c>
       <c r="L6" t="n">
         <v>35.69</v>
@@ -14016,7 +14015,7 @@
         <v>0.29</v>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.313</v>
       </c>
     </row>
     <row r="7">
@@ -14055,7 +14054,7 @@
         <v>2.14</v>
       </c>
       <c r="K7" t="n">
-        <v>5.74</v>
+        <v>5.741</v>
       </c>
       <c r="L7" t="n">
         <v>13.79</v>
@@ -14064,7 +14063,7 @@
         <v>0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="8">
@@ -14112,7 +14111,7 @@
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>2.245</v>
       </c>
     </row>
     <row r="9">
@@ -14151,7 +14150,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>6.74</v>
+        <v>6.743</v>
       </c>
       <c r="L9" t="n">
         <v>11.28</v>
@@ -14160,7 +14159,7 @@
         <v>0.22</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.758</v>
       </c>
     </row>
     <row r="10">
@@ -14199,7 +14198,7 @@
         <v>-5.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.43</v>
+        <v>5.432</v>
       </c>
       <c r="L10" t="n">
         <v>13.27</v>
@@ -14208,7 +14207,7 @@
         <v>0.29</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="11">
@@ -14247,7 +14246,7 @@
         <v>1.75</v>
       </c>
       <c r="K11" t="n">
-        <v>11.04</v>
+        <v>11.037</v>
       </c>
       <c r="L11" t="n">
         <v>27.81</v>
@@ -14256,7 +14255,7 @@
         <v>0.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="12">
@@ -14295,7 +14294,7 @@
         <v>-2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.77</v>
+        <v>3.771</v>
       </c>
       <c r="L12" t="n">
         <v>7.29</v>
@@ -14304,7 +14303,7 @@
         <v>0.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="13">
@@ -14343,7 +14342,7 @@
         <v>3.53</v>
       </c>
       <c r="K13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.635</v>
       </c>
       <c r="L13" t="n">
         <v>14.19</v>
@@ -14352,7 +14351,7 @@
         <v>0.14</v>
       </c>
       <c r="N13" t="n">
-        <v>3.46</v>
+        <v>3.455</v>
       </c>
     </row>
     <row r="14">
@@ -14400,7 +14399,7 @@
         <v>0.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.31</v>
+        <v>3.313</v>
       </c>
     </row>
     <row r="15">
@@ -14439,7 +14438,7 @@
         <v>-3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>9.000999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>22.75</v>
@@ -14448,7 +14447,7 @@
         <v>0.22</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="16">
@@ -14487,7 +14486,7 @@
         <v>1.27</v>
       </c>
       <c r="K16" t="n">
-        <v>4.99</v>
+        <v>4.992</v>
       </c>
       <c r="L16" t="n">
         <v>11.28</v>
@@ -14496,7 +14495,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.24</v>
+        <v>2.245</v>
       </c>
     </row>
     <row r="17">
@@ -14535,7 +14534,7 @@
         <v>2.78</v>
       </c>
       <c r="K17" t="n">
-        <v>6.83</v>
+        <v>6.827</v>
       </c>
       <c r="L17" t="n">
         <v>14.49</v>
@@ -14544,7 +14543,7 @@
         <v>-0.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>2.758</v>
       </c>
     </row>
   </sheetData>
@@ -14702,7 +14701,7 @@
         <v>13.33</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="L2" t="n">
         <v>12.75</v>
@@ -14716,21 +14715,21 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[-2.40, 2.12]</t>
+          <t>[-2.59, 2.35]</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
       <c r="S2" t="n">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
       <c r="T2" t="n">
         <v>10.23</v>
@@ -14773,7 +14772,7 @@
         <v>13.33</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="L3" t="n">
         <v>12.75</v>
@@ -14787,21 +14786,21 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-1.42</v>
+        <v>-1.51</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[-3.94, 0.18]</t>
+          <t>[-3.99, 0.28]</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="S3" t="n">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="T3" t="n">
         <v>8.58</v>
@@ -14844,7 +14843,7 @@
         <v>10.51</v>
       </c>
       <c r="K4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="L4" t="n">
         <v>12.21</v>
@@ -14858,21 +14857,21 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[-0.54, 2.27]</t>
+          <t>[-0.60, 2.23]</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>84.5</v>
       </c>
       <c r="R4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="S4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
         <v>9.48</v>
@@ -14915,7 +14914,7 @@
         <v>10.51</v>
       </c>
       <c r="K5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="L5" t="n">
         <v>12.21</v>
@@ -14929,21 +14928,21 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[-2.12, 0.39]</t>
+          <t>[-2.17, 0.33]</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>89</v>
+        <v>90.5</v>
       </c>
       <c r="S5" t="n">
-        <v>89</v>
+        <v>90.5</v>
       </c>
       <c r="T5" t="n">
         <v>7.8</v>
@@ -14986,7 +14985,7 @@
         <v>8.84</v>
       </c>
       <c r="K6" t="n">
-        <v>8.1</v>
+        <v>8.16</v>
       </c>
       <c r="L6" t="n">
         <v>12.01</v>
@@ -15000,21 +14999,21 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[0.07, 2.19]</t>
+          <t>[-0.06, 2.18]</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>31.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
         <v>9.17</v>
@@ -15057,7 +15056,7 @@
         <v>8.84</v>
       </c>
       <c r="K7" t="n">
-        <v>8.1</v>
+        <v>8.16</v>
       </c>
       <c r="L7" t="n">
         <v>12.01</v>
@@ -15071,21 +15070,21 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-0.64</v>
+        <v>-0.7</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[-1.55, 0.19]</t>
+          <t>[-1.63, 0.21]</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>98</v>
       </c>
       <c r="R7" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="S7" t="n">
         <v>90.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>88.5</v>
       </c>
       <c r="T7" t="n">
         <v>7.46</v>
@@ -15128,7 +15127,7 @@
         <v>7.26</v>
       </c>
       <c r="K8" t="n">
-        <v>7.68</v>
+        <v>7.71</v>
       </c>
       <c r="L8" t="n">
         <v>11.88</v>
@@ -15142,18 +15141,18 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[0.36, 2.08]</t>
+          <t>[0.29, 2.08]</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -15199,7 +15198,7 @@
         <v>7.26</v>
       </c>
       <c r="K9" t="n">
-        <v>7.68</v>
+        <v>7.71</v>
       </c>
       <c r="L9" t="n">
         <v>11.88</v>
@@ -15213,21 +15212,21 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[-1.38, 0.23]</t>
+          <t>[-1.36, 0.21]</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>52</v>
       </c>
       <c r="R9" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="S9" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="T9" t="n">
         <v>7.14</v>
@@ -15270,7 +15269,7 @@
         <v>5.42</v>
       </c>
       <c r="K10" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="L10" t="n">
         <v>11.78</v>
@@ -15284,11 +15283,11 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[0.61, 1.86]</t>
+          <t>[0.59, 1.89]</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -15341,7 +15340,7 @@
         <v>5.42</v>
       </c>
       <c r="K11" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="L11" t="n">
         <v>11.78</v>
@@ -15355,11 +15354,11 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[-1.00, 0.10]</t>
+          <t>[-1.02, 0.11]</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -15475,19 +15474,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.69</v>
+        <v>13.74</v>
       </c>
       <c r="C4" t="n">
-        <v>13.18</v>
+        <v>13.23</v>
       </c>
       <c r="D4" t="n">
-        <v>14.25</v>
+        <v>14.28</v>
       </c>
       <c r="E4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="5">
@@ -15754,10 +15753,10 @@
         <v>13.39</v>
       </c>
       <c r="P2" t="n">
-        <v>10.05</v>
+        <v>10.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.7</v>
+        <v>10.74</v>
       </c>
       <c r="R2" t="n">
         <v>12.73</v>
@@ -15766,62 +15765,62 @@
         <v>0.627</v>
       </c>
       <c r="T2" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
       <c r="U2" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[-2.17, 2.22]</t>
+          <t>[-2.40, 2.11]</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>42.5</v>
+        <v>46.5</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.48</v>
+        <v>-1.57</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[-3.59, 1.03]</t>
+          <t>[-3.71, 0.99]</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>92</v>
+        <v>90.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.76</v>
+        <v>-0.85</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[-3.25, 1.53]</t>
+          <t>[-3.40, 1.42]</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>73.5</v>
+        <v>75.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.42</v>
+        <v>-1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[-3.96, 1.07]</t>
+          <t>[-4.04, 1.17]</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[-1.35, 0.78]</t>
+          <t>[-1.45, 0.82]</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>38.3</v>
@@ -15881,10 +15880,10 @@
         <v>13.39</v>
       </c>
       <c r="P3" t="n">
-        <v>10.05</v>
+        <v>10.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.7</v>
+        <v>10.74</v>
       </c>
       <c r="R3" t="n">
         <v>12.73</v>
@@ -15893,62 +15892,62 @@
         <v>0.616</v>
       </c>
       <c r="T3" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.44</v>
+        <v>-1.52</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[-3.71, 0.22]</t>
+          <t>[-3.84, 0.21]</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>93.5</v>
+        <v>95</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.93</v>
+        <v>-2.01</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[-4.21, 0.35]</t>
+          <t>[-4.36, 0.16]</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.57</v>
+        <v>-1.66</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[-4.19, 0.68]</t>
+          <t>[-4.23, 0.74]</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2.22</v>
+        <v>-2.26</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[-4.59, 0.10]</t>
+          <t>[-4.62, -0.03]</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.62</v>
+        <v>-0.66</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[-1.60, 0.11]</t>
+          <t>[-1.74, 0.20]</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>93.5</v>
+        <v>94.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>35.1</v>
@@ -16008,10 +16007,10 @@
         <v>10.51</v>
       </c>
       <c r="P4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.08</v>
+        <v>8.1</v>
       </c>
       <c r="R4" t="n">
         <v>12.18</v>
@@ -16020,62 +16019,62 @@
         <v>0.556</v>
       </c>
       <c r="T4" t="n">
-        <v>0.521</v>
+        <v>0.523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[-0.66, 2.03]</t>
+          <t>[-0.92, 2.05]</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.38</v>
+        <v>-1.42</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[-3.02, 0.18]</t>
+          <t>[-3.25, 0.25]</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1</v>
+        <v>-1.05</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[-2.65, 0.95]</t>
+          <t>[-2.68, 0.80]</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>86.5</v>
+        <v>87.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[-2.12, 1.54]</t>
+          <t>[-2.12, 1.41]</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[-1.29, 0.89]</t>
+          <t>[-1.34, 0.88]</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>49.6</v>
@@ -16135,10 +16134,10 @@
         <v>10.51</v>
       </c>
       <c r="P5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.08</v>
+        <v>8.1</v>
       </c>
       <c r="R5" t="n">
         <v>12.18</v>
@@ -16147,62 +16146,62 @@
         <v>0.537</v>
       </c>
       <c r="T5" t="n">
-        <v>0.521</v>
+        <v>0.523</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.86</v>
+        <v>-0.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>[-2.19, 0.36]</t>
+          <t>[-2.46, 0.29]</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>91</v>
+        <v>91.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.86</v>
+        <v>-1.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[-3.67, -0.28]</t>
+          <t>[-3.68, -0.34]</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.35</v>
+        <v>-1.39</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[-2.89, 0.03]</t>
+          <t>[-3.04, 0.04]</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>96.5</v>
+        <v>97</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[-2.22, 0.76]</t>
+          <t>[-2.23, 0.78]</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.54</v>
+        <v>-0.57</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[-1.57, 0.11]</t>
+          <t>[-1.62, 0.17]</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>93</v>
+        <v>92.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>39.8</v>
@@ -16262,10 +16261,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>8.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="R6" t="n">
         <v>11.98</v>
@@ -16274,62 +16273,62 @@
         <v>0.537</v>
       </c>
       <c r="T6" t="n">
-        <v>0.502</v>
+        <v>0.506</v>
       </c>
       <c r="U6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>[-0.23, 2.11]</t>
+          <t>[-0.39, 2.12]</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[-2.74, 0.09]</t>
+          <t>[-2.81, -0.08]</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[-2.51, 0.48]</t>
+          <t>[-2.66, 0.47]</t>
         </is>
       </c>
       <c r="AC6" t="n">
         <v>95.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[-1.42, 1.48]</t>
+          <t>[-1.47, 1.51]</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>61</v>
+        <v>60.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.14</v>
+        <v>-0.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[-1.07, 0.80]</t>
+          <t>[-1.08, 0.76]</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>63.5</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>54</v>
@@ -16389,10 +16388,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>8.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="R7" t="n">
         <v>11.98</v>
@@ -16401,62 +16400,62 @@
         <v>0.51</v>
       </c>
       <c r="T7" t="n">
-        <v>0.502</v>
+        <v>0.506</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>[-1.66, 0.26]</t>
+          <t>[-1.83, 0.17]</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>89</v>
+        <v>91.5</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.04</v>
+        <v>-2.07</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[-3.34, -0.66]</t>
+          <t>[-3.36, -0.71]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>100</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.58</v>
+        <v>-1.61</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[-2.78, -0.34]</t>
+          <t>[-2.84, -0.45]</t>
         </is>
       </c>
       <c r="AC7" t="n">
         <v>98.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[-1.65, 1.01]</t>
+          <t>[-1.68, 0.95]</t>
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>69.5</v>
+        <v>71.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[-1.29, 0.01]</t>
+          <t>[-1.35, -0.02]</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>46.1</v>
@@ -16516,10 +16515,10 @@
         <v>7.28</v>
       </c>
       <c r="P8" t="n">
-        <v>7.73</v>
+        <v>7.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.91</v>
+        <v>5.93</v>
       </c>
       <c r="R8" t="n">
         <v>11.88</v>
@@ -16528,62 +16527,62 @@
         <v>0.55</v>
       </c>
       <c r="T8" t="n">
-        <v>0.503</v>
+        <v>0.505</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>[0.59, 2.81]</t>
+          <t>[0.49, 2.81]</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.16</v>
+        <v>-1.17</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[-2.26, -0.04]</t>
+          <t>[-2.30, -0.04]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>98</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[-2.06, 0.18]</t>
+          <t>[-2.08, 0.18]</t>
         </is>
       </c>
       <c r="AC8" t="n">
         <v>96</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[-0.91, 1.23]</t>
+          <t>[-0.95, 1.18]</t>
         </is>
       </c>
       <c r="AF8" t="n">
         <v>36.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[-0.98, 0.48]</t>
+          <t>[-0.96, 0.51]</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>58.2</v>
@@ -16643,10 +16642,10 @@
         <v>7.28</v>
       </c>
       <c r="P9" t="n">
-        <v>7.73</v>
+        <v>7.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.91</v>
+        <v>5.93</v>
       </c>
       <c r="R9" t="n">
         <v>11.88</v>
@@ -16655,62 +16654,62 @@
         <v>0.506</v>
       </c>
       <c r="T9" t="n">
-        <v>0.503</v>
+        <v>0.505</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>[-1.11, 1.06]</t>
+          <t>[-1.14, 1.06]</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.69</v>
+        <v>-1.7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[-2.81, -0.52]</t>
+          <t>[-2.79, -0.52]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[-2.54, -0.16]</t>
+          <t>[-2.60, -0.16]</t>
         </is>
       </c>
       <c r="AC9" t="n">
         <v>98</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[-1.31, 1.08]</t>
+          <t>[-1.33, 1.16]</t>
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[-1.01, 0.17]</t>
+          <t>[-1.00, 0.19]</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
         <v>53.2</v>
@@ -16770,10 +16769,10 @@
         <v>5.48</v>
       </c>
       <c r="P10" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="R10" t="n">
         <v>11.78</v>
@@ -16782,7 +16781,7 @@
         <v>0.576</v>
       </c>
       <c r="T10" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="U10" t="n">
         <v>3.03</v>
@@ -16818,26 +16817,26 @@
         <v>49.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[-0.20, 1.50]</t>
+          <t>[-0.22, 1.48]</t>
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[-0.88, 0.30]</t>
+          <t>[-0.89, 0.37]</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>78</v>
+        <v>79.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>63</v>
@@ -16897,10 +16896,10 @@
         <v>5.48</v>
       </c>
       <c r="P11" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="R11" t="n">
         <v>11.78</v>
@@ -16909,7 +16908,7 @@
         <v>0.555</v>
       </c>
       <c r="T11" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="U11" t="n">
         <v>1.35</v>
@@ -16945,26 +16944,26 @@
         <v>80.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[-0.55, 1.38]</t>
+          <t>[-0.57, 1.33]</t>
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[-0.60, 0.23]</t>
+          <t>[-0.62, 0.21]</t>
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AJ11" t="n">
         <v>60.3</v>
@@ -17027,7 +17026,7 @@
         <v>7.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="R12" t="n">
         <v>11.75</v>
@@ -17036,7 +17035,7 @@
         <v>0.638</v>
       </c>
       <c r="T12" t="n">
-        <v>0.642</v>
+        <v>0.643</v>
       </c>
       <c r="U12" t="n">
         <v>4.15</v>
@@ -17076,7 +17075,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[0.38, 1.89]</t>
+          <t>[0.36, 1.88]</t>
         </is>
       </c>
       <c r="AF12" t="n">
@@ -17087,11 +17086,11 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[-0.79, 0.32]</t>
+          <t>[-0.79, 0.33]</t>
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>66.3</v>
@@ -17154,7 +17153,7 @@
         <v>7.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="R13" t="n">
         <v>11.75</v>
@@ -17163,7 +17162,7 @@
         <v>0.653</v>
       </c>
       <c r="T13" t="n">
-        <v>0.642</v>
+        <v>0.643</v>
       </c>
       <c r="U13" t="n">
         <v>2.5</v>
@@ -17199,26 +17198,26 @@
         <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[0.03, 1.31]</t>
+          <t>[0.02, 1.32]</t>
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[-0.38, 0.18]</t>
+          <t>[-0.39, 0.18]</t>
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>72</v>
+        <v>74.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>66.40000000000001</v>
@@ -17278,7 +17277,7 @@
         <v>3.63</v>
       </c>
       <c r="P14" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="Q14" t="n">
         <v>3.5</v>
@@ -17290,7 +17289,7 @@
         <v>0.6820000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>4.65</v>
@@ -17330,7 +17329,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[0.79, 2.04]</t>
+          <t>[0.81, 2.02]</t>
         </is>
       </c>
       <c r="AF14" t="n">
@@ -17341,11 +17340,11 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[-0.59, 0.18]</t>
+          <t>[-0.58, 0.19]</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ14" t="n">
         <v>66.09999999999999</v>
@@ -17405,7 +17404,7 @@
         <v>3.63</v>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="Q15" t="n">
         <v>3.5</v>
@@ -17417,7 +17416,7 @@
         <v>0.724</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>3.02</v>
@@ -17457,7 +17456,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[0.34, 1.40]</t>
+          <t>[0.32, 1.40]</t>
         </is>
       </c>
       <c r="AF15" t="n">
@@ -17468,11 +17467,11 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[-0.29, 0.20]</t>
+          <t>[-0.30, 0.21]</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>63</v>
+        <v>64.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>67.8</v>
@@ -17532,10 +17531,10 @@
         <v>13.24</v>
       </c>
       <c r="P16" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.04</v>
+        <v>11.08</v>
       </c>
       <c r="R16" t="n">
         <v>12.99</v>
@@ -17544,62 +17543,62 @@
         <v>0.642</v>
       </c>
       <c r="T16" t="n">
-        <v>0.599</v>
+        <v>0.602</v>
       </c>
       <c r="U16" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>[-2.41, 3.28]</t>
+          <t>[-2.58, 3.10]</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.05</v>
+        <v>-1.12</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[-3.99, 1.98]</t>
+          <t>[-4.03, 1.77]</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>77</v>
+        <v>78.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>[-3.76, 3.17]</t>
+          <t>[-3.93, 2.95]</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.37</v>
+        <v>-1.41</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[-4.64, 1.58]</t>
+          <t>[-4.64, 1.55]</t>
         </is>
       </c>
       <c r="AF16" t="n">
         <v>86.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[-1.20, 1.59]</t>
+          <t>[-1.23, 1.57]</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>47</v>
+        <v>52.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>39.7</v>
@@ -17659,10 +17658,10 @@
         <v>13.24</v>
       </c>
       <c r="P17" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.04</v>
+        <v>11.08</v>
       </c>
       <c r="R17" t="n">
         <v>12.99</v>
@@ -17671,62 +17670,62 @@
         <v>0.623</v>
       </c>
       <c r="T17" t="n">
-        <v>0.599</v>
+        <v>0.602</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.97</v>
+        <v>-1.04</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>[-3.52, 1.49]</t>
+          <t>[-3.81, 1.38]</t>
         </is>
       </c>
       <c r="W17" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>[-4.38, 1.42]</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>[-4.53, 1.97]</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
         <v>80</v>
       </c>
-      <c r="X17" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>[-4.35, 1.67]</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>[-4.40, 2.18]</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>78.5</v>
-      </c>
       <c r="AD17" t="n">
-        <v>-2.07</v>
+        <v>-2.11</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[-4.60, 0.55]</t>
+          <t>[-4.67, 0.29]</t>
         </is>
       </c>
       <c r="AF17" t="n">
         <v>95</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.39</v>
+        <v>-0.43</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[-1.57, 0.81]</t>
+          <t>[-1.59, 0.78]</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="n">
         <v>37.8</v>
@@ -17786,10 +17785,10 @@
         <v>10.46</v>
       </c>
       <c r="P18" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.31</v>
+        <v>8.35</v>
       </c>
       <c r="R18" t="n">
         <v>12.36</v>
@@ -17798,62 +17797,62 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.528</v>
+        <v>0.531</v>
       </c>
       <c r="U18" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>[-0.70, 2.61]</t>
+          <t>[-0.93, 2.56]</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.28</v>
+        <v>-1.35</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[-2.93, 0.76]</t>
+          <t>[-3.16, 0.79]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>92.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.85</v>
+        <v>-0.92</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>[-2.87, 1.60]</t>
+          <t>[-3.12, 1.58]</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.33</v>
+        <v>-0.38</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[-2.25, 2.15]</t>
+          <t>[-2.37, 2.14]</t>
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[-1.05, 0.94]</t>
+          <t>[-1.15, 0.95]</t>
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AJ18" t="n">
         <v>46.6</v>
@@ -17913,10 +17912,10 @@
         <v>10.46</v>
       </c>
       <c r="P19" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.31</v>
+        <v>8.35</v>
       </c>
       <c r="R19" t="n">
         <v>12.36</v>
@@ -17925,62 +17924,62 @@
         <v>0.537</v>
       </c>
       <c r="T19" t="n">
-        <v>0.528</v>
+        <v>0.531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.74</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>[-2.25, 0.94]</t>
+          <t>[-2.48, 0.84]</t>
         </is>
       </c>
       <c r="W19" t="n">
         <v>83</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.76</v>
+        <v>-1.82</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[-3.53, 0.29]</t>
+          <t>[-3.65, 0.24]</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.32</v>
+        <v>-1.39</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>[-3.27, 0.66]</t>
+          <t>[-3.35, 0.74]</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[-2.74, 0.99]</t>
+          <t>[-2.78, 0.91]</t>
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>80.5</v>
+        <v>82.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.44</v>
+        <v>-0.49</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[-1.19, 0.24]</t>
+          <t>[-1.32, 0.26]</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>41.2</v>
@@ -18040,10 +18039,10 @@
         <v>9.01</v>
       </c>
       <c r="P20" t="n">
-        <v>8.31</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.18</v>
+        <v>7.21</v>
       </c>
       <c r="R20" t="n">
         <v>12.13</v>
@@ -18052,62 +18051,62 @@
         <v>0.54</v>
       </c>
       <c r="T20" t="n">
-        <v>0.499</v>
+        <v>0.501</v>
       </c>
       <c r="U20" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>[-0.16, 2.31]</t>
+          <t>[-0.16, 2.50]</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.28</v>
+        <v>-1.33</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[-2.54, 0.47]</t>
+          <t>[-2.70, 0.48]</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.08</v>
+        <v>-1.13</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>[-2.38, 0.67]</t>
+          <t>[-2.59, 0.75]</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[-1.43, 1.55]</t>
+          <t>[-1.51, 1.42]</t>
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>55.5</v>
+        <v>59</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[-0.92, 0.77]</t>
+          <t>[-1.03, 0.73]</t>
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>56.5</v>
+        <v>61</v>
       </c>
       <c r="AJ20" t="n">
         <v>52.3</v>
@@ -18167,10 +18166,10 @@
         <v>9.01</v>
       </c>
       <c r="P21" t="n">
-        <v>8.31</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.18</v>
+        <v>7.21</v>
       </c>
       <c r="R21" t="n">
         <v>12.13</v>
@@ -18179,62 +18178,62 @@
         <v>0.503</v>
       </c>
       <c r="T21" t="n">
-        <v>0.499</v>
+        <v>0.501</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.52</v>
+        <v>-0.57</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>[-1.57, 0.67]</t>
+          <t>[-1.59, 0.61]</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.78</v>
+        <v>-1.83</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[-2.98, -0.09]</t>
+          <t>[-2.98, -0.14]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>98</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.32</v>
+        <v>-1.37</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>[-2.66, 0.11]</t>
+          <t>[-2.86, 0.29]</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>96.5</v>
+        <v>96</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[-1.74, 1.20]</t>
+          <t>[-1.88, 1.25]</t>
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[-1.07, 0.25]</t>
+          <t>[-1.13, 0.25]</t>
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="AJ21" t="n">
         <v>45.2</v>
@@ -18294,10 +18293,10 @@
         <v>7.36</v>
       </c>
       <c r="P22" t="n">
-        <v>7.78</v>
+        <v>7.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="R22" t="n">
         <v>11.96</v>
@@ -18306,14 +18305,14 @@
         <v>0.531</v>
       </c>
       <c r="T22" t="n">
-        <v>0.489</v>
+        <v>0.491</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>[0.70, 2.87]</t>
+          <t>[0.75, 2.87]</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -18328,36 +18327,36 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>[-2.05, 0.16]</t>
+          <t>[-2.02, 0.16]</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[-0.73, 1.39]</t>
+          <t>[-0.70, 1.35]</t>
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>31.5</v>
+        <v>33</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[-0.77, 0.62]</t>
+          <t>[-0.82, 0.61]</t>
         </is>
       </c>
       <c r="AI22" t="n">
@@ -18421,10 +18420,10 @@
         <v>7.36</v>
       </c>
       <c r="P23" t="n">
-        <v>7.78</v>
+        <v>7.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="R23" t="n">
         <v>11.96</v>
@@ -18433,25 +18432,25 @@
         <v>0.496</v>
       </c>
       <c r="T23" t="n">
-        <v>0.489</v>
+        <v>0.491</v>
       </c>
       <c r="U23" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>[-0.97, 1.14]</t>
+          <t>[-1.02, 1.14]</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[-2.48, -0.56]</t>
+          <t>[-2.50, -0.58]</t>
         </is>
       </c>
       <c r="Z23" t="n">
@@ -18462,33 +18461,33 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>[-2.28, -0.05]</t>
+          <t>[-2.23, -0.05]</t>
         </is>
       </c>
       <c r="AC23" t="n">
         <v>98</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[-1.03, 1.21]</t>
+          <t>[-1.07, 1.21]</t>
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>52.5</v>
+        <v>55.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[-0.88, 0.26]</t>
+          <t>[-0.88, 0.27]</t>
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="AJ23" t="n">
         <v>51.6</v>
@@ -18548,10 +18547,10 @@
         <v>5.47</v>
       </c>
       <c r="P24" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
         <v>11.82</v>
@@ -18560,7 +18559,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.544</v>
+        <v>0.546</v>
       </c>
       <c r="U24" t="n">
         <v>3.08</v>
@@ -18596,26 +18595,26 @@
         <v>44.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[-0.16, 1.42]</t>
+          <t>[-0.14, 1.42]</t>
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[-0.69, 0.35]</t>
+          <t>[-0.78, 0.33]</t>
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
         <v>61.3</v>
@@ -18675,10 +18674,10 @@
         <v>5.47</v>
       </c>
       <c r="P25" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
         <v>11.82</v>
@@ -18687,7 +18686,7 @@
         <v>0.541</v>
       </c>
       <c r="T25" t="n">
-        <v>0.544</v>
+        <v>0.546</v>
       </c>
       <c r="U25" t="n">
         <v>1.42</v>
@@ -18723,26 +18722,26 @@
         <v>75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[-0.55, 1.23]</t>
+          <t>[-0.54, 1.22]</t>
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[-0.65, 0.20]</t>
+          <t>[-0.68, 0.21]</t>
         </is>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="n">
         <v>61.2</v>
@@ -18802,7 +18801,7 @@
         <v>4.18</v>
       </c>
       <c r="P26" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="Q26" t="n">
         <v>3.99</v>
@@ -18814,7 +18813,7 @@
         <v>0.621</v>
       </c>
       <c r="T26" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
       <c r="U26" t="n">
         <v>4.2</v>
@@ -18854,22 +18853,22 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[0.47, 1.88]</t>
+          <t>[0.45, 1.84]</t>
         </is>
       </c>
       <c r="AF26" t="n">
         <v>0.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[-0.76, 0.30]</t>
+          <t>[-0.74, 0.33]</t>
         </is>
       </c>
       <c r="AI26" t="n">
-        <v>76.5</v>
+        <v>79.5</v>
       </c>
       <c r="AJ26" t="n">
         <v>65.40000000000001</v>
@@ -18929,7 +18928,7 @@
         <v>4.18</v>
       </c>
       <c r="P27" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="Q27" t="n">
         <v>3.99</v>
@@ -18941,7 +18940,7 @@
         <v>0.637</v>
       </c>
       <c r="T27" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
       <c r="U27" t="n">
         <v>2.56</v>
@@ -18977,11 +18976,11 @@
         <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>[0.01, 1.34]</t>
+          <t>[0.03, 1.37]</t>
         </is>
       </c>
       <c r="AF27" t="n">
@@ -18992,11 +18991,11 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[-0.41, 0.22]</t>
+          <t>[-0.42, 0.21]</t>
         </is>
       </c>
       <c r="AI27" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="AJ27" t="n">
         <v>66.90000000000001</v>
@@ -19056,7 +19055,7 @@
         <v>3.68</v>
       </c>
       <c r="P28" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="Q28" t="n">
         <v>3.59</v>
@@ -19068,7 +19067,7 @@
         <v>0.669</v>
       </c>
       <c r="T28" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U28" t="n">
         <v>4.68</v>
@@ -19108,7 +19107,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[0.75, 2.13]</t>
+          <t>[0.73, 2.10]</t>
         </is>
       </c>
       <c r="AF28" t="n">
@@ -19119,7 +19118,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[-0.69, 0.32]</t>
+          <t>[-0.64, 0.31]</t>
         </is>
       </c>
       <c r="AI28" t="n">
@@ -19183,7 +19182,7 @@
         <v>3.68</v>
       </c>
       <c r="P29" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="Q29" t="n">
         <v>3.59</v>
@@ -19195,7 +19194,7 @@
         <v>0.714</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U29" t="n">
         <v>3.04</v>
@@ -19235,7 +19234,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[0.39, 1.43]</t>
+          <t>[0.39, 1.41]</t>
         </is>
       </c>
       <c r="AF29" t="n">
@@ -19246,11 +19245,11 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[-0.31, 0.25]</t>
+          <t>[-0.32, 0.24]</t>
         </is>
       </c>
       <c r="AI29" t="n">
-        <v>67.5</v>
+        <v>66.5</v>
       </c>
       <c r="AJ29" t="n">
         <v>68.90000000000001</v>
@@ -19329,7 +19328,7 @@
         <v>6.16</v>
       </c>
       <c r="F2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="G2" t="n">
         <v>12.5</v>
@@ -19354,7 +19353,7 @@
         <v>5.68</v>
       </c>
       <c r="F3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>12.48</v>
@@ -23558,7 +23557,7 @@
         <v>6.72</v>
       </c>
       <c r="G4" t="n">
-        <v>6.21</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="5">
@@ -23577,7 +23576,7 @@
         <v>4.83</v>
       </c>
       <c r="G5" t="n">
-        <v>6.18</v>
+        <v>6.12</v>
       </c>
     </row>
   </sheetData>
@@ -23644,7 +23643,7 @@
         <v>10.39</v>
       </c>
       <c r="D2" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="E2" t="n">
         <v>10.23</v>
@@ -23669,7 +23668,7 @@
         <v>9.98</v>
       </c>
       <c r="D3" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="E3" t="n">
         <v>8.58</v>
@@ -23694,7 +23693,7 @@
         <v>7.89</v>
       </c>
       <c r="D4" t="n">
-        <v>7.98</v>
+        <v>8.02</v>
       </c>
       <c r="E4" t="n">
         <v>9.48</v>
@@ -23719,7 +23718,7 @@
         <v>7.45</v>
       </c>
       <c r="D5" t="n">
-        <v>7.98</v>
+        <v>8.02</v>
       </c>
       <c r="E5" t="n">
         <v>7.8</v>
@@ -23744,7 +23743,7 @@
         <v>6.72</v>
       </c>
       <c r="D6" t="n">
-        <v>6.84</v>
+        <v>6.88</v>
       </c>
       <c r="E6" t="n">
         <v>9.17</v>
@@ -23769,7 +23768,7 @@
         <v>6.42</v>
       </c>
       <c r="D7" t="n">
-        <v>6.84</v>
+        <v>6.88</v>
       </c>
       <c r="E7" t="n">
         <v>7.46</v>
@@ -23794,7 +23793,7 @@
         <v>5.73</v>
       </c>
       <c r="D8" t="n">
-        <v>5.87</v>
+        <v>5.89</v>
       </c>
       <c r="E8" t="n">
         <v>8.85</v>
@@ -23819,7 +23818,7 @@
         <v>5.58</v>
       </c>
       <c r="D9" t="n">
-        <v>5.87</v>
+        <v>5.89</v>
       </c>
       <c r="E9" t="n">
         <v>7.14</v>
@@ -23844,7 +23843,7 @@
         <v>4.58</v>
       </c>
       <c r="D10" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="E10" t="n">
         <v>8.48</v>
@@ -23869,7 +23868,7 @@
         <v>4.63</v>
       </c>
       <c r="D11" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="E11" t="n">
         <v>6.82</v>
@@ -24895,13 +24894,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.17</v>
+        <v>15.98</v>
       </c>
       <c r="C2" t="n">
-        <v>17.74</v>
+        <v>17.42</v>
       </c>
       <c r="D2" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="3">
@@ -24911,13 +24910,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.19</v>
+        <v>16.12</v>
       </c>
       <c r="C3" t="n">
-        <v>17.86</v>
+        <v>17.57</v>
       </c>
       <c r="D3" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="4">
@@ -24927,13 +24926,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.22</v>
+        <v>16.2</v>
       </c>
       <c r="C4" t="n">
-        <v>17.76</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -25180,7 +25179,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>가구군집(4016) 부트스트랩 B=600; 행단위 [16.7,17.6]</t>
+          <t>가구군집(4016) 부트스트랩 B=600; 행단위 CI 는 rq_uncertainty.py 콘솔 출력 참조</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25196,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>행단위 [14.3,15.6]; 비중첩 유지</t>
+          <t>가구군집(4016) 부트스트랩 B=600; 행단위 CI 는 rq_uncertainty.py 콘솔 출력 참조</t>
         </is>
       </c>
     </row>
@@ -25256,10 +25255,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="C2" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="3">
@@ -25269,10 +25268,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -25282,10 +25281,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="5">
@@ -25295,10 +25294,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C5" t="n">
         <v>15.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -26154,7 +26153,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>18.3</v>
@@ -26170,7 +26169,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="C3" t="n">
         <v>22.1</v>
@@ -26202,7 +26201,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="C5" t="n">
         <v>22</v>
@@ -26264,10 +26263,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.804</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="D2" t="n">
         <v>0.97</v>
@@ -26286,7 +26285,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.91</v>
+        <v>0.912</v>
       </c>
       <c r="C3" t="n">
         <v>0.72</v>
@@ -26615,19 +26614,19 @@
         <v>19.4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="E4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="F4" t="n">
         <v>22.1</v>
       </c>
       <c r="G4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="5">
@@ -26640,19 +26639,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="E5" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="G5" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H5" t="n">
         <v>11.1</v>
@@ -26798,7 +26797,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100.0 (IV-D, 2024, 게이트 적용 후)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26848,7 +26847,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>93.9 (IV-D, 2025 문항셋)</t>
+          <t>100.0 (IV-D, 2025 문항셋, 게이트 적용 후)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -27298,7 +27297,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51.6% (Gemini), 57.5% (EXAONE) (IV-C)</t>
+          <t>52.5% (Gemini), 59.5% (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -27323,7 +27322,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>51.6% (Gemini), 57.5% (EXAONE) (IV-C)</t>
+          <t>52.5% (Gemini), 59.5% (EXAONE) (IV-C)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">

--- a/outputs/validity_results.xlsx
+++ b/outputs/validity_results.xlsx
@@ -77,6 +77,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베이스라인_공통6_보정" sheetId="68" state="visible" r:id="rId68"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_보조수치" sheetId="69" state="visible" r:id="rId69"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_연령대별_부호오차" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_게이트셀_합성" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="심사_게이트셀_실측분할" sheetId="72" state="visible" r:id="rId72"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15512,7 +15514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK29"/>
+  <dimension ref="A1:AO29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15663,40 +15665,60 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>최우수빈도_nested%</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>최우수빈도_dir%</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>최우수빈도_reg%</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>최우수빈도_eb%</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>Δ(중첩−실측EB)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Δ(중첩−실측EB)_CI</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>중첩−실측EB&lt;0%</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Δ(합성EB−실측EB)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Δ(합성EB−실측EB)_CI</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>합성EB−실측EB&lt;0%</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>nested선택: quad%</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>nested선택: lin%</t>
         </is>
@@ -15801,31 +15823,43 @@
         <v>75.5</v>
       </c>
       <c r="AD2" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>-1.45</v>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>[-4.04, 1.17]</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AJ2" t="n">
         <v>86</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AK2" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>[-1.45, 0.82]</t>
         </is>
       </c>
-      <c r="AI2" t="n">
+      <c r="AM2" t="n">
         <v>69.5</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AN2" t="n">
         <v>38.3</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AO2" t="n">
         <v>24.1</v>
       </c>
     </row>
@@ -15928,31 +15962,43 @@
         <v>94</v>
       </c>
       <c r="AD3" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-2.26</v>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>[-4.62, -0.03]</t>
         </is>
       </c>
-      <c r="AF3" t="n">
+      <c r="AJ3" t="n">
         <v>97.5</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AK3" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>[-1.74, 0.20]</t>
         </is>
       </c>
-      <c r="AI3" t="n">
+      <c r="AM3" t="n">
         <v>94.5</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AN3" t="n">
         <v>35.1</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AO3" t="n">
         <v>26.8</v>
       </c>
     </row>
@@ -16055,31 +16101,43 @@
         <v>87.5</v>
       </c>
       <c r="AD4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>[-2.12, 1.41]</t>
         </is>
       </c>
-      <c r="AF4" t="n">
+      <c r="AJ4" t="n">
         <v>66</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AK4" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>[-1.34, 0.88]</t>
         </is>
       </c>
-      <c r="AI4" t="n">
+      <c r="AM4" t="n">
         <v>65.5</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AN4" t="n">
         <v>49.6</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AO4" t="n">
         <v>19.2</v>
       </c>
     </row>
@@ -16182,31 +16240,43 @@
         <v>97</v>
       </c>
       <c r="AD5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>[-2.23, 0.78]</t>
         </is>
       </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
         <v>79</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AK5" t="n">
         <v>-0.57</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>[-1.62, 0.17]</t>
         </is>
       </c>
-      <c r="AI5" t="n">
+      <c r="AM5" t="n">
         <v>92.5</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AN5" t="n">
         <v>39.8</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AO5" t="n">
         <v>24.8</v>
       </c>
     </row>
@@ -16309,31 +16379,43 @@
         <v>95.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>[-1.47, 1.51]</t>
         </is>
       </c>
-      <c r="AF6" t="n">
+      <c r="AJ6" t="n">
         <v>60.5</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AK6" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>[-1.08, 0.76]</t>
         </is>
       </c>
-      <c r="AI6" t="n">
+      <c r="AM6" t="n">
         <v>65</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AN6" t="n">
         <v>54</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AO6" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -16436,31 +16518,43 @@
         <v>98.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>[-1.68, 0.95]</t>
         </is>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
         <v>71.5</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AK7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>[-1.35, -0.02]</t>
         </is>
       </c>
-      <c r="AI7" t="n">
+      <c r="AM7" t="n">
         <v>98.5</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AN7" t="n">
         <v>46.1</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AO7" t="n">
         <v>21.6</v>
       </c>
     </row>
@@ -16563,31 +16657,43 @@
         <v>96</v>
       </c>
       <c r="AD8" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.19</v>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[-0.95, 1.18]</t>
         </is>
       </c>
-      <c r="AF8" t="n">
+      <c r="AJ8" t="n">
         <v>36.5</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AK8" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>[-0.96, 0.51]</t>
         </is>
       </c>
-      <c r="AI8" t="n">
+      <c r="AM8" t="n">
         <v>75.5</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AN8" t="n">
         <v>58.2</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AO8" t="n">
         <v>20</v>
       </c>
     </row>
@@ -16690,31 +16796,43 @@
         <v>98</v>
       </c>
       <c r="AD9" t="n">
+        <v>58</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>[-1.33, 1.16]</t>
         </is>
       </c>
-      <c r="AF9" t="n">
+      <c r="AJ9" t="n">
         <v>58</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AK9" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>[-1.00, 0.19]</t>
         </is>
       </c>
-      <c r="AI9" t="n">
+      <c r="AM9" t="n">
         <v>90</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AN9" t="n">
         <v>53.2</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AO9" t="n">
         <v>20.2</v>
       </c>
     </row>
@@ -16795,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -16817,31 +16935,43 @@
         <v>49.5</v>
       </c>
       <c r="AD10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.63</v>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>[-0.22, 1.48]</t>
         </is>
       </c>
-      <c r="AF10" t="n">
+      <c r="AJ10" t="n">
         <v>8</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AK10" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>[-0.89, 0.37]</t>
         </is>
       </c>
-      <c r="AI10" t="n">
+      <c r="AM10" t="n">
         <v>79.5</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AN10" t="n">
         <v>63</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AO10" t="n">
         <v>17.6</v>
       </c>
     </row>
@@ -16944,31 +17074,43 @@
         <v>80.5</v>
       </c>
       <c r="AD11" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>63</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.24</v>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>[-0.57, 1.33]</t>
         </is>
       </c>
-      <c r="AF11" t="n">
+      <c r="AJ11" t="n">
         <v>34</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AK11" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>[-0.62, 0.21]</t>
         </is>
       </c>
-      <c r="AI11" t="n">
+      <c r="AM11" t="n">
         <v>86</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AN11" t="n">
         <v>60.3</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AO11" t="n">
         <v>20.5</v>
       </c>
     </row>
@@ -17071,31 +17213,43 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[0.36, 1.88]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>25.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[0.36, 1.88]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>[-0.79, 0.33]</t>
         </is>
       </c>
-      <c r="AI12" t="n">
+      <c r="AM12" t="n">
         <v>81.5</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AN12" t="n">
         <v>66.3</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AO12" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17198,31 +17352,43 @@
         <v>12</v>
       </c>
       <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0.64</v>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>[0.02, 1.32]</t>
         </is>
       </c>
-      <c r="AF13" t="n">
+      <c r="AJ13" t="n">
         <v>2</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AK13" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>[-0.39, 0.18]</t>
         </is>
       </c>
-      <c r="AI13" t="n">
+      <c r="AM13" t="n">
         <v>74.5</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AN13" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AO13" t="n">
         <v>16.2</v>
       </c>
     </row>
@@ -17325,31 +17491,43 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[0.81, 2.02]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>32.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[0.81, 2.02]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>[-0.58, 0.19]</t>
         </is>
       </c>
-      <c r="AI14" t="n">
+      <c r="AM14" t="n">
         <v>78</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AN14" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AO14" t="n">
         <v>13.8</v>
       </c>
     </row>
@@ -17452,31 +17630,43 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[0.32, 1.40]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>32.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[0.32, 1.40]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>[-0.30, 0.21]</t>
         </is>
       </c>
-      <c r="AI15" t="n">
+      <c r="AM15" t="n">
         <v>64.5</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AN15" t="n">
         <v>67.8</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AO15" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -17579,31 +17769,43 @@
         <v>59</v>
       </c>
       <c r="AD16" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
         <v>-1.41</v>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>[-4.64, 1.55]</t>
         </is>
       </c>
-      <c r="AF16" t="n">
+      <c r="AJ16" t="n">
         <v>86.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL16" t="inlineStr">
         <is>
           <t>[-1.23, 1.57]</t>
         </is>
       </c>
-      <c r="AI16" t="n">
+      <c r="AM16" t="n">
         <v>52.5</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AN16" t="n">
         <v>39.7</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AO16" t="n">
         <v>23.5</v>
       </c>
     </row>
@@ -17706,31 +17908,43 @@
         <v>80</v>
       </c>
       <c r="AD17" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="n">
         <v>-2.11</v>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>[-4.67, 0.29]</t>
         </is>
       </c>
-      <c r="AF17" t="n">
+      <c r="AJ17" t="n">
         <v>95</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AK17" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>[-1.59, 0.78]</t>
         </is>
       </c>
-      <c r="AI17" t="n">
+      <c r="AM17" t="n">
         <v>82</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AN17" t="n">
         <v>37.8</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AO17" t="n">
         <v>26.1</v>
       </c>
     </row>
@@ -17833,31 +18047,43 @@
         <v>78.5</v>
       </c>
       <c r="AD18" t="n">
+        <v>63</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH18" t="n">
         <v>-0.38</v>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>[-2.37, 2.14]</t>
         </is>
       </c>
-      <c r="AF18" t="n">
+      <c r="AJ18" t="n">
         <v>65</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AK18" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>[-1.15, 0.95]</t>
         </is>
       </c>
-      <c r="AI18" t="n">
+      <c r="AM18" t="n">
         <v>60</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AN18" t="n">
         <v>46.6</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AO18" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -17960,31 +18186,43 @@
         <v>91</v>
       </c>
       <c r="AD19" t="n">
+        <v>79</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>[-2.78, 0.91]</t>
         </is>
       </c>
-      <c r="AF19" t="n">
+      <c r="AJ19" t="n">
         <v>82.5</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AK19" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>[-1.32, 0.26]</t>
         </is>
       </c>
-      <c r="AI19" t="n">
+      <c r="AM19" t="n">
         <v>87.5</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AN19" t="n">
         <v>41.2</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AO19" t="n">
         <v>26</v>
       </c>
     </row>
@@ -18087,31 +18325,43 @@
         <v>91</v>
       </c>
       <c r="AD20" t="n">
+        <v>58</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>[-1.51, 1.42]</t>
         </is>
       </c>
-      <c r="AF20" t="n">
+      <c r="AJ20" t="n">
         <v>59</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AK20" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>[-1.03, 0.73]</t>
         </is>
       </c>
-      <c r="AI20" t="n">
+      <c r="AM20" t="n">
         <v>61</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AN20" t="n">
         <v>52.3</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AO20" t="n">
         <v>21.4</v>
       </c>
     </row>
@@ -18214,31 +18464,43 @@
         <v>96</v>
       </c>
       <c r="AD21" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH21" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>[-1.88, 1.25]</t>
         </is>
       </c>
-      <c r="AF21" t="n">
+      <c r="AJ21" t="n">
         <v>70</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AK21" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>[-1.13, 0.25]</t>
         </is>
       </c>
-      <c r="AI21" t="n">
+      <c r="AM21" t="n">
         <v>86.5</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AN21" t="n">
         <v>45.2</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AO21" t="n">
         <v>22.6</v>
       </c>
     </row>
@@ -18341,31 +18603,43 @@
         <v>95.5</v>
       </c>
       <c r="AD22" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>[-0.70, 1.35]</t>
         </is>
       </c>
-      <c r="AF22" t="n">
+      <c r="AJ22" t="n">
         <v>33</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AK22" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>[-0.82, 0.61]</t>
         </is>
       </c>
-      <c r="AI22" t="n">
+      <c r="AM22" t="n">
         <v>62.5</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AN22" t="n">
         <v>56.4</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AO22" t="n">
         <v>20.8</v>
       </c>
     </row>
@@ -18468,31 +18742,43 @@
         <v>98</v>
       </c>
       <c r="AD23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AG23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>[-1.07, 1.21]</t>
         </is>
       </c>
-      <c r="AF23" t="n">
+      <c r="AJ23" t="n">
         <v>55.5</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AK23" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>[-0.88, 0.27]</t>
         </is>
       </c>
-      <c r="AI23" t="n">
+      <c r="AM23" t="n">
         <v>82.5</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AN23" t="n">
         <v>51.6</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AO23" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -18595,31 +18881,43 @@
         <v>44.5</v>
       </c>
       <c r="AD24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.62</v>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>[-0.14, 1.42]</t>
         </is>
       </c>
-      <c r="AF24" t="n">
+      <c r="AJ24" t="n">
         <v>6</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AK24" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>[-0.78, 0.33]</t>
         </is>
       </c>
-      <c r="AI24" t="n">
+      <c r="AM24" t="n">
         <v>75</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AN24" t="n">
         <v>61.3</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AO24" t="n">
         <v>20.2</v>
       </c>
     </row>
@@ -18722,31 +19020,43 @@
         <v>75</v>
       </c>
       <c r="AD25" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.23</v>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>[-0.54, 1.22]</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AJ25" t="n">
         <v>31.5</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AK25" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>[-0.68, 0.21]</t>
         </is>
       </c>
-      <c r="AI25" t="n">
+      <c r="AM25" t="n">
         <v>82</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AN25" t="n">
         <v>61.2</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AO25" t="n">
         <v>20.7</v>
       </c>
     </row>
@@ -18849,31 +19159,43 @@
         <v>1</v>
       </c>
       <c r="AD26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>69</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.13</v>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>[0.45, 1.84]</t>
         </is>
       </c>
-      <c r="AF26" t="n">
+      <c r="AJ26" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AK26" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>[-0.74, 0.33]</t>
         </is>
       </c>
-      <c r="AI26" t="n">
+      <c r="AM26" t="n">
         <v>79.5</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AN26" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AO26" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18976,31 +19298,43 @@
         <v>9.5</v>
       </c>
       <c r="AD27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>68</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.64</v>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>[0.03, 1.37]</t>
         </is>
       </c>
-      <c r="AF27" t="n">
+      <c r="AJ27" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AK27" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>[-0.42, 0.21]</t>
         </is>
       </c>
-      <c r="AI27" t="n">
+      <c r="AM27" t="n">
         <v>73.5</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AN27" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AO27" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -19103,31 +19437,43 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[0.73, 2.10]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>35.5</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[0.73, 2.10]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>[-0.64, 0.31]</t>
         </is>
       </c>
-      <c r="AI28" t="n">
+      <c r="AM28" t="n">
         <v>79</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AN28" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AO28" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -19230,31 +19576,43 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[0.39, 1.41]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>35.5</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[0.39, 1.41]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AL29" t="inlineStr">
         <is>
           <t>[-0.32, 0.24]</t>
         </is>
       </c>
-      <c r="AI29" t="n">
+      <c r="AM29" t="n">
         <v>66.5</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AN29" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AO29" t="n">
         <v>16.1</v>
       </c>
     </row>
@@ -30814,6 +31172,721 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>차수</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>유효페르소나</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>게이트통과합계</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>셀최소</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>셀중앙값</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>셀최대</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>남성_10대</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>남성_20대</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>남성_30대</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>남성_40대</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>남성_50대</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>남성_60대</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>남성_70대이상</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>여성_10대</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>여성_20대</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>여성_30대</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>여성_40대</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>여성_50대</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>여성_60대</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>여성_70대이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8168</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5389</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2" t="n">
+        <v>596</v>
+      </c>
+      <c r="H2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I2" t="n">
+        <v>596</v>
+      </c>
+      <c r="J2" t="n">
+        <v>574</v>
+      </c>
+      <c r="K2" t="n">
+        <v>517</v>
+      </c>
+      <c r="L2" t="n">
+        <v>339</v>
+      </c>
+      <c r="M2" t="n">
+        <v>157</v>
+      </c>
+      <c r="N2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O2" t="n">
+        <v>486</v>
+      </c>
+      <c r="P2" t="n">
+        <v>594</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>581</v>
+      </c>
+      <c r="R2" t="n">
+        <v>533</v>
+      </c>
+      <c r="S2" t="n">
+        <v>329</v>
+      </c>
+      <c r="T2" t="n">
+        <v>143</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8165</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E3" t="n">
+        <v>402</v>
+      </c>
+      <c r="F3" t="n">
+        <v>503</v>
+      </c>
+      <c r="G3" t="n">
+        <v>572</v>
+      </c>
+      <c r="H3" t="n">
+        <v>433</v>
+      </c>
+      <c r="I3" t="n">
+        <v>558</v>
+      </c>
+      <c r="J3" t="n">
+        <v>544</v>
+      </c>
+      <c r="K3" t="n">
+        <v>522</v>
+      </c>
+      <c r="L3" t="n">
+        <v>499</v>
+      </c>
+      <c r="M3" t="n">
+        <v>461</v>
+      </c>
+      <c r="N3" t="n">
+        <v>402</v>
+      </c>
+      <c r="O3" t="n">
+        <v>458</v>
+      </c>
+      <c r="P3" t="n">
+        <v>572</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>543</v>
+      </c>
+      <c r="R3" t="n">
+        <v>527</v>
+      </c>
+      <c r="S3" t="n">
+        <v>507</v>
+      </c>
+      <c r="T3" t="n">
+        <v>432</v>
+      </c>
+      <c r="U3" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7938</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4614</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>364</v>
+      </c>
+      <c r="G4" t="n">
+        <v>594</v>
+      </c>
+      <c r="H4" t="n">
+        <v>375</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>559</v>
+      </c>
+      <c r="K4" t="n">
+        <v>438</v>
+      </c>
+      <c r="L4" t="n">
+        <v>245</v>
+      </c>
+      <c r="M4" t="n">
+        <v>74</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O4" t="n">
+        <v>353</v>
+      </c>
+      <c r="P4" t="n">
+        <v>594</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>569</v>
+      </c>
+      <c r="R4" t="n">
+        <v>485</v>
+      </c>
+      <c r="S4" t="n">
+        <v>243</v>
+      </c>
+      <c r="T4" t="n">
+        <v>59</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EXAONE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7794</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6241</v>
+      </c>
+      <c r="E5" t="n">
+        <v>307</v>
+      </c>
+      <c r="F5" t="n">
+        <v>475</v>
+      </c>
+      <c r="G5" t="n">
+        <v>548</v>
+      </c>
+      <c r="H5" t="n">
+        <v>319</v>
+      </c>
+      <c r="I5" t="n">
+        <v>548</v>
+      </c>
+      <c r="J5" t="n">
+        <v>524</v>
+      </c>
+      <c r="K5" t="n">
+        <v>476</v>
+      </c>
+      <c r="L5" t="n">
+        <v>475</v>
+      </c>
+      <c r="M5" t="n">
+        <v>421</v>
+      </c>
+      <c r="N5" t="n">
+        <v>354</v>
+      </c>
+      <c r="O5" t="n">
+        <v>307</v>
+      </c>
+      <c r="P5" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>505</v>
+      </c>
+      <c r="S5" t="n">
+        <v>493</v>
+      </c>
+      <c r="T5" t="n">
+        <v>422</v>
+      </c>
+      <c r="U5" t="n">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>차수</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>보정률</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>보정셋n(평균)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>게이트빈셀수(평균)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>게이트빈셀발생분할%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>게이트최소셀n(평균)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C3" t="n">
+        <v>166</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C4" t="n">
+        <v>255</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>426</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>859</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1729</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2598</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C11" t="n">
+        <v>245</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>414</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>832</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1673</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
